--- a/data/Quina_scraper_surface.xlsx
+++ b/data/Quina_scraper_surface.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Quina_valleys\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF5D7D5-4F07-4183-B0A0-E6949043772A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD4C91C-4FF5-4710-91BD-85BA7B3AC369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="30936" windowHeight="18696" xr2:uid="{51F75AC8-9BCC-468F-8814-35286D6AD1E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{51F75AC8-9BCC-468F-8814-35286D6AD1E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Quina scraper" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="368">
   <si>
     <t>2022.10.BC.MHD-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1144,263 +1144,262 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>E1_GIUR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2_GIUR</t>
+  </si>
+  <si>
+    <t>E3_GIUR</t>
+  </si>
+  <si>
+    <t>Section_asymmetric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quina_scraper</t>
+  </si>
+  <si>
+    <t>Inverse scraper</t>
+  </si>
+  <si>
+    <t>Alternate scraper</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Double</t>
+  </si>
+  <si>
+    <t>Multi</t>
+  </si>
+  <si>
+    <t>Non_cortex</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Lateral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Primary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obverse</t>
+  </si>
+  <si>
+    <t>Inverse</t>
+  </si>
+  <si>
+    <t>Bifacial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alternating</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edge_Angle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invasive_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022.YBC采-11</t>
+  </si>
+  <si>
+    <t>Resharpening_flake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retouch_length_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tot_Direction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alternate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Site_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MHD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PJDD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MHLZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPD_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WYW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZXYLZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NNT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPD_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZKZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZJLZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WGQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QGS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JCW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LJS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HBC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPD_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZKZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HBC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NNT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YJQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022.9.BC.SW-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YJQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NJZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>N_Scar</t>
-  </si>
-  <si>
-    <t>E1_GIUR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E2_GIUR</t>
-  </si>
-  <si>
-    <t>E3_GIUR</t>
-  </si>
-  <si>
-    <t>Section_asymmetric</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Quina_scraper</t>
-  </si>
-  <si>
-    <t>Tranchoir</t>
-  </si>
-  <si>
-    <t>Notched scraper</t>
-  </si>
-  <si>
-    <t>Inverse scraper</t>
-  </si>
-  <si>
-    <t>Alternate scraper</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>Double</t>
-  </si>
-  <si>
-    <t>Multi</t>
-  </si>
-  <si>
-    <t>Non_cortex</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>Lateral</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Primary</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Obverse</t>
-  </si>
-  <si>
-    <t>Inverse</t>
-  </si>
-  <si>
-    <t>Bifacial</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Alternating</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Edge_Angle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Invasive_index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2022.YBC采-11</t>
-  </si>
-  <si>
-    <t>Resharpening_flake</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Retouch_length_index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tot_Direction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Alternate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Site_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MHD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>THC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PJDD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MHLZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DPD_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WYW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZXYLZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NNT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DPD_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZKZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZJLZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WGQ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CFC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QGS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JCW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LJS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HBC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>THC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DPD_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZKZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZZS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HBC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NNT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YJQ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2022.9.BC.SW-8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YJQ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NJZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CFC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FTZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bifacial scraper</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1944,7 +1943,7 @@
         <v>264</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>269</v>
@@ -2055,31 +2054,31 @@
         <v>298</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AN1" s="3" t="s">
         <v>299</v>
       </c>
       <c r="AO1" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="AP1" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="AR1" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="AS1" s="3" t="s">
         <v>199</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AV1" s="1" t="s">
         <v>200</v>
@@ -2088,10 +2087,10 @@
         <v>201</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
@@ -2099,25 +2098,25 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I2" s="6">
         <v>75.88</v>
@@ -2147,7 +2146,7 @@
         <v>150</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S2" s="6">
         <v>3</v>
@@ -2169,7 +2168,7 @@
         <v>25.17736585118746</v>
       </c>
       <c r="AM2" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN2" s="6">
         <f>AVERAGE(S2,Z2,AG2)</f>
@@ -2211,25 +2210,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I3" s="6">
         <v>69.06</v>
@@ -2247,7 +2246,7 @@
         <v>165.05</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S3" s="6">
         <v>3</v>
@@ -2269,7 +2268,7 @@
         <v>20.741455152497892</v>
       </c>
       <c r="AM3" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN3" s="6">
         <f t="shared" ref="AN3:AN66" si="1">AVERAGE(S3,Z3,AG3)</f>
@@ -2311,19 +2310,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>306</v>
+        <v>367</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>190</v>
@@ -2347,7 +2346,7 @@
         <v>141.11000000000001</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="S4" s="6">
         <v>4</v>
@@ -2369,7 +2368,7 @@
         <v>16.978446245134464</v>
       </c>
       <c r="AM4" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AN4" s="6">
         <f t="shared" si="1"/>
@@ -2399,25 +2398,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I5" s="6">
         <v>49</v>
@@ -2435,7 +2434,7 @@
         <v>123.08000000000001</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S5" s="6">
         <v>2</v>
@@ -2457,7 +2456,7 @@
         <v>11.218924640258127</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z5" s="6">
         <v>3</v>
@@ -2479,7 +2478,7 @@
         <v>17.978619638516228</v>
       </c>
       <c r="AM5" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN5" s="6">
         <f t="shared" si="1"/>
@@ -2521,19 +2520,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>191</v>
@@ -2569,7 +2568,7 @@
         <v>121</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S6" s="6">
         <v>3</v>
@@ -2591,7 +2590,7 @@
         <v>8.2021024237235967</v>
       </c>
       <c r="AM6" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN6" s="6">
         <f t="shared" si="1"/>
@@ -2633,19 +2632,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>310</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>191</v>
@@ -2669,7 +2668,7 @@
         <v>204.61</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S7" s="6">
         <v>3</v>
@@ -2691,7 +2690,7 @@
         <v>12.522149670795411</v>
       </c>
       <c r="AM7" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN7" s="6">
         <f t="shared" si="1"/>
@@ -2733,19 +2732,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>191</v>
@@ -2769,7 +2768,7 @@
         <v>163.69999999999999</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S8" s="6">
         <v>3</v>
@@ -2791,7 +2790,7 @@
         <v>32.053079712816839</v>
       </c>
       <c r="Y8" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z8" s="6">
         <v>2</v>
@@ -2813,7 +2812,7 @@
         <v>13.038100222318585</v>
       </c>
       <c r="AM8" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN8" s="6">
         <f t="shared" si="1"/>
@@ -2858,19 +2857,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>190</v>
@@ -2894,7 +2893,7 @@
         <v>152.29999999999998</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S9" s="6">
         <v>3</v>
@@ -2916,7 +2915,7 @@
         <v>19.030131066261088</v>
       </c>
       <c r="AM9" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN9" s="6">
         <f t="shared" si="1"/>
@@ -2958,25 +2957,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>173</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I10" s="6">
         <v>70</v>
@@ -3006,7 +3005,7 @@
         <v>134</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S10" s="6">
         <v>4</v>
@@ -3028,7 +3027,7 @@
         <v>24.896677924802457</v>
       </c>
       <c r="AM10" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN10" s="6">
         <f t="shared" si="1"/>
@@ -3068,19 +3067,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>174</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>190</v>
@@ -3116,7 +3115,7 @@
         <v>110</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S11" s="6">
         <v>3</v>
@@ -3138,7 +3137,7 @@
         <v>15.072669637405969</v>
       </c>
       <c r="Y11" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z11" s="6">
         <v>1</v>
@@ -3160,7 +3159,7 @@
         <v>4.3278392389558444</v>
       </c>
       <c r="AM11" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN11" s="6">
         <f t="shared" si="1"/>
@@ -3205,25 +3204,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I12" s="6">
         <v>65.400000000000006</v>
@@ -3253,7 +3252,7 @@
         <v>141</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S12" s="6">
         <v>2</v>
@@ -3275,7 +3274,7 @@
         <v>17.804829635114952</v>
       </c>
       <c r="Y12" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z12" s="6">
         <v>1</v>
@@ -3297,7 +3296,7 @@
         <v>15.625889274292234</v>
       </c>
       <c r="AM12" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN12" s="6">
         <f t="shared" si="1"/>
@@ -3342,19 +3341,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>176</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>191</v>
@@ -3378,7 +3377,7 @@
         <v>141.42000000000002</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S13" s="6">
         <v>3</v>
@@ -3400,7 +3399,7 @@
         <v>19.706910127176432</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z13" s="6">
         <v>3</v>
@@ -3422,7 +3421,7 @@
         <v>26.006575990805636</v>
       </c>
       <c r="AM13" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN13" s="6">
         <f t="shared" si="1"/>
@@ -3467,25 +3466,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>260</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I14" s="6">
         <v>65.400000000000006</v>
@@ -3515,7 +3514,7 @@
         <v>122</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S14" s="6">
         <v>2</v>
@@ -3537,7 +3536,7 @@
         <v>9.6544106099784219</v>
       </c>
       <c r="AM14" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN14" s="6">
         <f t="shared" si="1"/>
@@ -3579,19 +3578,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>191</v>
@@ -3615,7 +3614,7 @@
         <v>144.73000000000002</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S15" s="6">
         <v>2</v>
@@ -3637,7 +3636,7 @@
         <v>5.6014825589832107</v>
       </c>
       <c r="AM15" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN15" s="6">
         <f t="shared" si="1"/>
@@ -3679,25 +3678,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>169</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I16" s="6">
         <v>60.27</v>
@@ -3715,7 +3714,7 @@
         <v>150.43</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S16" s="6">
         <v>3</v>
@@ -3737,7 +3736,7 @@
         <v>14.816726834199148</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z16" s="6">
         <v>3</v>
@@ -3759,7 +3758,7 @@
         <v>15.195878069926168</v>
       </c>
       <c r="AM16" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN16" s="6">
         <f t="shared" si="1"/>
@@ -3799,19 +3798,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>188</v>
@@ -3835,7 +3834,7 @@
         <v>174.56</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S17" s="6">
         <v>3</v>
@@ -3857,7 +3856,7 @@
         <v>19.40470707729456</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z17" s="6">
         <v>2</v>
@@ -3879,7 +3878,7 @@
         <v>19.122809689875545</v>
       </c>
       <c r="AM17" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="1"/>
@@ -3924,19 +3923,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>191</v>
@@ -3972,7 +3971,7 @@
         <v>117</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S18" s="6">
         <v>2</v>
@@ -3994,7 +3993,7 @@
         <v>9.1893025239203574</v>
       </c>
       <c r="Y18" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z18" s="6">
         <v>2</v>
@@ -4016,7 +4015,7 @@
         <v>9.6219152574665134</v>
       </c>
       <c r="AM18" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN18" s="6">
         <f t="shared" si="1"/>
@@ -4061,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>190</v>
@@ -4097,7 +4096,7 @@
         <v>192.03999999999996</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S19" s="6">
         <v>3</v>
@@ -4119,7 +4118,7 @@
         <v>22.76687568606954</v>
       </c>
       <c r="AM19" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN19" s="6">
         <f t="shared" si="1"/>
@@ -4158,25 +4157,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G20" s="6">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I20" s="6">
         <v>56.13</v>
@@ -4194,7 +4193,7 @@
         <v>147.16</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S20" s="6">
         <v>2</v>
@@ -4216,7 +4215,7 @@
         <v>16.377150863464049</v>
       </c>
       <c r="AM20" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN20" s="6">
         <f t="shared" si="1"/>
@@ -4258,19 +4257,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>190</v>
@@ -4294,7 +4293,7 @@
         <v>160.33000000000001</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S21" s="6">
         <v>3</v>
@@ -4316,7 +4315,7 @@
         <v>17.630273346434858</v>
       </c>
       <c r="AM21" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN21" s="6">
         <f t="shared" si="1"/>
@@ -4355,19 +4354,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>190</v>
@@ -4391,7 +4390,7 @@
         <v>121.94</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S22" s="6">
         <v>2</v>
@@ -4413,7 +4412,7 @@
         <v>8.9885891886005993</v>
       </c>
       <c r="AM22" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN22" s="6">
         <f t="shared" si="1"/>
@@ -4455,25 +4454,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I23" s="6">
         <v>70.03</v>
@@ -4491,7 +4490,7 @@
         <v>174.66</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S23" s="6">
         <v>3</v>
@@ -4513,7 +4512,7 @@
         <v>16.777359243677918</v>
       </c>
       <c r="Y23" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z23" s="6">
         <v>2</v>
@@ -4535,7 +4534,7 @@
         <v>11.196577131452354</v>
       </c>
       <c r="AM23" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN23" s="6">
         <f t="shared" si="1"/>
@@ -4580,25 +4579,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I24" s="6">
         <v>39.299999999999997</v>
@@ -4616,7 +4615,7 @@
         <v>103.33999999999999</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S24" s="6">
         <v>2</v>
@@ -4638,7 +4637,7 @@
         <v>10.746361523073173</v>
       </c>
       <c r="AM24" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN24" s="6">
         <f t="shared" si="1"/>
@@ -4677,25 +4676,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>174</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I25" s="6">
         <v>103.46</v>
@@ -4713,7 +4712,7 @@
         <v>264.04000000000002</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S25" s="6">
         <v>3</v>
@@ -4735,7 +4734,7 @@
         <v>24.31741237289777</v>
       </c>
       <c r="Y25" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z25" s="6">
         <v>2</v>
@@ -4757,7 +4756,7 @@
         <v>23.356222843902469</v>
       </c>
       <c r="AM25" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN25" s="6">
         <f t="shared" si="1"/>
@@ -4799,19 +4798,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>191</v>
@@ -4847,7 +4846,7 @@
         <v>131</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S26" s="6">
         <v>1</v>
@@ -4869,7 +4868,7 @@
         <v>4.9149122657339506</v>
       </c>
       <c r="AM26" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="1"/>
@@ -4911,19 +4910,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>190</v>
@@ -4947,7 +4946,7 @@
         <v>170.32999999999998</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S27" s="6">
         <v>2</v>
@@ -4969,7 +4968,7 @@
         <v>9.0718168662728278</v>
       </c>
       <c r="AM27" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN27" s="6">
         <f t="shared" si="1"/>
@@ -5011,19 +5010,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>188</v>
@@ -5047,7 +5046,7 @@
         <v>189.77</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S28" s="6">
         <v>3</v>
@@ -5069,7 +5068,7 @@
         <v>28.187738430246146</v>
       </c>
       <c r="AM28" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN28" s="6">
         <f t="shared" si="1"/>
@@ -5106,19 +5105,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>188</v>
@@ -5154,7 +5153,7 @@
         <v>133</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S29" s="6">
         <v>2</v>
@@ -5176,7 +5175,7 @@
         <v>7.7074106932948903</v>
       </c>
       <c r="AM29" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN29" s="6">
         <f t="shared" si="1"/>
@@ -5218,25 +5217,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I30" s="6">
         <v>82.39</v>
@@ -5254,7 +5253,7 @@
         <v>238.71</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S30" s="6">
         <v>3</v>
@@ -5276,7 +5275,7 @@
         <v>40.196644433595488</v>
       </c>
       <c r="AM30" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="1"/>
@@ -5313,25 +5312,25 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D31" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="F31" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I31" s="6">
         <v>67.400000000000006</v>
@@ -5361,7 +5360,7 @@
         <v>120</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S31" s="6">
         <v>3</v>
@@ -5383,7 +5382,7 @@
         <v>16.749153827852446</v>
       </c>
       <c r="AM31" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN31" s="6">
         <f t="shared" si="1"/>
@@ -5422,25 +5421,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>173</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I32" s="6">
         <v>74.739999999999995</v>
@@ -5458,7 +5457,7 @@
         <v>199.04</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S32" s="6">
         <v>2</v>
@@ -5480,7 +5479,7 @@
         <v>21.450779901224649</v>
       </c>
       <c r="AM32" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN32" s="6">
         <f t="shared" si="1"/>
@@ -5522,25 +5521,25 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I33" s="6">
         <v>81.459999999999994</v>
@@ -5570,7 +5569,7 @@
         <v>119</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S33" s="6">
         <v>3</v>
@@ -5592,7 +5591,7 @@
         <v>18.922266658129271</v>
       </c>
       <c r="Y33" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z33" s="6">
         <v>3</v>
@@ -5614,7 +5613,7 @@
         <v>19.761319852272681</v>
       </c>
       <c r="AM33" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN33" s="6">
         <f t="shared" si="1"/>
@@ -5659,19 +5658,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>190</v>
@@ -5695,7 +5694,7 @@
         <v>207.08</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S34" s="6">
         <v>2</v>
@@ -5717,7 +5716,7 @@
         <v>35.036401663351207</v>
       </c>
       <c r="AM34" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN34" s="6">
         <f t="shared" si="1"/>
@@ -5759,25 +5758,25 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G35" s="6">
         <v>0</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I35" s="6">
         <v>55.1</v>
@@ -5807,7 +5806,7 @@
         <v>90</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S35" s="6">
         <v>2</v>
@@ -5829,7 +5828,7 @@
         <v>19.336566174175516</v>
       </c>
       <c r="AM35" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN35" s="6">
         <f t="shared" si="1"/>
@@ -5871,19 +5870,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>178</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>188</v>
@@ -5907,7 +5906,7 @@
         <v>215.3</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S36" s="6">
         <v>3</v>
@@ -5929,7 +5928,7 @@
         <v>16.575620592477811</v>
       </c>
       <c r="AM36" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="1"/>
@@ -5971,25 +5970,25 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I37" s="6">
         <v>62.98</v>
@@ -6019,7 +6018,7 @@
         <v>129.35</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S37" s="6">
         <v>3</v>
@@ -6041,7 +6040,7 @@
         <v>24.308705747523518</v>
       </c>
       <c r="Y37" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z37" s="6">
         <v>3</v>
@@ -6063,7 +6062,7 @@
         <v>11.899669099704663</v>
       </c>
       <c r="AM37" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN37" s="6">
         <f t="shared" si="1"/>
@@ -6108,19 +6107,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>174</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>190</v>
@@ -6156,7 +6155,7 @@
         <v>121</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S38" s="6">
         <v>2</v>
@@ -6178,7 +6177,7 @@
         <v>13.697591925711032</v>
       </c>
       <c r="Y38" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z38" s="6">
         <v>3</v>
@@ -6200,7 +6199,7 @@
         <v>11.565121479822277</v>
       </c>
       <c r="AM38" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN38" s="6">
         <f t="shared" si="1"/>
@@ -6245,19 +6244,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>191</v>
@@ -6281,7 +6280,7 @@
         <v>93.23</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S39" s="6">
         <v>3</v>
@@ -6303,7 +6302,7 @@
         <v>10.980873087829764</v>
       </c>
       <c r="AM39" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN39" s="6">
         <f t="shared" si="1"/>
@@ -6345,25 +6344,25 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I40" s="6">
         <v>64.2</v>
@@ -6381,7 +6380,7 @@
         <v>157.76000000000002</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S40" s="6">
         <v>2</v>
@@ -6403,7 +6402,7 @@
         <v>24.262863468692153</v>
       </c>
       <c r="AM40" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="1"/>
@@ -6443,19 +6442,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>188</v>
@@ -6479,7 +6478,7 @@
         <v>150.04000000000002</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S41" s="6">
         <v>3</v>
@@ -6501,7 +6500,7 @@
         <v>16.584395816012016</v>
       </c>
       <c r="AM41" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN41" s="6">
         <f t="shared" si="1"/>
@@ -6543,19 +6542,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>190</v>
@@ -6579,7 +6578,7 @@
         <v>100.45</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S42" s="6">
         <v>4</v>
@@ -6601,7 +6600,7 @@
         <v>15.58841603460546</v>
       </c>
       <c r="AM42" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN42" s="6">
         <f t="shared" si="1"/>
@@ -6643,25 +6642,25 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I43" s="6">
         <v>62.1</v>
@@ -6691,7 +6690,7 @@
         <v>120</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S43" s="6">
         <v>4</v>
@@ -6713,7 +6712,7 @@
         <v>20.867146283813973</v>
       </c>
       <c r="AM43" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN43" s="6">
         <f t="shared" si="1"/>
@@ -6753,19 +6752,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>179</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>190</v>
@@ -6789,7 +6788,7 @@
         <v>212.27</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S44" s="6">
         <v>2</v>
@@ -6811,7 +6810,7 @@
         <v>23.151652374804655</v>
       </c>
       <c r="Y44" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z44" s="6">
         <v>2</v>
@@ -6833,7 +6832,7 @@
         <v>21.054484166571129</v>
       </c>
       <c r="AM44" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN44" s="6">
         <f t="shared" si="1"/>
@@ -6878,25 +6877,25 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I45" s="6">
         <v>71.25</v>
@@ -6926,7 +6925,7 @@
         <v>125.9</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S45" s="6">
         <v>3</v>
@@ -6948,7 +6947,7 @@
         <v>25.21188461329978</v>
       </c>
       <c r="AM45" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN45" s="6">
         <f t="shared" si="1"/>
@@ -6990,25 +6989,25 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I46" s="6">
         <v>75.61</v>
@@ -7026,7 +7025,7 @@
         <v>200.41</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S46" s="6">
         <v>4</v>
@@ -7048,7 +7047,7 @@
         <v>33.913459000265327</v>
       </c>
       <c r="AM46" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN46" s="6">
         <f t="shared" si="1"/>
@@ -7085,25 +7084,25 @@
         <v>265</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I47" s="6">
         <v>36.14</v>
@@ -7121,7 +7120,7 @@
         <v>86.210000000000008</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S47" s="6">
         <v>4</v>
@@ -7143,7 +7142,7 @@
         <v>16.5449691415388</v>
       </c>
       <c r="AM47" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN47" s="6">
         <f t="shared" si="1"/>
@@ -7182,19 +7181,19 @@
         <v>45</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>191</v>
@@ -7218,7 +7217,7 @@
         <v>199.03</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S48" s="6">
         <v>3</v>
@@ -7240,7 +7239,7 @@
         <v>30.506171888961408</v>
       </c>
       <c r="AM48" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN48" s="6">
         <f t="shared" si="1"/>
@@ -7277,25 +7276,25 @@
         <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I49" s="6">
         <v>61.43</v>
@@ -7325,7 +7324,7 @@
         <v>89.7</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S49" s="6">
         <v>3</v>
@@ -7347,7 +7346,7 @@
         <v>12.908637111510565</v>
       </c>
       <c r="AM49" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN49" s="6">
         <f t="shared" si="1"/>
@@ -7389,25 +7388,25 @@
         <v>47</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G50" s="6">
         <v>0</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I50" s="6">
         <v>86.7</v>
@@ -7437,7 +7436,7 @@
         <v>114.9</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S50" s="6">
         <v>3</v>
@@ -7459,7 +7458,7 @@
         <v>21.95923418745085</v>
       </c>
       <c r="Y50" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z50" s="6">
         <v>3</v>
@@ -7481,7 +7480,7 @@
         <v>27.437286406270015</v>
       </c>
       <c r="AM50" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN50" s="6">
         <f t="shared" si="1"/>
@@ -7524,25 +7523,25 @@
         <v>48</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>180</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I51" s="6">
         <v>59.82</v>
@@ -7560,7 +7559,7 @@
         <v>156.19</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S51" s="6">
         <v>2</v>
@@ -7582,7 +7581,7 @@
         <v>10.199022400234661</v>
       </c>
       <c r="Y51" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z51" s="6">
         <v>3</v>
@@ -7604,7 +7603,7 @@
         <v>21.886152387730434</v>
       </c>
       <c r="AM51" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN51" s="6">
         <f t="shared" si="1"/>
@@ -7647,25 +7646,25 @@
         <v>49</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>174</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G52" s="6">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I52" s="6">
         <v>69.94</v>
@@ -7683,7 +7682,7 @@
         <v>181.24000000000004</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S52" s="6">
         <v>3</v>
@@ -7705,7 +7704,7 @@
         <v>16.316802488063733</v>
       </c>
       <c r="Y52" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z52" s="6">
         <v>2</v>
@@ -7727,7 +7726,7 @@
         <v>13.151549281849475</v>
       </c>
       <c r="AM52" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN52" s="6">
         <f t="shared" si="1"/>
@@ -7772,25 +7771,25 @@
         <v>50</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>181</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I53" s="6">
         <v>71.28</v>
@@ -7820,7 +7819,7 @@
         <v>126.05</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S53" s="6">
         <v>3</v>
@@ -7842,7 +7841,7 @@
         <v>11.987854889189681</v>
       </c>
       <c r="Y53" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z53" s="6">
         <v>2</v>
@@ -7864,7 +7863,7 @@
         <v>15.585329061622406</v>
       </c>
       <c r="AM53" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN53" s="6">
         <f t="shared" si="1"/>
@@ -7909,25 +7908,25 @@
         <v>51</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I54" s="6">
         <v>56.6</v>
@@ -7957,7 +7956,7 @@
         <v>121.3</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S54" s="6">
         <v>2</v>
@@ -7979,7 +7978,7 @@
         <v>9.1774333889208304</v>
       </c>
       <c r="Y54" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z54" s="6">
         <v>3</v>
@@ -8001,7 +8000,7 @@
         <v>11.005836219976047</v>
       </c>
       <c r="AM54" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN54" s="6">
         <f t="shared" si="1"/>
@@ -8046,25 +8045,25 @@
         <v>52</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I55" s="6">
         <v>72.53</v>
@@ -8094,7 +8093,7 @@
         <v>130.15</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S55" s="6">
         <v>2</v>
@@ -8116,7 +8115,7 @@
         <v>12.723438085441197</v>
       </c>
       <c r="AM55" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN55" s="6">
         <f t="shared" si="1"/>
@@ -8158,25 +8157,25 @@
         <v>53</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I56" s="6">
         <v>52.67</v>
@@ -8194,7 +8193,7 @@
         <v>166.92</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S56" s="6">
         <v>3</v>
@@ -8216,7 +8215,7 @@
         <v>19.02166329082668</v>
       </c>
       <c r="Y56" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z56" s="6">
         <v>3</v>
@@ -8238,7 +8237,7 @@
         <v>32.442711854572337</v>
       </c>
       <c r="AM56" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN56" s="6">
         <f t="shared" si="1"/>
@@ -8278,25 +8277,25 @@
         <v>54</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I57" s="6">
         <v>62.78</v>
@@ -8314,7 +8313,7 @@
         <v>163.21</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S57" s="6">
         <v>3</v>
@@ -8336,7 +8335,7 @@
         <v>33.348440161387906</v>
       </c>
       <c r="AM57" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN57" s="6">
         <f t="shared" si="1"/>
@@ -8375,25 +8374,25 @@
         <v>55</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>263</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>173</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I58" s="6">
         <v>54.51</v>
@@ -8411,7 +8410,7 @@
         <v>141.30000000000001</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S58" s="6">
         <v>3</v>
@@ -8433,7 +8432,7 @@
         <v>17.840585501738627</v>
       </c>
       <c r="AM58" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN58" s="6">
         <f t="shared" si="1"/>
@@ -8475,25 +8474,25 @@
         <v>56</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>182</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I59" s="6">
         <v>60.11</v>
@@ -8511,7 +8510,7 @@
         <v>175.31</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S59" s="6">
         <v>3</v>
@@ -8533,7 +8532,7 @@
         <v>20.763746314986548</v>
       </c>
       <c r="Y59" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z59" s="6">
         <v>2</v>
@@ -8555,7 +8554,7 @@
         <v>24.644908708517857</v>
       </c>
       <c r="AM59" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN59" s="6">
         <f t="shared" si="1"/>
@@ -8595,25 +8594,25 @@
         <v>57</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>180</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I60" s="6">
         <v>64.3</v>
@@ -8631,7 +8630,7 @@
         <v>171.08</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S60" s="6">
         <v>3</v>
@@ -8653,7 +8652,7 @@
         <v>23.605078634142018</v>
       </c>
       <c r="Y60" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z60" s="6">
         <v>3</v>
@@ -8675,7 +8674,7 @@
         <v>23.817088532793786</v>
       </c>
       <c r="AM60" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN60" s="6">
         <f t="shared" si="1"/>
@@ -8715,25 +8714,25 @@
         <v>58</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I61" s="6">
         <v>58.76</v>
@@ -8763,7 +8762,7 @@
         <v>123.8</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S61" s="6">
         <v>3</v>
@@ -8785,7 +8784,7 @@
         <v>12.171729292522489</v>
       </c>
       <c r="Y61" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Z61" s="6">
         <v>3</v>
@@ -8807,7 +8806,7 @@
         <v>14.742223287611921</v>
       </c>
       <c r="AM61" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN61" s="6">
         <f t="shared" si="1"/>
@@ -8847,25 +8846,25 @@
         <v>59</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D62" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="F62" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I62" s="6">
         <v>65.599999999999994</v>
@@ -8883,7 +8882,7 @@
         <v>167.96</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S62" s="6">
         <v>2</v>
@@ -8905,7 +8904,7 @@
         <v>12.814775688235958</v>
       </c>
       <c r="AM62" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN62" s="6">
         <f t="shared" si="1"/>
@@ -8944,25 +8943,25 @@
         <v>60</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I63" s="6">
         <v>76.319999999999993</v>
@@ -8992,7 +8991,7 @@
         <v>127.2</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S63" s="6">
         <v>2</v>
@@ -9014,7 +9013,7 @@
         <v>12.081517814948691</v>
       </c>
       <c r="AM63" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN63" s="6">
         <f t="shared" si="1"/>
@@ -9056,25 +9055,25 @@
         <v>61</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I64" s="6">
         <v>56.76</v>
@@ -9104,7 +9103,7 @@
         <v>113.15</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S64" s="6">
         <v>2</v>
@@ -9126,7 +9125,7 @@
         <v>14.286101785774161</v>
       </c>
       <c r="Y64" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z64" s="6">
         <v>3</v>
@@ -9148,7 +9147,7 @@
         <v>11.279343113575962</v>
       </c>
       <c r="AM64" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN64" s="6">
         <f t="shared" si="1"/>
@@ -9193,19 +9192,19 @@
         <v>62</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>191</v>
@@ -9229,7 +9228,7 @@
         <v>148.87</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S65" s="6">
         <v>2</v>
@@ -9251,7 +9250,7 @@
         <v>9.4013857242892875</v>
       </c>
       <c r="AM65" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN65" s="6">
         <f t="shared" si="1"/>
@@ -9293,25 +9292,25 @@
         <v>63</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I66" s="6">
         <v>49.6</v>
@@ -9329,7 +9328,7 @@
         <v>136.22</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S66" s="6">
         <v>2</v>
@@ -9351,7 +9350,7 @@
         <v>4.8857465128089927</v>
       </c>
       <c r="Y66" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z66" s="6">
         <v>2</v>
@@ -9373,7 +9372,7 @@
         <v>8.0823281558191677</v>
       </c>
       <c r="AM66" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN66" s="6">
         <f t="shared" si="1"/>
@@ -9418,19 +9417,19 @@
         <v>64</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E67" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>310</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>190</v>
@@ -9454,7 +9453,7 @@
         <v>141.29</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S67" s="6">
         <v>2</v>
@@ -9476,7 +9475,7 @@
         <v>9.7339632717781885</v>
       </c>
       <c r="AM67" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN67" s="6">
         <f t="shared" ref="AN67:AN130" si="7">AVERAGE(S67,Z67,AG67)</f>
@@ -9518,25 +9517,25 @@
         <v>65</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>180</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I68" s="6">
         <v>48.52</v>
@@ -9554,7 +9553,7 @@
         <v>134.85</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S68" s="6">
         <v>3</v>
@@ -9595,7 +9594,7 @@
         <v>25.75939794203514</v>
       </c>
       <c r="AM68" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN68" s="6">
         <f t="shared" si="7"/>
@@ -9635,25 +9634,25 @@
         <v>66</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G69" s="6">
         <v>0</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I69" s="6">
         <v>75</v>
@@ -9671,7 +9670,7 @@
         <v>196.26</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S69" s="6">
         <v>3</v>
@@ -9693,7 +9692,7 @@
         <v>17.277471752066514</v>
       </c>
       <c r="AM69" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN69" s="6">
         <f t="shared" si="7"/>
@@ -9730,25 +9729,25 @@
         <v>67</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I70" s="6">
         <v>50.79</v>
@@ -9766,7 +9765,7 @@
         <v>140.35</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S70" s="6">
         <v>3</v>
@@ -9788,7 +9787,7 @@
         <v>23.027753608190118</v>
       </c>
       <c r="Y70" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z70" s="6">
         <v>3</v>
@@ -9810,7 +9809,7 @@
         <v>20.546452405300197</v>
       </c>
       <c r="AM70" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN70" s="6">
         <f t="shared" si="7"/>
@@ -9850,25 +9849,25 @@
         <v>68</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G71" s="6">
         <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I71" s="6">
         <v>72.53</v>
@@ -9886,7 +9885,7 @@
         <v>210.89</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S71" s="6">
         <v>2</v>
@@ -9908,7 +9907,7 @@
         <v>20.673237657289985</v>
       </c>
       <c r="AM71" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN71" s="6">
         <f t="shared" si="7"/>
@@ -9948,19 +9947,19 @@
         <v>69</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>183</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>190</v>
@@ -9984,7 +9983,7 @@
         <v>144.37</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S72" s="6">
         <v>4</v>
@@ -10006,7 +10005,7 @@
         <v>24.326530830249744</v>
       </c>
       <c r="Y72" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z72" s="6">
         <v>3</v>
@@ -10028,7 +10027,7 @@
         <v>24.283998484236491</v>
       </c>
       <c r="AM72" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN72" s="6">
         <f t="shared" si="7"/>
@@ -10068,25 +10067,25 @@
         <v>70</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G73" s="6">
         <v>0</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I73" s="6">
         <v>44.2</v>
@@ -10104,7 +10103,7 @@
         <v>119.71</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S73" s="6">
         <v>4</v>
@@ -10126,7 +10125,7 @@
         <v>15.914163842325291</v>
       </c>
       <c r="AM73" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN73" s="6">
         <f t="shared" si="7"/>
@@ -10168,19 +10167,19 @@
         <v>71</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>190</v>
@@ -10204,7 +10203,7 @@
         <v>133.32</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S74" s="6">
         <v>2</v>
@@ -10226,7 +10225,7 @@
         <v>8.2474008620335137</v>
       </c>
       <c r="Y74" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z74" s="6">
         <v>2</v>
@@ -10248,7 +10247,7 @@
         <v>15.36766220264513</v>
       </c>
       <c r="AM74" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN74" s="6">
         <f t="shared" si="7"/>
@@ -10293,19 +10292,19 @@
         <v>72</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>190</v>
@@ -10329,7 +10328,7 @@
         <v>139.01000000000002</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S75" s="6">
         <v>3</v>
@@ -10351,7 +10350,7 @@
         <v>13.904358261314172</v>
       </c>
       <c r="AM75" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN75" s="6">
         <f t="shared" si="7"/>
@@ -10391,19 +10390,19 @@
         <v>73</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>188</v>
@@ -10439,7 +10438,7 @@
         <v>139.9</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S76" s="6">
         <v>3</v>
@@ -10461,7 +10460,7 @@
         <v>8.7615300382978507</v>
       </c>
       <c r="AM76" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN76" s="6">
         <f t="shared" si="7"/>
@@ -10503,25 +10502,25 @@
         <v>74</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G77" s="6">
         <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I77" s="6">
         <v>57.27</v>
@@ -10551,7 +10550,7 @@
         <v>133.1</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S77" s="6">
         <v>3</v>
@@ -10573,7 +10572,7 @@
         <v>25.520840608084626</v>
       </c>
       <c r="Y77" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z77" s="6">
         <v>4</v>
@@ -10595,7 +10594,7 @@
         <v>25.035415730972346</v>
       </c>
       <c r="AM77" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN77" s="6">
         <f t="shared" si="7"/>
@@ -10635,25 +10634,25 @@
         <v>75</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I78" s="6">
         <v>47.5</v>
@@ -10683,7 +10682,7 @@
         <v>133.19999999999999</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S78" s="6">
         <v>2</v>
@@ -10705,7 +10704,7 @@
         <v>5.959822514817577</v>
       </c>
       <c r="Y78" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z78" s="6">
         <v>2</v>
@@ -10727,7 +10726,7 @@
         <v>8.61603099009319</v>
       </c>
       <c r="AM78" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN78" s="6">
         <f t="shared" si="7"/>
@@ -10769,25 +10768,25 @@
         <v>76</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I79" s="6">
         <v>65.400000000000006</v>
@@ -10805,7 +10804,7 @@
         <v>147.79000000000002</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S79" s="6">
         <v>2</v>
@@ -10827,7 +10826,7 @@
         <v>12.202448686088331</v>
       </c>
       <c r="AM79" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN79" s="6">
         <f t="shared" si="7"/>
@@ -10866,25 +10865,25 @@
         <v>77</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I80" s="6">
         <v>41.66</v>
@@ -10902,7 +10901,7 @@
         <v>123.41999999999999</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S80" s="6">
         <v>2</v>
@@ -10924,7 +10923,7 @@
         <v>12.97251170051457</v>
       </c>
       <c r="AM80" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN80" s="6">
         <f t="shared" si="7"/>
@@ -10961,25 +10960,25 @@
         <v>78</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I81" s="6">
         <v>57.47</v>
@@ -11009,7 +11008,7 @@
         <v>116.25</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S81" s="6">
         <v>2</v>
@@ -11031,7 +11030,7 @@
         <v>13.510982849600779</v>
       </c>
       <c r="AM81" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN81" s="6">
         <f t="shared" si="7"/>
@@ -11073,25 +11072,25 @@
         <v>79</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G82" s="6">
         <v>0</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I82" s="6">
         <v>44.6</v>
@@ -11109,7 +11108,7 @@
         <v>118.35</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S82" s="6">
         <v>2</v>
@@ -11131,7 +11130,7 @@
         <v>19.655506385712442</v>
       </c>
       <c r="Y82" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z82" s="6">
         <v>2</v>
@@ -11153,7 +11152,7 @@
         <v>10.609752109785402</v>
       </c>
       <c r="AM82" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN82" s="6">
         <f t="shared" si="7"/>
@@ -11196,25 +11195,25 @@
         <v>80</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G83" s="6">
         <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I83" s="6">
         <v>38.9</v>
@@ -11232,7 +11231,7 @@
         <v>101.85999999999999</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S83" s="6">
         <v>3</v>
@@ -11254,7 +11253,7 @@
         <v>18.958689494227176</v>
       </c>
       <c r="Y83" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z83" s="6">
         <v>3</v>
@@ -11276,7 +11275,7 @@
         <v>13.705177957783425</v>
       </c>
       <c r="AM83" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN83" s="6">
         <f t="shared" si="7"/>
@@ -11319,25 +11318,25 @@
         <v>81</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G84" s="6">
         <v>0</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I84" s="6">
         <v>102.28</v>
@@ -11355,7 +11354,7 @@
         <v>288.97999999999996</v>
       </c>
       <c r="R84" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S84" s="6">
         <v>2</v>
@@ -11377,7 +11376,7 @@
         <v>16.493832990870189</v>
       </c>
       <c r="AM84" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN84" s="6">
         <f t="shared" si="7"/>
@@ -11419,25 +11418,25 @@
         <v>82</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D85" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E85" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="F85" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G85" s="6">
         <v>0</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I85" s="6">
         <v>68.150000000000006</v>
@@ -11455,7 +11454,7 @@
         <v>183.54</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S85" s="6">
         <v>2</v>
@@ -11477,7 +11476,7 @@
         <v>19.236627439141742</v>
       </c>
       <c r="AM85" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN85" s="6">
         <f t="shared" si="7"/>
@@ -11516,25 +11515,25 @@
         <v>83</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>263</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G86" s="6">
         <v>0</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I86" s="6">
         <v>52.66</v>
@@ -11552,7 +11551,7 @@
         <v>141.04000000000002</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S86" s="6">
         <v>2</v>
@@ -11574,7 +11573,7 @@
         <v>19.63254054252539</v>
       </c>
       <c r="AM86" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN86" s="6">
         <f t="shared" si="7"/>
@@ -11616,25 +11615,25 @@
         <v>84</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I87" s="6">
         <v>49.48</v>
@@ -11652,7 +11651,7 @@
         <v>125.63</v>
       </c>
       <c r="R87" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S87" s="6">
         <v>3</v>
@@ -11674,7 +11673,7 @@
         <v>11.808498988778878</v>
       </c>
       <c r="Y87" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z87" s="6">
         <v>3</v>
@@ -11696,7 +11695,7 @@
         <v>8.8067770960057192</v>
       </c>
       <c r="AM87" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN87" s="6">
         <f t="shared" si="7"/>
@@ -11739,25 +11738,25 @@
         <v>85</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G88" s="6">
         <v>0</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I88" s="6">
         <v>53.9</v>
@@ -11787,7 +11786,7 @@
         <v>136.9</v>
       </c>
       <c r="R88" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S88" s="6">
         <v>4</v>
@@ -11809,7 +11808,7 @@
         <v>27.090609082310138</v>
       </c>
       <c r="AM88" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN88" s="6">
         <f t="shared" si="7"/>
@@ -11849,25 +11848,25 @@
         <v>86</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G89" s="6">
         <v>0</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I89" s="6">
         <v>46.9</v>
@@ -11885,7 +11884,7 @@
         <v>134.49</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S89" s="6">
         <v>2</v>
@@ -11907,7 +11906,7 @@
         <v>20.219226588887881</v>
       </c>
       <c r="AM89" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN89" s="6">
         <f t="shared" si="7"/>
@@ -11947,25 +11946,25 @@
         <v>87</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I90" s="6">
         <v>43.97</v>
@@ -11983,7 +11982,7 @@
         <v>109.05999999999999</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S90" s="6">
         <v>3</v>
@@ -12005,7 +12004,7 @@
         <v>9.5901917683953588</v>
       </c>
       <c r="AM90" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN90" s="6">
         <f t="shared" si="7"/>
@@ -12047,25 +12046,25 @@
         <v>88</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>263</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G91" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I91" s="6">
         <v>38.4</v>
@@ -12095,7 +12094,7 @@
         <v>135.9</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S91" s="6">
         <v>3</v>
@@ -12117,7 +12116,7 @@
         <v>15.798808758283929</v>
       </c>
       <c r="AM91" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN91" s="6">
         <f t="shared" si="7"/>
@@ -12159,25 +12158,25 @@
         <v>89</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I92" s="6">
         <v>44.8</v>
@@ -12195,7 +12194,7 @@
         <v>102.42000000000002</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S92" s="6">
         <v>2</v>
@@ -12217,7 +12216,7 @@
         <v>14.895636945092344</v>
       </c>
       <c r="AM92" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN92" s="6">
         <f t="shared" si="7"/>
@@ -12259,25 +12258,25 @@
         <v>90</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G93" s="6">
         <v>0</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I93" s="6">
         <v>45.35</v>
@@ -12295,7 +12294,7 @@
         <v>126.56</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S93" s="6">
         <v>3</v>
@@ -12317,7 +12316,7 @@
         <v>16.233634350032396</v>
       </c>
       <c r="AM93" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN93" s="6">
         <f t="shared" si="7"/>
@@ -12354,25 +12353,25 @@
         <v>91</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G94" s="6">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I94" s="6">
         <v>44.37</v>
@@ -12390,7 +12389,7 @@
         <v>112.82</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S94" s="6">
         <v>2</v>
@@ -12412,7 +12411,7 @@
         <v>12.453495055824163</v>
       </c>
       <c r="AM94" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN94" s="6">
         <f t="shared" si="7"/>
@@ -12449,19 +12448,19 @@
         <v>92</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G95" s="6" t="s">
         <v>191</v>
@@ -12485,7 +12484,7 @@
         <v>262.13</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S95" s="6">
         <v>4</v>
@@ -12507,7 +12506,7 @@
         <v>40.286132340769697</v>
       </c>
       <c r="AM95" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN95" s="6">
         <f t="shared" si="7"/>
@@ -12546,25 +12545,25 @@
         <v>93</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I96" s="6">
         <v>39.6</v>
@@ -12582,7 +12581,7 @@
         <v>111.59</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S96" s="6">
         <v>3</v>
@@ -12604,7 +12603,7 @@
         <v>15.546778903660144</v>
       </c>
       <c r="AM96" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN96" s="6">
         <f t="shared" si="7"/>
@@ -12646,25 +12645,25 @@
         <v>94</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I97" s="6">
         <v>54.67</v>
@@ -12694,7 +12693,7 @@
         <v>129.5</v>
       </c>
       <c r="R97" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S97" s="6">
         <v>3</v>
@@ -12716,7 +12715,7 @@
         <v>12.164572889883988</v>
       </c>
       <c r="AM97" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN97" s="6">
         <f t="shared" si="7"/>
@@ -12758,25 +12757,25 @@
         <v>95</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>180</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I98" s="6">
         <v>55.1</v>
@@ -12794,7 +12793,7 @@
         <v>156.32</v>
       </c>
       <c r="R98" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S98" s="6">
         <v>3</v>
@@ -12816,7 +12815,7 @@
         <v>24.428732564044967</v>
       </c>
       <c r="Y98" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z98" s="6">
         <v>4</v>
@@ -12838,7 +12837,7 @@
         <v>14.255137057322228</v>
       </c>
       <c r="AM98" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN98" s="6">
         <f t="shared" si="7"/>
@@ -12878,25 +12877,25 @@
         <v>96</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G99" s="6">
         <v>0</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I99" s="6">
         <v>45.95</v>
@@ -12926,7 +12925,7 @@
         <v>74.849999999999994</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S99" s="6">
         <v>2</v>
@@ -12948,7 +12947,7 @@
         <v>9.6822749644449448</v>
       </c>
       <c r="Y99" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z99" s="6">
         <v>2</v>
@@ -12970,7 +12969,7 @@
         <v>13.875228885746751</v>
       </c>
       <c r="AM99" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN99" s="6">
         <f t="shared" si="7"/>
@@ -13015,25 +13014,25 @@
         <v>97</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G100" s="6">
         <v>0</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I100" s="6">
         <v>63.84</v>
@@ -13051,7 +13050,7 @@
         <v>179.26000000000005</v>
       </c>
       <c r="R100" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S100" s="6">
         <v>3</v>
@@ -13073,7 +13072,7 @@
         <v>13.667455695918255</v>
       </c>
       <c r="AM100" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN100" s="6">
         <f t="shared" si="7"/>
@@ -13113,25 +13112,25 @@
         <v>98</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G101" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I101" s="6">
         <v>58.95</v>
@@ -13149,7 +13148,7 @@
         <v>159.19</v>
       </c>
       <c r="R101" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S101" s="6">
         <v>2</v>
@@ -13171,7 +13170,7 @@
         <v>16.996741162534342</v>
       </c>
       <c r="AM101" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN101" s="6">
         <f t="shared" si="7"/>
@@ -13208,19 +13207,19 @@
         <v>99</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>188</v>
@@ -13244,7 +13243,7 @@
         <v>200.05</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S102" s="6">
         <v>2</v>
@@ -13266,7 +13265,7 @@
         <v>26.488901940201846</v>
       </c>
       <c r="AM102" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN102" s="6">
         <f t="shared" si="7"/>
@@ -13308,25 +13307,25 @@
         <v>266</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G103" s="6">
         <v>0</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I103" s="6">
         <v>97.37</v>
@@ -13344,7 +13343,7 @@
         <v>205.82999999999998</v>
       </c>
       <c r="R103" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S103" s="6">
         <v>2</v>
@@ -13366,7 +13365,7 @@
         <v>27.988509377503501</v>
       </c>
       <c r="AM103" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN103" s="6">
         <f t="shared" si="7"/>
@@ -13406,25 +13405,25 @@
         <v>100</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>182</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I104" s="6">
         <v>75.599999999999994</v>
@@ -13442,7 +13441,7 @@
         <v>213.57999999999998</v>
       </c>
       <c r="R104" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S104" s="6">
         <v>4</v>
@@ -13464,7 +13463,7 @@
         <v>33.19494347919219</v>
       </c>
       <c r="Y104" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z104" s="6">
         <v>2</v>
@@ -13486,7 +13485,7 @@
         <v>26.131803082391563</v>
       </c>
       <c r="AM104" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN104" s="6">
         <f t="shared" si="7"/>
@@ -13528,25 +13527,25 @@
         <v>101</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G105" s="6">
         <v>0</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I105" s="6">
         <v>65.52</v>
@@ -13576,7 +13575,7 @@
         <v>116.85</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S105" s="6">
         <v>2</v>
@@ -13598,7 +13597,7 @@
         <v>10.923299264545177</v>
       </c>
       <c r="AM105" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN105" s="6">
         <f t="shared" si="7"/>
@@ -13640,19 +13639,19 @@
         <v>102</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>190</v>
@@ -13676,7 +13675,7 @@
         <v>179.59</v>
       </c>
       <c r="R106" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S106" s="6">
         <v>3</v>
@@ -13698,7 +13697,7 @@
         <v>15.374108955161219</v>
       </c>
       <c r="Y106" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z106" s="6">
         <v>3</v>
@@ -13720,7 +13719,7 @@
         <v>15.967340440012162</v>
       </c>
       <c r="AM106" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN106" s="6">
         <f t="shared" si="7"/>
@@ -13762,25 +13761,25 @@
         <v>103</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>180</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I107" s="6">
         <v>55.2</v>
@@ -13798,7 +13797,7 @@
         <v>147.94999999999999</v>
       </c>
       <c r="R107" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S107" s="6">
         <v>2</v>
@@ -13820,7 +13819,7 @@
         <v>19.478883671101229</v>
       </c>
       <c r="Y107" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z107" s="6">
         <v>3</v>
@@ -13842,7 +13841,7 @@
         <v>19.826925643298019</v>
       </c>
       <c r="AM107" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN107" s="6">
         <f t="shared" si="7"/>
@@ -13882,19 +13881,19 @@
         <v>104</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>169</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>191</v>
@@ -13930,7 +13929,7 @@
         <v>126.05</v>
       </c>
       <c r="R108" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S108" s="6">
         <v>2</v>
@@ -13952,7 +13951,7 @@
         <v>15.975377814185748</v>
       </c>
       <c r="AM108" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN108" s="6">
         <f t="shared" si="7"/>
@@ -13994,25 +13993,25 @@
         <v>105</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G109" s="6" t="s">
         <v>192</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I109" s="6">
         <v>48.61</v>
@@ -14042,7 +14041,7 @@
         <v>126.2</v>
       </c>
       <c r="R109" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S109" s="6">
         <v>2</v>
@@ -14064,7 +14063,7 @@
         <v>9.8014294725450366</v>
       </c>
       <c r="AM109" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN109" s="6">
         <f t="shared" si="7"/>
@@ -14106,25 +14105,25 @@
         <v>106</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D110" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E110" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E110" s="6" t="s">
+      <c r="F110" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>311</v>
       </c>
       <c r="G110" s="6">
         <v>0</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I110" s="6">
         <v>52.2</v>
@@ -14142,7 +14141,7 @@
         <v>164.24</v>
       </c>
       <c r="R110" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S110" s="6">
         <v>3</v>
@@ -14164,7 +14163,7 @@
         <v>17.312110548163123</v>
       </c>
       <c r="Y110" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z110" s="6">
         <v>3</v>
@@ -14186,7 +14185,7 @@
         <v>11.633798074173074</v>
       </c>
       <c r="AM110" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN110" s="6">
         <f t="shared" si="7"/>
@@ -14226,25 +14225,25 @@
         <v>107</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G111" s="6">
         <v>0</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I111" s="6">
         <v>53.45</v>
@@ -14262,7 +14261,7 @@
         <v>147.34</v>
       </c>
       <c r="R111" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S111" s="6">
         <v>3</v>
@@ -14284,7 +14283,7 @@
         <v>17.697223598044278</v>
       </c>
       <c r="AM111" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN111" s="6">
         <f t="shared" si="7"/>
@@ -14321,25 +14320,25 @@
         <v>108</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G112" s="6">
         <v>0</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I112" s="6">
         <v>50.3</v>
@@ -14357,7 +14356,7 @@
         <v>134.24</v>
       </c>
       <c r="R112" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S112" s="6">
         <v>3</v>
@@ -14379,7 +14378,7 @@
         <v>24.087010291486969</v>
       </c>
       <c r="AM112" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN112" s="6">
         <f t="shared" si="7"/>
@@ -14416,25 +14415,25 @@
         <v>109</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G113" s="6">
         <v>0</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I113" s="6">
         <v>47.12</v>
@@ -14452,7 +14451,7 @@
         <v>134.88999999999999</v>
       </c>
       <c r="R113" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S113" s="6">
         <v>2</v>
@@ -14474,7 +14473,7 @@
         <v>9.3809786483741231</v>
       </c>
       <c r="AM113" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN113" s="6">
         <f t="shared" si="7"/>
@@ -14516,25 +14515,25 @@
         <v>110</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G114" s="6">
         <v>0</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I114" s="6">
         <v>34.5</v>
@@ -14552,7 +14551,7 @@
         <v>91.73</v>
       </c>
       <c r="R114" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S114" s="6">
         <v>3</v>
@@ -14574,7 +14573,7 @@
         <v>8.1506648823278276</v>
       </c>
       <c r="Y114" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z114" s="6">
         <v>3</v>
@@ -14596,7 +14595,7 @@
         <v>12.955234861698868</v>
       </c>
       <c r="AM114" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN114" s="6">
         <f t="shared" si="7"/>
@@ -14639,25 +14638,25 @@
         <v>111</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G115" s="6">
         <v>0</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I115" s="6">
         <v>37.1</v>
@@ -14675,7 +14674,7 @@
         <v>97.609999999999985</v>
       </c>
       <c r="R115" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S115" s="6">
         <v>2</v>
@@ -14697,7 +14696,7 @@
         <v>13.229550300040245</v>
       </c>
       <c r="AM115" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN115" s="6">
         <f t="shared" si="7"/>
@@ -14739,25 +14738,25 @@
         <v>112</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D116" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E116" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E116" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="F116" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G116" s="6">
         <v>0</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I116" s="6">
         <v>39.9</v>
@@ -14775,7 +14774,7 @@
         <v>93.46</v>
       </c>
       <c r="R116" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S116" s="6">
         <v>4</v>
@@ -14797,7 +14796,7 @@
         <v>16.932276742751501</v>
       </c>
       <c r="AM116" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN116" s="6">
         <f t="shared" si="7"/>
@@ -14837,19 +14836,19 @@
         <v>113</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>181</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>191</v>
@@ -14885,7 +14884,7 @@
         <v>125.75</v>
       </c>
       <c r="R117" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S117" s="6">
         <v>2</v>
@@ -14907,7 +14906,7 @@
         <v>19.138298776183262</v>
       </c>
       <c r="Y117" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z117" s="6">
         <v>2</v>
@@ -14929,7 +14928,7 @@
         <v>11.697720148751639</v>
       </c>
       <c r="AM117" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN117" s="6">
         <f t="shared" si="7"/>
@@ -14972,25 +14971,25 @@
         <v>114</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>178</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I118" s="6">
         <v>65.95</v>
@@ -15020,7 +15019,7 @@
         <v>121.3</v>
       </c>
       <c r="R118" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S118" s="6">
         <v>3</v>
@@ -15042,7 +15041,7 @@
         <v>14.185912974871849</v>
       </c>
       <c r="AM118" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN118" s="6">
         <f t="shared" si="7"/>
@@ -15084,25 +15083,25 @@
         <v>115</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G119" s="6">
         <v>0</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I119" s="6">
         <v>57.65</v>
@@ -15132,7 +15131,7 @@
         <v>96</v>
       </c>
       <c r="R119" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S119" s="6">
         <v>2</v>
@@ -15154,7 +15153,7 @@
         <v>6.6488813318914346</v>
       </c>
       <c r="AM119" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN119" s="6">
         <f t="shared" si="7"/>
@@ -15196,25 +15195,25 @@
         <v>116</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>185</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G120" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I120" s="6">
         <v>59.7</v>
@@ -15244,7 +15243,7 @@
         <v>117.75</v>
       </c>
       <c r="R120" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S120" s="6">
         <v>2</v>
@@ -15266,7 +15265,7 @@
         <v>7.053223012741995</v>
       </c>
       <c r="Y120" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z120" s="6">
         <v>2</v>
@@ -15288,7 +15287,7 @@
         <v>8.9110751180113983</v>
       </c>
       <c r="AM120" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN120" s="6">
         <f t="shared" si="7"/>
@@ -15333,25 +15332,25 @@
         <v>117</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G121" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I121" s="6">
         <v>70.510000000000005</v>
@@ -15381,7 +15380,7 @@
         <v>126.05</v>
       </c>
       <c r="R121" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S121" s="6">
         <v>3</v>
@@ -15403,7 +15402,7 @@
         <v>18.484892444644593</v>
       </c>
       <c r="AM121" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN121" s="6">
         <f t="shared" si="7"/>
@@ -15445,25 +15444,25 @@
         <v>118</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G122" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I122" s="6">
         <v>63.98</v>
@@ -15481,7 +15480,7 @@
         <v>191.82</v>
       </c>
       <c r="R122" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S122" s="6">
         <v>4</v>
@@ -15503,7 +15502,7 @@
         <v>28.650890488652543</v>
       </c>
       <c r="AM122" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN122" s="6">
         <f t="shared" si="7"/>
@@ -15542,25 +15541,25 @@
         <v>119</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G123" s="6">
         <v>0</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I123" s="6">
         <v>54.1</v>
@@ -15590,7 +15589,7 @@
         <v>137.9</v>
       </c>
       <c r="R123" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S123" s="6">
         <v>3</v>
@@ -15612,7 +15611,7 @@
         <v>12.043187501813902</v>
       </c>
       <c r="AM123" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN123" s="6">
         <f t="shared" si="7"/>
@@ -15651,25 +15650,25 @@
         <v>120</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G124" s="6">
         <v>0</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I124" s="6">
         <v>53.3</v>
@@ -15687,7 +15686,7 @@
         <v>158.82</v>
       </c>
       <c r="R124" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S124" s="6">
         <v>3</v>
@@ -15709,7 +15708,7 @@
         <v>25.249537227980749</v>
       </c>
       <c r="AM124" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN124" s="6">
         <f t="shared" si="7"/>
@@ -15749,25 +15748,25 @@
         <v>267</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G125" s="6">
         <v>0</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I125" s="6">
         <v>37</v>
@@ -15785,7 +15784,7 @@
         <v>98.789999999999992</v>
       </c>
       <c r="R125" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S125" s="6">
         <v>2</v>
@@ -15807,7 +15806,7 @@
         <v>8.0598872825196981</v>
       </c>
       <c r="AM125" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN125" s="6">
         <f t="shared" si="7"/>
@@ -15849,25 +15848,25 @@
         <v>121</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E126" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E126" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="F126" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G126" s="6">
         <v>0</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I126" s="6">
         <v>71.099999999999994</v>
@@ -15885,7 +15884,7 @@
         <v>180.51999999999998</v>
       </c>
       <c r="R126" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S126" s="6">
         <v>3</v>
@@ -15907,7 +15906,7 @@
         <v>14.318826673198785</v>
       </c>
       <c r="AM126" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN126" s="6">
         <f t="shared" si="7"/>
@@ -15949,25 +15948,25 @@
         <v>122</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D127" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E127" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E127" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="F127" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G127" s="6">
         <v>0</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I127" s="6">
         <v>51.56</v>
@@ -15985,7 +15984,7 @@
         <v>161.92999999999998</v>
       </c>
       <c r="R127" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S127" s="6">
         <v>3</v>
@@ -16007,7 +16006,7 @@
         <v>17.684486397343925</v>
       </c>
       <c r="Y127" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z127" s="6">
         <v>2</v>
@@ -16029,7 +16028,7 @@
         <v>14.603596931447349</v>
       </c>
       <c r="AF127" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG127" s="6">
         <v>2</v>
@@ -16051,7 +16050,7 @@
         <v>15.633778798885512</v>
       </c>
       <c r="AM127" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN127" s="6">
         <f t="shared" si="7"/>
@@ -16099,25 +16098,25 @@
         <v>123</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G128" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I128" s="6">
         <v>54.86</v>
@@ -16147,7 +16146,7 @@
         <v>138</v>
       </c>
       <c r="R128" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S128" s="6">
         <v>3</v>
@@ -16169,7 +16168,7 @@
         <v>29.180145508478052</v>
       </c>
       <c r="Y128" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z128" s="6">
         <v>3</v>
@@ -16191,7 +16190,7 @@
         <v>22.416314404959227</v>
       </c>
       <c r="AF128" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG128" s="6">
         <v>4</v>
@@ -16213,7 +16212,7 @@
         <v>27.614083259533793</v>
       </c>
       <c r="AM128" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN128" s="6">
         <f t="shared" si="7"/>
@@ -16259,25 +16258,25 @@
         <v>124</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>169</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I129" s="6">
         <v>48.5</v>
@@ -16307,7 +16306,7 @@
         <v>138</v>
       </c>
       <c r="R129" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S129" s="6">
         <v>4</v>
@@ -16329,7 +16328,7 @@
         <v>19.723455782677814</v>
       </c>
       <c r="Y129" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z129" s="6">
         <v>4</v>
@@ -16351,7 +16350,7 @@
         <v>7.7072672124512112</v>
       </c>
       <c r="AF129" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG129" s="6">
         <v>4</v>
@@ -16373,7 +16372,7 @@
         <v>15.161016028135364</v>
       </c>
       <c r="AM129" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN129" s="6">
         <f t="shared" si="7"/>
@@ -16418,25 +16417,25 @@
         <v>125</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E130" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>309</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>312</v>
       </c>
       <c r="G130" s="6">
         <v>0</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I130" s="6">
         <v>72.31</v>
@@ -16454,7 +16453,7 @@
         <v>220.98000000000002</v>
       </c>
       <c r="R130" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S130" s="6">
         <v>3</v>
@@ -16476,7 +16475,7 @@
         <v>22.046368726195382</v>
       </c>
       <c r="Y130" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z130" s="6">
         <v>3</v>
@@ -16498,7 +16497,7 @@
         <v>18.246566222391351</v>
       </c>
       <c r="AF130" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG130" s="6">
         <v>4</v>
@@ -16520,7 +16519,7 @@
         <v>21.937802575723325</v>
       </c>
       <c r="AM130" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN130" s="6">
         <f t="shared" si="7"/>
@@ -16568,25 +16567,25 @@
         <v>126</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G131" s="6">
         <v>0</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I131" s="6">
         <v>76.510000000000005</v>
@@ -16604,7 +16603,7 @@
         <v>213.77</v>
       </c>
       <c r="R131" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S131" s="6">
         <v>3</v>
@@ -16626,7 +16625,7 @@
         <v>27.508686717113946</v>
       </c>
       <c r="Y131" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z131" s="6">
         <v>2</v>
@@ -16648,7 +16647,7 @@
         <v>19.192219804649216</v>
       </c>
       <c r="AM131" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN131" s="6">
         <f t="shared" ref="AN131:AN167" si="14">AVERAGE(S131,Z131,AG131)</f>
@@ -16691,25 +16690,25 @@
         <v>127</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G132" s="6">
         <v>0</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I132" s="6">
         <v>43.76</v>
@@ -16727,7 +16726,7 @@
         <v>100.07</v>
       </c>
       <c r="R132" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S132" s="6">
         <v>3</v>
@@ -16749,7 +16748,7 @@
         <v>22.754996225217404</v>
       </c>
       <c r="Y132" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z132" s="6">
         <v>4</v>
@@ -16771,7 +16770,7 @@
         <v>21.898365595563895</v>
       </c>
       <c r="AF132" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG132" s="6">
         <v>4</v>
@@ -16793,7 +16792,7 @@
         <v>18.300770099567362</v>
       </c>
       <c r="AM132" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN132" s="6">
         <f t="shared" si="14"/>
@@ -16839,19 +16838,19 @@
         <v>128</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G133" s="6" t="s">
         <v>191</v>
@@ -16887,7 +16886,7 @@
         <v>128</v>
       </c>
       <c r="R133" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S133" s="6">
         <v>2</v>
@@ -16909,7 +16908,7 @@
         <v>29.374636853482713</v>
       </c>
       <c r="Y133" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z133" s="6">
         <v>2</v>
@@ -16931,7 +16930,7 @@
         <v>30.981584280864471</v>
       </c>
       <c r="AM133" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN133" s="6">
         <f t="shared" si="14"/>
@@ -16976,25 +16975,25 @@
         <v>129</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I134" s="6">
         <v>60.43</v>
@@ -17024,7 +17023,7 @@
         <v>119</v>
       </c>
       <c r="R134" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S134" s="6">
         <v>4</v>
@@ -17046,7 +17045,7 @@
         <v>31.066851608554792</v>
       </c>
       <c r="Y134" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z134" s="6">
         <v>3</v>
@@ -17068,7 +17067,7 @@
         <v>20.069451848531756</v>
       </c>
       <c r="AM134" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN134" s="6">
         <f t="shared" si="14"/>
@@ -17111,25 +17110,25 @@
         <v>130</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G135" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I135" s="6">
         <v>60.09</v>
@@ -17159,7 +17158,7 @@
         <v>91</v>
       </c>
       <c r="R135" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S135" s="6">
         <v>3</v>
@@ -17181,7 +17180,7 @@
         <v>17.61742713148184</v>
       </c>
       <c r="Y135" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z135" s="6">
         <v>4</v>
@@ -17203,7 +17202,7 @@
         <v>20.40251382373123</v>
       </c>
       <c r="AF135" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG135" s="6">
         <v>3</v>
@@ -17225,7 +17224,7 @@
         <v>19.236519620151604</v>
       </c>
       <c r="AM135" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN135" s="6">
         <f t="shared" si="14"/>
@@ -17273,25 +17272,25 @@
         <v>131</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G136" s="6">
         <v>0</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I136" s="6">
         <v>54.76</v>
@@ -17309,7 +17308,7 @@
         <v>146.15</v>
       </c>
       <c r="R136" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S136" s="6">
         <v>4</v>
@@ -17331,7 +17330,7 @@
         <v>23.370109092921847</v>
       </c>
       <c r="Y136" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z136" s="6">
         <v>4</v>
@@ -17353,7 +17352,7 @@
         <v>21.626817496693231</v>
       </c>
       <c r="AM136" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN136" s="6">
         <f t="shared" si="14"/>
@@ -17395,25 +17394,25 @@
         <v>132</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G137" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I137" s="6">
         <v>64.13</v>
@@ -17431,7 +17430,7 @@
         <v>160.4</v>
       </c>
       <c r="R137" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S137" s="6">
         <v>2</v>
@@ -17453,7 +17452,7 @@
         <v>15.097426081425073</v>
       </c>
       <c r="Y137" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z137" s="6">
         <v>4</v>
@@ -17475,7 +17474,7 @@
         <v>27.410833748324947</v>
       </c>
       <c r="AF137" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG137" s="6">
         <v>3</v>
@@ -17497,7 +17496,7 @@
         <v>20.284642510167494</v>
       </c>
       <c r="AM137" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN137" s="6">
         <f t="shared" si="14"/>
@@ -17545,25 +17544,25 @@
         <v>133</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G138" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I138" s="6">
         <v>74.3</v>
@@ -17581,7 +17580,7 @@
         <v>176.94</v>
       </c>
       <c r="R138" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S138" s="6">
         <v>4</v>
@@ -17603,7 +17602,7 @@
         <v>24.963901530252578</v>
       </c>
       <c r="AM138" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN138" s="6">
         <f t="shared" si="14"/>
@@ -17642,25 +17641,25 @@
         <v>134</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>173</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G139" s="6">
         <v>0</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I139" s="6">
         <v>69.62</v>
@@ -17690,7 +17689,7 @@
         <v>127</v>
       </c>
       <c r="R139" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S139" s="6">
         <v>3</v>
@@ -17712,7 +17711,7 @@
         <v>32.134978495218</v>
       </c>
       <c r="AM139" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN139" s="6">
         <f t="shared" si="14"/>
@@ -17752,19 +17751,19 @@
         <v>135</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>190</v>
@@ -17788,7 +17787,7 @@
         <v>123.83</v>
       </c>
       <c r="R140" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S140" s="6">
         <v>4</v>
@@ -17810,7 +17809,7 @@
         <v>22.703004524387126</v>
       </c>
       <c r="AM140" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN140" s="6">
         <f t="shared" si="14"/>
@@ -17850,25 +17849,25 @@
         <v>136</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>180</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G141" s="6">
         <v>0</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I141" s="6">
         <v>50.1</v>
@@ -17886,7 +17885,7 @@
         <v>124.75</v>
       </c>
       <c r="R141" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S141" s="6">
         <v>4</v>
@@ -17908,7 +17907,7 @@
         <v>31.317185834445979</v>
       </c>
       <c r="Y141" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z141" s="6">
         <v>3</v>
@@ -17930,7 +17929,7 @@
         <v>24.883160207632706</v>
       </c>
       <c r="AM141" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN141" s="6">
         <f t="shared" si="14"/>
@@ -17973,25 +17972,25 @@
         <v>137</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G142" s="6">
         <v>0</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I142" s="6">
         <v>61.22</v>
@@ -18009,7 +18008,7 @@
         <v>172</v>
       </c>
       <c r="R142" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S142" s="6">
         <v>2</v>
@@ -18031,7 +18030,7 @@
         <v>26.017774633661272</v>
       </c>
       <c r="AM142" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN142" s="6">
         <f t="shared" si="14"/>
@@ -18071,19 +18070,19 @@
         <v>138</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D143" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E143" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E143" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="F143" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G143" s="6" t="s">
         <v>190</v>
@@ -18107,7 +18106,7 @@
         <v>166.45</v>
       </c>
       <c r="R143" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S143" s="6">
         <v>3</v>
@@ -18129,7 +18128,7 @@
         <v>20.389869128911052</v>
       </c>
       <c r="AM143" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN143" s="6">
         <f t="shared" si="14"/>
@@ -18171,25 +18170,25 @@
         <v>139</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I144" s="6">
         <v>40.29</v>
@@ -18219,7 +18218,7 @@
         <v>115</v>
       </c>
       <c r="R144" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S144" s="6">
         <v>2</v>
@@ -18241,7 +18240,7 @@
         <v>11.72750097173159</v>
       </c>
       <c r="AM144" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN144" s="6">
         <f t="shared" si="14"/>
@@ -18283,25 +18282,25 @@
         <v>140</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G145" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H145" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I145" s="6">
         <v>48.42</v>
@@ -18319,7 +18318,7 @@
         <v>127.92</v>
       </c>
       <c r="R145" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S145" s="6">
         <v>3</v>
@@ -18341,7 +18340,7 @@
         <v>17.855798466913008</v>
       </c>
       <c r="Y145" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z145" s="6">
         <v>3</v>
@@ -18363,7 +18362,7 @@
         <v>21.615954283399908</v>
       </c>
       <c r="AF145" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG145" s="6">
         <v>2</v>
@@ -18385,7 +18384,7 @@
         <v>23.15050364244151</v>
       </c>
       <c r="AM145" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN145" s="6">
         <f t="shared" si="14"/>
@@ -18431,19 +18430,19 @@
         <v>141</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G146" s="6" t="s">
         <v>190</v>
@@ -18479,7 +18478,7 @@
         <v>131</v>
       </c>
       <c r="R146" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S146" s="6">
         <v>2</v>
@@ -18501,7 +18500,7 @@
         <v>13.096551326554064</v>
       </c>
       <c r="AM146" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN146" s="6">
         <f t="shared" si="14"/>
@@ -18543,19 +18542,19 @@
         <v>268</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E147" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G147" s="6" t="s">
         <v>191</v>
@@ -18591,7 +18590,7 @@
         <v>115</v>
       </c>
       <c r="R147" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S147" s="6">
         <v>3</v>
@@ -18613,7 +18612,7 @@
         <v>24.28904869258222</v>
       </c>
       <c r="AM147" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN147" s="6">
         <f t="shared" si="14"/>
@@ -18653,25 +18652,25 @@
         <v>142</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G148" s="6">
         <v>0</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I148" s="6">
         <v>27.9</v>
@@ -18689,7 +18688,7 @@
         <v>84.15</v>
       </c>
       <c r="R148" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S148" s="6">
         <v>3</v>
@@ -18711,7 +18710,7 @@
         <v>19.95448531604065</v>
       </c>
       <c r="AM148" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN148" s="6">
         <f t="shared" si="14"/>
@@ -18751,25 +18750,25 @@
         <v>143</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E149" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G149" s="6">
         <v>0</v>
       </c>
       <c r="H149" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I149" s="6">
         <v>43.73</v>
@@ -18787,7 +18786,7 @@
         <v>113.3</v>
       </c>
       <c r="R149" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S149" s="6">
         <v>3</v>
@@ -18809,7 +18808,7 @@
         <v>16.058824361096757</v>
       </c>
       <c r="AM149" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN149" s="6">
         <f t="shared" si="14"/>
@@ -18849,25 +18848,25 @@
         <v>144</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>173</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G150" s="6">
         <v>0</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I150" s="6">
         <v>86.27</v>
@@ -18885,7 +18884,7 @@
         <v>222.47000000000003</v>
       </c>
       <c r="R150" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S150" s="6">
         <v>4</v>
@@ -18907,7 +18906,7 @@
         <v>47.707076560417086</v>
       </c>
       <c r="AM150" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN150" s="6">
         <f t="shared" si="14"/>
@@ -18944,19 +18943,19 @@
         <v>145</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E151" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G151" s="6" t="s">
         <v>191</v>
@@ -18980,7 +18979,7 @@
         <v>167.64</v>
       </c>
       <c r="R151" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S151" s="6">
         <v>4</v>
@@ -19002,7 +19001,7 @@
         <v>27.996640575536681</v>
       </c>
       <c r="AM151" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN151" s="6">
         <f t="shared" si="14"/>
@@ -19041,25 +19040,25 @@
         <v>146</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G152" s="6">
         <v>0</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I152" s="6">
         <v>56.24</v>
@@ -19077,7 +19076,7 @@
         <v>182.89</v>
       </c>
       <c r="R152" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S152" s="6">
         <v>4</v>
@@ -19099,7 +19098,7 @@
         <v>31.346065278706597</v>
       </c>
       <c r="Y152" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z152" s="6">
         <v>3</v>
@@ -19121,7 +19120,7 @@
         <v>24.84540767758968</v>
       </c>
       <c r="AF152" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG152" s="6">
         <v>2</v>
@@ -19143,7 +19142,7 @@
         <v>29.307978059998739</v>
       </c>
       <c r="AM152" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN152" s="6">
         <f t="shared" si="14"/>
@@ -19189,25 +19188,25 @@
         <v>147</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E153" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F153" s="5" t="s">
         <v>309</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>312</v>
       </c>
       <c r="G153" s="6">
         <v>0</v>
       </c>
       <c r="H153" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I153" s="6">
         <v>56.62</v>
@@ -19225,7 +19224,7 @@
         <v>154.46</v>
       </c>
       <c r="R153" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S153" s="6">
         <v>3</v>
@@ -19247,7 +19246,7 @@
         <v>17.497238242967224</v>
       </c>
       <c r="Y153" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z153" s="6">
         <v>4</v>
@@ -19269,7 +19268,7 @@
         <v>19.018341735325521</v>
       </c>
       <c r="AF153" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG153" s="6">
         <v>3</v>
@@ -19291,7 +19290,7 @@
         <v>17.426511243916899</v>
       </c>
       <c r="AM153" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN153" s="6">
         <f t="shared" si="14"/>
@@ -19336,19 +19335,19 @@
         <v>148</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>175</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>190</v>
@@ -19384,7 +19383,7 @@
         <v>117</v>
       </c>
       <c r="R154" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S154" s="6">
         <v>3</v>
@@ -19406,7 +19405,7 @@
         <v>29.776384549239658</v>
       </c>
       <c r="Y154" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z154" s="6">
         <v>3</v>
@@ -19428,7 +19427,7 @@
         <v>26.183248783936563</v>
       </c>
       <c r="AM154" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN154" s="6">
         <f t="shared" si="14"/>
@@ -19471,25 +19470,25 @@
         <v>149</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>186</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I155" s="6">
         <v>73.8</v>
@@ -19507,7 +19506,7 @@
         <v>206.94</v>
       </c>
       <c r="R155" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S155" s="6">
         <v>3</v>
@@ -19529,7 +19528,7 @@
         <v>32.55960587187321</v>
       </c>
       <c r="Y155" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z155" s="6">
         <v>2</v>
@@ -19551,7 +19550,7 @@
         <v>29.078659966250893</v>
       </c>
       <c r="AF155" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG155" s="6">
         <v>4</v>
@@ -19573,7 +19572,7 @@
         <v>16.988515775924807</v>
       </c>
       <c r="AM155" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN155" s="6">
         <f t="shared" si="14"/>
@@ -19618,25 +19617,25 @@
         <v>150</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G156" s="6">
         <v>0</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I156" s="6">
         <v>53.5</v>
@@ -19654,7 +19653,7 @@
         <v>149.23000000000002</v>
       </c>
       <c r="R156" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S156" s="6">
         <v>3</v>
@@ -19676,7 +19675,7 @@
         <v>11.672001541776943</v>
       </c>
       <c r="Y156" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z156" s="6">
         <v>3</v>
@@ -19698,7 +19697,7 @@
         <v>19.193672529298322</v>
       </c>
       <c r="AM156" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN156" s="6">
         <f t="shared" si="14"/>
@@ -19743,25 +19742,25 @@
         <v>151</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>174</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G157" s="6">
         <v>0</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I157" s="6">
         <v>48.42</v>
@@ -19779,7 +19778,7 @@
         <v>149.83000000000001</v>
       </c>
       <c r="R157" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S157" s="6">
         <v>2</v>
@@ -19801,7 +19800,7 @@
         <v>19.487137843101916</v>
       </c>
       <c r="Y157" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z157" s="6">
         <v>3</v>
@@ -19823,7 +19822,7 @@
         <v>22.225381177751213</v>
       </c>
       <c r="AM157" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN157" s="6">
         <f t="shared" si="14"/>
@@ -19868,25 +19867,25 @@
         <v>152</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G158" s="6">
         <v>0</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I158" s="6">
         <v>55.32</v>
@@ -19904,7 +19903,7 @@
         <v>147.13999999999999</v>
       </c>
       <c r="R158" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S158" s="6">
         <v>3</v>
@@ -19926,7 +19925,7 @@
         <v>18.859760583466677</v>
       </c>
       <c r="AM158" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN158" s="6">
         <f t="shared" si="14"/>
@@ -19968,25 +19967,25 @@
         <v>153</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>170</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G159" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I159" s="6">
         <v>48.38</v>
@@ -20004,7 +20003,7 @@
         <v>139.88</v>
       </c>
       <c r="R159" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S159" s="6">
         <v>3</v>
@@ -20026,7 +20025,7 @@
         <v>23.974279008494676</v>
       </c>
       <c r="AM159" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN159" s="6">
         <f t="shared" si="14"/>
@@ -20068,19 +20067,19 @@
         <v>154</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G160" s="6" t="s">
         <v>190</v>
@@ -20104,7 +20103,7 @@
         <v>152.47</v>
       </c>
       <c r="R160" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S160" s="6">
         <v>3</v>
@@ -20126,7 +20125,7 @@
         <v>19.537533109376934</v>
       </c>
       <c r="AM160" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN160" s="6">
         <f t="shared" si="14"/>
@@ -20166,25 +20165,25 @@
         <v>155</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>174</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G161" s="6" t="s">
         <v>191</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I161" s="6">
         <v>51.6</v>
@@ -20202,7 +20201,7 @@
         <v>146.16000000000003</v>
       </c>
       <c r="R161" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S161" s="6">
         <v>3</v>
@@ -20224,7 +20223,7 @@
         <v>30.070163865149066</v>
       </c>
       <c r="Y161" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Z161" s="6">
         <v>3</v>
@@ -20246,7 +20245,7 @@
         <v>28.400555908098415</v>
       </c>
       <c r="AM161" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN161" s="6">
         <f t="shared" si="14"/>
@@ -20289,25 +20288,25 @@
         <v>156</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>187</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G162" s="6">
         <v>0</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I162" s="6">
         <v>59.67</v>
@@ -20325,7 +20324,7 @@
         <v>146.68</v>
       </c>
       <c r="R162" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S162" s="6">
         <v>3</v>
@@ -20347,7 +20346,7 @@
         <v>32.798599231679162</v>
       </c>
       <c r="AM162" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN162" s="6">
         <f t="shared" si="14"/>
@@ -20389,25 +20388,25 @@
         <v>157</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E163" s="6" t="s">
         <v>187</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G163" s="6">
         <v>0</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I163" s="6">
         <v>60.2</v>
@@ -20425,7 +20424,7 @@
         <v>156.59</v>
       </c>
       <c r="R163" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S163" s="6">
         <v>3</v>
@@ -20447,7 +20446,7 @@
         <v>25.386722076360456</v>
       </c>
       <c r="AM163" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN163" s="6">
         <f t="shared" si="14"/>
@@ -20489,25 +20488,25 @@
         <v>158</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>187</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G164" s="6">
         <v>0</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I164" s="6">
         <v>67.78</v>
@@ -20525,7 +20524,7 @@
         <v>166.26999999999998</v>
       </c>
       <c r="R164" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S164" s="6">
         <v>3</v>
@@ -20547,7 +20546,7 @@
         <v>32.181284273566874</v>
       </c>
       <c r="AM164" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN164" s="6">
         <f t="shared" si="14"/>
@@ -20587,25 +20586,25 @@
         <v>159</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E165" s="6" t="s">
         <v>187</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G165" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I165" s="6">
         <v>65.08</v>
@@ -20623,7 +20622,7 @@
         <v>172.78</v>
       </c>
       <c r="R165" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S165" s="6">
         <v>4</v>
@@ -20645,7 +20644,7 @@
         <v>27.138514194731744</v>
       </c>
       <c r="AM165" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN165" s="6">
         <f t="shared" si="14"/>
@@ -20687,19 +20686,19 @@
         <v>160</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G166" s="6" t="s">
         <v>191</v>
@@ -20735,7 +20734,7 @@
         <v>124</v>
       </c>
       <c r="R166" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S166" s="6">
         <v>2</v>
@@ -20757,7 +20756,7 @@
         <v>5.4730721290354252</v>
       </c>
       <c r="AM166" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN166" s="6">
         <f t="shared" si="14"/>
@@ -20799,25 +20798,25 @@
         <v>161</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>263</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E167" s="6" t="s">
         <v>172</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G167" s="6">
         <v>0</v>
       </c>
       <c r="H167" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I167" s="6">
         <v>56.4</v>
@@ -20835,7 +20834,7 @@
         <v>126.55000000000001</v>
       </c>
       <c r="R167" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="S167" s="6">
         <v>3</v>
@@ -20857,7 +20856,7 @@
         <v>23.900503615307255</v>
       </c>
       <c r="AM167" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN167" s="6">
         <f t="shared" si="14"/>
@@ -20925,7 +20924,7 @@
         <v>264</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>167</v>
@@ -20972,13 +20971,13 @@
         <v>203</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E2" s="4">
         <v>32.07</v>
@@ -21019,13 +21018,13 @@
         <v>204</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E3" s="4">
         <v>27.96</v>
@@ -21066,13 +21065,13 @@
         <v>205</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E4" s="4">
         <v>41.83</v>
@@ -21113,13 +21112,13 @@
         <v>206</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>261</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E5" s="4">
         <v>38.51</v>
@@ -21160,13 +21159,13 @@
         <v>207</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E6" s="4">
         <v>25.83</v>
@@ -21207,13 +21206,13 @@
         <v>208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E7" s="4">
         <v>30.57</v>
@@ -21254,13 +21253,13 @@
         <v>209</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E8" s="4">
         <v>35.979999999999997</v>
@@ -21301,13 +21300,13 @@
         <v>210</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E9" s="4">
         <v>28.19</v>
@@ -21345,16 +21344,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E10" s="4">
         <v>29.73</v>
@@ -21395,13 +21394,13 @@
         <v>211</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E11" s="4">
         <v>45.06</v>
@@ -21442,13 +21441,13 @@
         <v>212</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E12" s="4">
         <v>28.78</v>
@@ -21489,13 +21488,13 @@
         <v>213</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E13" s="4">
         <v>42.52</v>
@@ -21536,13 +21535,13 @@
         <v>214</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E14" s="4">
         <v>31.19</v>
@@ -21583,13 +21582,13 @@
         <v>215</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E15" s="4">
         <v>54</v>
@@ -21630,13 +21629,13 @@
         <v>216</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E16" s="4">
         <v>53.7</v>
@@ -21677,13 +21676,13 @@
         <v>217</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E17" s="4">
         <v>49.95</v>
@@ -21724,13 +21723,13 @@
         <v>218</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E18" s="4">
         <v>43.95</v>
@@ -21771,13 +21770,13 @@
         <v>219</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E19" s="4">
         <v>51.05</v>
@@ -21806,13 +21805,13 @@
         <v>220</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E20" s="4">
         <v>47.35</v>
@@ -21853,13 +21852,13 @@
         <v>221</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E21" s="4">
         <v>72.52</v>
@@ -21900,13 +21899,13 @@
         <v>222</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E22" s="4">
         <v>40.14</v>
@@ -21947,13 +21946,13 @@
         <v>223</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E23" s="4">
         <v>36.369999999999997</v>
@@ -21994,13 +21993,13 @@
         <v>224</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E24" s="4">
         <v>21.08</v>
@@ -22041,13 +22040,13 @@
         <v>225</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E25" s="4">
         <v>34.61</v>
@@ -22088,13 +22087,13 @@
         <v>226</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E26" s="4">
         <v>35.43</v>
@@ -22135,13 +22134,13 @@
         <v>227</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E27" s="4">
         <v>41.33</v>
@@ -22182,13 +22181,13 @@
         <v>228</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E28" s="4">
         <v>29.5</v>
@@ -22229,13 +22228,13 @@
         <v>229</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E29" s="4">
         <v>26.75</v>
@@ -22276,13 +22275,13 @@
         <v>230</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E30" s="4">
         <v>42.11</v>
@@ -22323,13 +22322,13 @@
         <v>231</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>263</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E31" s="4">
         <v>23.42</v>
@@ -22370,13 +22369,13 @@
         <v>232</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E32" s="4">
         <v>40.450000000000003</v>
@@ -22417,13 +22416,13 @@
         <v>233</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E33" s="4">
         <v>47.84</v>
@@ -22464,13 +22463,13 @@
         <v>234</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E34" s="4">
         <v>23.85</v>
@@ -22511,13 +22510,13 @@
         <v>235</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E35" s="4">
         <v>25.83</v>
@@ -22558,13 +22557,13 @@
         <v>236</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E36" s="4">
         <v>30.06</v>
@@ -22605,13 +22604,13 @@
         <v>237</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E37" s="4">
         <v>45.1</v>
@@ -22652,13 +22651,13 @@
         <v>238</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E38" s="4">
         <v>41.1</v>
@@ -22699,13 +22698,13 @@
         <v>239</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E39" s="4">
         <v>31.55</v>
@@ -22746,13 +22745,13 @@
         <v>240</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E40" s="4">
         <v>33.22</v>
@@ -22793,13 +22792,13 @@
         <v>241</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E41" s="4">
         <v>20.85</v>
@@ -22840,13 +22839,13 @@
         <v>242</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E42" s="4">
         <v>27.6</v>
@@ -22887,13 +22886,13 @@
         <v>243</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E43" s="4">
         <v>35.53</v>
@@ -22934,13 +22933,13 @@
         <v>244</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E44" s="4">
         <v>40.06</v>
@@ -22981,13 +22980,13 @@
         <v>245</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E45" s="4">
         <v>44.75</v>
@@ -23028,13 +23027,13 @@
         <v>246</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E46" s="4">
         <v>28.6</v>
@@ -23075,13 +23074,13 @@
         <v>247</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E47" s="4">
         <v>44.32</v>
@@ -23110,13 +23109,13 @@
         <v>248</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E48" s="4">
         <v>60.27</v>
@@ -23157,13 +23156,13 @@
         <v>249</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E49" s="4">
         <v>42.27</v>
@@ -23204,13 +23203,13 @@
         <v>250</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E50" s="4">
         <v>35.619999999999997</v>
@@ -23251,13 +23250,13 @@
         <v>251</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E51" s="4">
         <v>32.99</v>
@@ -23298,13 +23297,13 @@
         <v>252</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E52" s="4">
         <v>37.159999999999997</v>
@@ -23345,13 +23344,13 @@
         <v>253</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E53" s="4">
         <v>47.13</v>
@@ -23392,13 +23391,13 @@
         <v>254</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E54" s="4">
         <v>27.58</v>
@@ -23439,13 +23438,13 @@
         <v>255</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E55" s="4">
         <v>38.65</v>
@@ -23486,13 +23485,13 @@
         <v>256</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E56" s="4">
         <v>34.880000000000003</v>
@@ -23533,13 +23532,13 @@
         <v>257</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E57" s="4">
         <v>34.770000000000003</v>
@@ -23577,16 +23576,16 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E58" s="4">
         <v>35.67</v>
@@ -23627,13 +23626,13 @@
         <v>258</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E59" s="4">
         <v>30.1</v>

--- a/data/Quina_scraper_surface.xlsx
+++ b/data/Quina_scraper_surface.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Quina_valleys\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD4C91C-4FF5-4710-91BD-85BA7B3AC369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FE25FC-BEC4-4E2A-B6DD-10EEB96ED384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{51F75AC8-9BCC-468F-8814-35286D6AD1E7}"/>
   </bookViews>
@@ -1407,8 +1407,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1524,7 +1525,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1557,6 +1558,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1926,7 +1933,8 @@
     <col min="6" max="6" width="8.88671875" style="7"/>
     <col min="7" max="7" width="8.88671875" style="6"/>
     <col min="8" max="8" width="11.6640625" style="6" customWidth="1"/>
-    <col min="9" max="24" width="8.88671875" style="6"/>
+    <col min="9" max="13" width="8.88671875" style="12"/>
+    <col min="14" max="24" width="8.88671875" style="6"/>
     <col min="25" max="25" width="12" style="6" customWidth="1"/>
     <col min="26" max="38" width="8.88671875" style="6"/>
     <col min="39" max="39" width="14.33203125" style="6" customWidth="1"/>
@@ -1938,7 +1946,7 @@
     <col min="52" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="4" customFormat="1" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" s="4" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>264</v>
       </c>
@@ -1963,19 +1971,19 @@
       <c r="H1" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="11" t="s">
         <v>166</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -2118,19 +2126,19 @@
       <c r="H2" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="12">
         <v>75.88</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="12">
         <v>63.94</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="12">
         <v>37</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="12">
         <v>177.1</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="12">
         <v>205.39</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -2230,19 +2238,19 @@
       <c r="H3" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="12">
         <v>69.06</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="12">
         <v>37.049999999999997</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="12">
         <v>23.2</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="12">
         <v>59.9</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="12">
         <v>165.05</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -2330,19 +2338,19 @@
       <c r="H4" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="12">
         <v>53.66</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="12">
         <v>47.47</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="12">
         <v>22.9</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="12">
         <v>47.8</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="12">
         <v>141.11000000000001</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2418,19 +2426,19 @@
       <c r="H5" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="12">
         <v>49</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="12">
         <v>42.1</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="12">
         <v>20.56</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="12">
         <v>26.8</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="12">
         <v>123.08000000000001</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2540,19 +2548,19 @@
       <c r="H6" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="12">
         <v>69.03</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="12">
         <v>63.1</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="12">
         <v>28.6</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="12">
         <v>101.5</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="12">
         <v>181.26999999999998</v>
       </c>
       <c r="N6" s="6" t="s">
@@ -2652,19 +2660,19 @@
       <c r="H7" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="12">
         <v>66.8</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="12">
         <v>60.3</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="12">
         <v>24.66</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="12">
         <v>87.4</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="12">
         <v>204.61</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -2752,19 +2760,19 @@
       <c r="H8" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="12">
         <v>65.900000000000006</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="12">
         <v>65</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="12">
         <v>33.5</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="12">
         <v>113.4</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="12">
         <v>163.69999999999999</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -2877,19 +2885,19 @@
       <c r="H9" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="12">
         <v>62.3</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="12">
         <v>57.8</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="12">
         <v>25.3</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="12">
         <v>47.2</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="12">
         <v>152.29999999999998</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -2977,19 +2985,19 @@
       <c r="H10" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="12">
         <v>70</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="12">
         <v>38.4</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="12">
         <v>24.9</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="12">
         <v>91.1</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="12">
         <v>152.41999999999999</v>
       </c>
       <c r="N10" s="6" t="s">
@@ -3087,19 +3095,19 @@
       <c r="H11" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="12">
         <v>65.099999999999994</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="12">
         <v>61.8</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="12">
         <v>26.7</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="12">
         <v>98.5</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="12">
         <v>167.65000000000003</v>
       </c>
       <c r="N11" s="6" t="s">
@@ -3224,19 +3232,19 @@
       <c r="H12" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="12">
         <v>65.400000000000006</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="12">
         <v>37.97</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="12">
         <v>28.87</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="12">
         <v>65.2</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="12">
         <v>115.54999999999998</v>
       </c>
       <c r="N12" s="6" t="s">
@@ -3361,19 +3369,19 @@
       <c r="H13" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="12">
         <v>50.94</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="12">
         <v>44.85</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="12">
         <v>34.97</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="12">
         <v>58.9</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="12">
         <v>141.42000000000002</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -3486,19 +3494,19 @@
       <c r="H14" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="12">
         <v>65.400000000000006</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="12">
         <v>45.2</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="12">
         <v>25.8</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="12">
         <v>76.900000000000006</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="12">
         <v>156.89999999999998</v>
       </c>
       <c r="N14" s="6" t="s">
@@ -3598,19 +3606,19 @@
       <c r="H15" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="12">
         <v>55.75</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="12">
         <v>36.85</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="12">
         <v>22.6</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="12">
         <v>48.1</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="12">
         <v>144.73000000000002</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -3698,19 +3706,19 @@
       <c r="H16" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="12">
         <v>60.27</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="12">
         <v>50.35</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="12">
         <v>15.1</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="12">
         <v>70</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="12">
         <v>150.43</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -3818,19 +3826,19 @@
       <c r="H17" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="12">
         <v>60.7</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="12">
         <v>55.18</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="12">
         <v>37.049999999999997</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="12">
         <v>130.19999999999999</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="12">
         <v>174.56</v>
       </c>
       <c r="R17" s="6" t="s">
@@ -3943,19 +3951,19 @@
       <c r="H18" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="12">
         <v>58.54</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="12">
         <v>54.7</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="12">
         <v>18.86</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="12">
         <v>63</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="12">
         <v>143.66000000000003</v>
       </c>
       <c r="N18" s="6" t="s">
@@ -4080,19 +4088,19 @@
       <c r="H19" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="12">
         <v>72.66</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="12">
         <v>69.39</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="12">
         <v>38.15</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="12">
         <v>131.4</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="12">
         <v>192.03999999999996</v>
       </c>
       <c r="R19" s="6" t="s">
@@ -4177,19 +4185,19 @@
       <c r="H20" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="12">
         <v>56.13</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="12">
         <v>40.17</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="12">
         <v>21.4</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="12">
         <v>45.5</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="12">
         <v>147.16</v>
       </c>
       <c r="R20" s="6" t="s">
@@ -4277,19 +4285,19 @@
       <c r="H21" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="12">
         <v>56.49</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="12">
         <v>34.450000000000003</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="12">
         <v>23.1</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="12">
         <v>56.2</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="12">
         <v>160.33000000000001</v>
       </c>
       <c r="R21" s="6" t="s">
@@ -4374,19 +4382,19 @@
       <c r="H22" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="12">
         <v>49.71</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="12">
         <v>37.729999999999997</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="12">
         <v>19.920000000000002</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="12">
         <v>32.4</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="12">
         <v>121.94</v>
       </c>
       <c r="R22" s="6" t="s">
@@ -4474,19 +4482,19 @@
       <c r="H23" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="12">
         <v>70.03</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="12">
         <v>54.7</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="12">
         <v>26.85</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="12">
         <v>94.5</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="12">
         <v>174.66</v>
       </c>
       <c r="R23" s="6" t="s">
@@ -4599,19 +4607,19 @@
       <c r="H24" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="12">
         <v>39.299999999999997</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="12">
         <v>33.9</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="12">
         <v>15.5</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="12">
         <v>15.9</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="12">
         <v>103.33999999999999</v>
       </c>
       <c r="R24" s="6" t="s">
@@ -4696,19 +4704,19 @@
       <c r="H25" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="12">
         <v>103.46</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="12">
         <v>79.75</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="12">
         <v>44.2</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="12">
         <v>357.1</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="12">
         <v>264.04000000000002</v>
       </c>
       <c r="R25" s="6" t="s">
@@ -4818,19 +4826,19 @@
       <c r="H26" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="12">
         <v>61.57</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="12">
         <v>47.32</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="12">
         <v>22.92</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="12">
         <v>70.7</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="12">
         <v>155.12</v>
       </c>
       <c r="N26" s="6" t="s">
@@ -4930,19 +4938,19 @@
       <c r="H27" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="12">
         <v>60.06</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="12">
         <v>57.38</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="12">
         <v>32.700000000000003</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="12">
         <v>93.4</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="12">
         <v>170.32999999999998</v>
       </c>
       <c r="R27" s="6" t="s">
@@ -5030,19 +5038,19 @@
       <c r="H28" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="12">
         <v>72.739999999999995</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="12">
         <v>55.7</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="12">
         <v>28.44</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="12">
         <v>131.19999999999999</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="12">
         <v>189.77</v>
       </c>
       <c r="R28" s="6" t="s">
@@ -5125,19 +5133,19 @@
       <c r="H29" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="12">
         <v>51.5</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="12">
         <v>46</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="12">
         <v>20.9</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="12">
         <v>49.7</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="12">
         <v>149.46999999999997</v>
       </c>
       <c r="N29" s="6" t="s">
@@ -5237,19 +5245,19 @@
       <c r="H30" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="12">
         <v>82.39</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="12">
         <v>81.069999999999993</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="12">
         <v>38.6</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="12">
         <v>250.2</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="12">
         <v>238.71</v>
       </c>
       <c r="R30" s="6" t="s">
@@ -5332,19 +5340,19 @@
       <c r="H31" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="12">
         <v>67.400000000000006</v>
       </c>
-      <c r="J31" s="6">
+      <c r="J31" s="12">
         <v>63.67</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="12">
         <v>27.5</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="12">
         <v>129.69999999999999</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="12">
         <v>189.95000000000002</v>
       </c>
       <c r="N31" s="6" t="s">
@@ -5441,19 +5449,19 @@
       <c r="H32" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="12">
         <v>74.739999999999995</v>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="12">
         <v>54.29</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="12">
         <v>27.1</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="12">
         <v>106.2</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="12">
         <v>199.04</v>
       </c>
       <c r="R32" s="6" t="s">
@@ -5541,19 +5549,19 @@
       <c r="H33" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="12">
         <v>81.459999999999994</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="12">
         <v>59.944000000000003</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="12">
         <v>31.5</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="12">
         <v>142.19999999999999</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="12">
         <v>209.73999999999998</v>
       </c>
       <c r="N33" s="6" t="s">
@@ -5678,19 +5686,19 @@
       <c r="H34" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="12">
         <v>75.099999999999994</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="12">
         <v>72</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="12">
         <v>35.700000000000003</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="12">
         <v>174</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="12">
         <v>207.08</v>
       </c>
       <c r="R34" s="6" t="s">
@@ -5778,19 +5786,19 @@
       <c r="H35" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="12">
         <v>55.1</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="12">
         <v>39</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="12">
         <v>24.58</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="12">
         <v>47.5</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="12">
         <v>137.76</v>
       </c>
       <c r="N35" s="6" t="s">
@@ -5890,19 +5898,19 @@
       <c r="H36" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="12">
         <v>77.900000000000006</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="12">
         <v>67.56</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="12">
         <v>27</v>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="12">
         <v>121.2</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="12">
         <v>215.3</v>
       </c>
       <c r="R36" s="6" t="s">
@@ -5990,19 +5998,19 @@
       <c r="H37" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="12">
         <v>62.98</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="12">
         <v>52.4</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="12">
         <v>24.93</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="12">
         <v>77.400000000000006</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="12">
         <v>166.07999999999998</v>
       </c>
       <c r="N37" s="6" t="s">
@@ -6127,19 +6135,19 @@
       <c r="H38" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="12">
         <v>58.3</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="12">
         <v>38.24</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="12">
         <v>23.76</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="12">
         <v>45.3</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="12">
         <v>138.33000000000001</v>
       </c>
       <c r="N38" s="6" t="s">
@@ -6264,19 +6272,19 @@
       <c r="H39" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="12">
         <v>39.47</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="12">
         <v>29.45</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="12">
         <v>23.72</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="12">
         <v>20.6</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="12">
         <v>93.23</v>
       </c>
       <c r="R39" s="6" t="s">
@@ -6364,19 +6372,19 @@
       <c r="H40" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="12">
         <v>64.2</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="12">
         <v>44.25</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="12">
         <v>24.54</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="12">
         <v>64</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="12">
         <v>157.76000000000002</v>
       </c>
       <c r="R40" s="6" t="s">
@@ -6462,19 +6470,19 @@
       <c r="H41" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="12">
         <v>61.08</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="12">
         <v>35.549999999999997</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="12">
         <v>19.940000000000001</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="12">
         <v>47.4</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="12">
         <v>150.04000000000002</v>
       </c>
       <c r="R41" s="6" t="s">
@@ -6562,19 +6570,19 @@
       <c r="H42" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="12">
         <v>41.72</v>
       </c>
-      <c r="J42" s="6">
+      <c r="J42" s="12">
         <v>24.1</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="12">
         <v>20.79</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="12">
         <v>26.1</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42" s="12">
         <v>100.45</v>
       </c>
       <c r="R42" s="6" t="s">
@@ -6662,19 +6670,19 @@
       <c r="H43" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="12">
         <v>62.1</v>
       </c>
-      <c r="J43" s="6">
+      <c r="J43" s="12">
         <v>48.5</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="12">
         <v>23.2</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="12">
         <v>74.900000000000006</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="12">
         <v>169.09000000000003</v>
       </c>
       <c r="N43" s="6" t="s">
@@ -6772,19 +6780,19 @@
       <c r="H44" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="12">
         <v>77.650000000000006</v>
       </c>
-      <c r="J44" s="6">
+      <c r="J44" s="12">
         <v>49.85</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="12">
         <v>32.86</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="12">
         <v>128.30000000000001</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="12">
         <v>212.27</v>
       </c>
       <c r="R44" s="6" t="s">
@@ -6897,19 +6905,19 @@
       <c r="H45" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="12">
         <v>71.25</v>
       </c>
-      <c r="J45" s="6">
+      <c r="J45" s="12">
         <v>52.3</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="12">
         <v>35.799999999999997</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="12">
         <v>114.1</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45" s="12">
         <v>186.97</v>
       </c>
       <c r="N45" s="6" t="s">
@@ -7009,19 +7017,19 @@
       <c r="H46" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="12">
         <v>75.61</v>
       </c>
-      <c r="J46" s="6">
+      <c r="J46" s="12">
         <v>69.12</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="12">
         <v>34.5</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="12">
         <v>225.6</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="12">
         <v>200.41</v>
       </c>
       <c r="R46" s="6" t="s">
@@ -7104,19 +7112,19 @@
       <c r="H47" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="12">
         <v>36.14</v>
       </c>
-      <c r="J47" s="6">
+      <c r="J47" s="12">
         <v>28.94</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="12">
         <v>18.3</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="12">
         <v>15.2</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="12">
         <v>86.210000000000008</v>
       </c>
       <c r="R47" s="6" t="s">
@@ -7201,19 +7209,19 @@
       <c r="H48" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="12">
         <v>78.25</v>
       </c>
-      <c r="J48" s="6">
+      <c r="J48" s="12">
         <v>57.8</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="12">
         <v>31</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="12">
         <v>136.80000000000001</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="12">
         <v>199.03</v>
       </c>
       <c r="R48" s="6" t="s">
@@ -7296,19 +7304,19 @@
       <c r="H49" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="12">
         <v>61.43</v>
       </c>
-      <c r="J49" s="6">
+      <c r="J49" s="12">
         <v>58.87</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="12">
         <v>15.4</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49" s="12">
         <v>71.2</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="12">
         <v>163.62</v>
       </c>
       <c r="N49" s="6" t="s">
@@ -7408,19 +7416,19 @@
       <c r="H50" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="12">
         <v>86.7</v>
       </c>
-      <c r="J50" s="6">
+      <c r="J50" s="12">
         <v>57.17</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="12">
         <v>27.23</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="12">
         <v>135.5</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="12">
         <v>229.22999999999996</v>
       </c>
       <c r="N50" s="6" t="s">
@@ -7543,19 +7551,19 @@
       <c r="H51" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I51" s="6">
+      <c r="I51" s="12">
         <v>59.82</v>
       </c>
-      <c r="J51" s="6">
+      <c r="J51" s="12">
         <v>42.8</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="12">
         <v>22.32</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="12">
         <v>52.5</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="12">
         <v>156.19</v>
       </c>
       <c r="R51" s="6" t="s">
@@ -7666,19 +7674,19 @@
       <c r="H52" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I52" s="6">
+      <c r="I52" s="12">
         <v>69.94</v>
       </c>
-      <c r="J52" s="6">
+      <c r="J52" s="12">
         <v>46.332999999999998</v>
       </c>
-      <c r="K52" s="6">
+      <c r="K52" s="12">
         <v>24.7</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52" s="12">
         <v>69.2</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="12">
         <v>181.24000000000004</v>
       </c>
       <c r="R52" s="6" t="s">
@@ -7791,19 +7799,19 @@
       <c r="H53" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I53" s="6">
+      <c r="I53" s="12">
         <v>71.28</v>
       </c>
-      <c r="J53" s="6">
+      <c r="J53" s="12">
         <v>68.739999999999995</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="12">
         <v>27.03</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53" s="12">
         <v>140.6</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="12">
         <v>195.87</v>
       </c>
       <c r="N53" s="6" t="s">
@@ -7928,19 +7936,19 @@
       <c r="H54" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I54" s="6">
+      <c r="I54" s="12">
         <v>56.6</v>
       </c>
-      <c r="J54" s="6">
+      <c r="J54" s="12">
         <v>52.19</v>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="12">
         <v>20.100000000000001</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="12">
         <v>58.4</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="12">
         <v>169.29</v>
       </c>
       <c r="N54" s="6" t="s">
@@ -8065,19 +8073,19 @@
       <c r="H55" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I55" s="12">
         <v>72.53</v>
       </c>
-      <c r="J55" s="6">
+      <c r="J55" s="12">
         <v>61.59</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="12">
         <v>19.75</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55" s="12">
         <v>112.8</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="12">
         <v>181.98000000000002</v>
       </c>
       <c r="N55" s="6" t="s">
@@ -8177,19 +8185,19 @@
       <c r="H56" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I56" s="6">
+      <c r="I56" s="12">
         <v>52.67</v>
       </c>
-      <c r="J56" s="6">
+      <c r="J56" s="12">
         <v>43</v>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="12">
         <v>31.3</v>
       </c>
-      <c r="L56" s="6">
+      <c r="L56" s="12">
         <v>84.4</v>
       </c>
-      <c r="M56" s="6">
+      <c r="M56" s="12">
         <v>166.92</v>
       </c>
       <c r="R56" s="6" t="s">
@@ -8297,19 +8305,19 @@
       <c r="H57" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I57" s="6">
+      <c r="I57" s="12">
         <v>62.78</v>
       </c>
-      <c r="J57" s="6">
+      <c r="J57" s="12">
         <v>42.38</v>
       </c>
-      <c r="K57" s="6">
+      <c r="K57" s="12">
         <v>36.06</v>
       </c>
-      <c r="L57" s="6">
+      <c r="L57" s="12">
         <v>100.3</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="12">
         <v>163.21</v>
       </c>
       <c r="R57" s="6" t="s">
@@ -8394,19 +8402,19 @@
       <c r="H58" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I58" s="6">
+      <c r="I58" s="12">
         <v>54.51</v>
       </c>
-      <c r="J58" s="6">
+      <c r="J58" s="12">
         <v>42.8</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="12">
         <v>26.63</v>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="12">
         <v>62.3</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="12">
         <v>141.30000000000001</v>
       </c>
       <c r="R58" s="6" t="s">
@@ -8494,19 +8502,19 @@
       <c r="H59" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I59" s="6">
+      <c r="I59" s="12">
         <v>60.11</v>
       </c>
-      <c r="J59" s="6">
+      <c r="J59" s="12">
         <v>59.19</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="12">
         <v>25.2</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="12">
         <v>112.2</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="12">
         <v>175.31</v>
       </c>
       <c r="R59" s="6" t="s">
@@ -8614,19 +8622,19 @@
       <c r="H60" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I60" s="6">
+      <c r="I60" s="12">
         <v>64.3</v>
       </c>
-      <c r="J60" s="6">
+      <c r="J60" s="12">
         <v>56.45</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="12">
         <v>23.88</v>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="12">
         <v>84.8</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="12">
         <v>171.08</v>
       </c>
       <c r="R60" s="6" t="s">
@@ -8734,19 +8742,19 @@
       <c r="H61" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I61" s="6">
+      <c r="I61" s="12">
         <v>58.76</v>
       </c>
-      <c r="J61" s="6">
+      <c r="J61" s="12">
         <v>39.47</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="12">
         <v>13.5</v>
       </c>
-      <c r="L61" s="6">
+      <c r="L61" s="12">
         <v>42.9</v>
       </c>
-      <c r="M61" s="6">
+      <c r="M61" s="12">
         <v>157.04000000000002</v>
       </c>
       <c r="N61" s="6" t="s">
@@ -8866,19 +8874,19 @@
       <c r="H62" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I62" s="6">
+      <c r="I62" s="12">
         <v>65.599999999999994</v>
       </c>
-      <c r="J62" s="6">
+      <c r="J62" s="12">
         <v>46.2</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="12">
         <v>15.9</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="12">
         <v>55.7</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="12">
         <v>167.96</v>
       </c>
       <c r="R62" s="6" t="s">
@@ -8963,19 +8971,19 @@
       <c r="H63" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I63" s="6">
+      <c r="I63" s="12">
         <v>76.319999999999993</v>
       </c>
-      <c r="J63" s="6">
+      <c r="J63" s="12">
         <v>51.55</v>
       </c>
-      <c r="K63" s="6">
+      <c r="K63" s="12">
         <v>17.48</v>
       </c>
-      <c r="L63" s="6">
+      <c r="L63" s="12">
         <v>75.900000000000006</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="12">
         <v>192.92000000000002</v>
       </c>
       <c r="N63" s="6" t="s">
@@ -9075,19 +9083,19 @@
       <c r="H64" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I64" s="6">
+      <c r="I64" s="12">
         <v>56.76</v>
       </c>
-      <c r="J64" s="6">
+      <c r="J64" s="12">
         <v>52.67</v>
       </c>
-      <c r="K64" s="6">
+      <c r="K64" s="12">
         <v>24.16</v>
       </c>
-      <c r="L64" s="6">
+      <c r="L64" s="12">
         <v>66.099999999999994</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M64" s="12">
         <v>127.50999999999999</v>
       </c>
       <c r="N64" s="6" t="s">
@@ -9212,19 +9220,19 @@
       <c r="H65" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I65" s="6">
+      <c r="I65" s="12">
         <v>52.37</v>
       </c>
-      <c r="J65" s="6">
+      <c r="J65" s="12">
         <v>45.2</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="12">
         <v>21</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="12">
         <v>40</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="12">
         <v>148.87</v>
       </c>
       <c r="R65" s="6" t="s">
@@ -9312,19 +9320,19 @@
       <c r="H66" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I66" s="12">
         <v>49.6</v>
       </c>
-      <c r="J66" s="6">
+      <c r="J66" s="12">
         <v>49.3</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="12">
         <v>22.9</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="12">
         <v>37</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="12">
         <v>136.22</v>
       </c>
       <c r="R66" s="6" t="s">
@@ -9437,19 +9445,19 @@
       <c r="H67" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I67" s="6">
+      <c r="I67" s="12">
         <v>67.510000000000005</v>
       </c>
-      <c r="J67" s="6">
+      <c r="J67" s="12">
         <v>55.5</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="12">
         <v>31.5</v>
       </c>
-      <c r="L67" s="6">
+      <c r="L67" s="12">
         <v>117.7</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="12">
         <v>141.29</v>
       </c>
       <c r="R67" s="6" t="s">
@@ -9537,19 +9545,19 @@
       <c r="H68" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I68" s="6">
+      <c r="I68" s="12">
         <v>48.52</v>
       </c>
-      <c r="J68" s="6">
+      <c r="J68" s="12">
         <v>31.96</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="12">
         <v>26.1</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="12">
         <v>56.6</v>
       </c>
-      <c r="M68" s="6">
+      <c r="M68" s="12">
         <v>134.85</v>
       </c>
       <c r="R68" s="6" t="s">
@@ -9654,19 +9662,19 @@
       <c r="H69" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I69" s="6">
+      <c r="I69" s="12">
         <v>75</v>
       </c>
-      <c r="J69" s="6">
+      <c r="J69" s="12">
         <v>52</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="12">
         <v>16.25</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="12">
         <v>77.900000000000006</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="12">
         <v>196.26</v>
       </c>
       <c r="R69" s="6" t="s">
@@ -9749,19 +9757,19 @@
       <c r="H70" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I70" s="6">
+      <c r="I70" s="12">
         <v>50.79</v>
       </c>
-      <c r="J70" s="6">
+      <c r="J70" s="12">
         <v>47.48</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="12">
         <v>20.5</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="12">
         <v>63.4</v>
       </c>
-      <c r="M70" s="6">
+      <c r="M70" s="12">
         <v>140.35</v>
       </c>
       <c r="R70" s="6" t="s">
@@ -9869,19 +9877,19 @@
       <c r="H71" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I71" s="6">
+      <c r="I71" s="12">
         <v>72.53</v>
       </c>
-      <c r="J71" s="6">
+      <c r="J71" s="12">
         <v>64.7</v>
       </c>
-      <c r="K71" s="6">
+      <c r="K71" s="12">
         <v>20</v>
       </c>
-      <c r="L71" s="6">
+      <c r="L71" s="12">
         <v>110.8</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="12">
         <v>210.89</v>
       </c>
       <c r="R71" s="6" t="s">
@@ -9967,19 +9975,19 @@
       <c r="H72" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I72" s="6">
+      <c r="I72" s="12">
         <v>54.35</v>
       </c>
-      <c r="J72" s="6">
+      <c r="J72" s="12">
         <v>51.02</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="12">
         <v>24.7</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="12">
         <v>64</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="12">
         <v>144.37</v>
       </c>
       <c r="R72" s="6" t="s">
@@ -10087,19 +10095,19 @@
       <c r="H73" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I73" s="6">
+      <c r="I73" s="12">
         <v>44.2</v>
       </c>
-      <c r="J73" s="6">
+      <c r="J73" s="12">
         <v>41.34</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="12">
         <v>22.33</v>
       </c>
-      <c r="L73" s="6">
+      <c r="L73" s="12">
         <v>42.7</v>
       </c>
-      <c r="M73" s="6">
+      <c r="M73" s="12">
         <v>119.71</v>
       </c>
       <c r="R73" s="6" t="s">
@@ -10187,19 +10195,19 @@
       <c r="H74" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I74" s="6">
+      <c r="I74" s="12">
         <v>49.59</v>
       </c>
-      <c r="J74" s="6">
+      <c r="J74" s="12">
         <v>38.06</v>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="12">
         <v>19.98</v>
       </c>
-      <c r="L74" s="6">
+      <c r="L74" s="12">
         <v>42.6</v>
       </c>
-      <c r="M74" s="6">
+      <c r="M74" s="12">
         <v>133.32</v>
       </c>
       <c r="R74" s="6" t="s">
@@ -10312,19 +10320,19 @@
       <c r="H75" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I75" s="6">
+      <c r="I75" s="12">
         <v>50.83</v>
       </c>
-      <c r="J75" s="6">
+      <c r="J75" s="12">
         <v>43.21</v>
       </c>
-      <c r="K75" s="6">
+      <c r="K75" s="12">
         <v>12.6</v>
       </c>
-      <c r="L75" s="6">
+      <c r="L75" s="12">
         <v>27.9</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="12">
         <v>139.01000000000002</v>
       </c>
       <c r="R75" s="6" t="s">
@@ -10410,19 +10418,19 @@
       <c r="H76" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I76" s="6">
+      <c r="I76" s="12">
         <v>48.7</v>
       </c>
-      <c r="J76" s="6">
+      <c r="J76" s="12">
         <v>39.35</v>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="12">
         <v>16.93</v>
       </c>
-      <c r="L76" s="6">
+      <c r="L76" s="12">
         <v>30.8</v>
       </c>
-      <c r="M76" s="6">
+      <c r="M76" s="12">
         <v>117.26</v>
       </c>
       <c r="N76" s="6" t="s">
@@ -10522,19 +10530,19 @@
       <c r="H77" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I77" s="6">
+      <c r="I77" s="12">
         <v>57.27</v>
       </c>
-      <c r="J77" s="6">
+      <c r="J77" s="12">
         <v>50.38</v>
       </c>
-      <c r="K77" s="6">
+      <c r="K77" s="12">
         <v>26.16</v>
       </c>
-      <c r="L77" s="6">
+      <c r="L77" s="12">
         <v>83.3</v>
       </c>
-      <c r="M77" s="6">
+      <c r="M77" s="12">
         <v>161.12</v>
       </c>
       <c r="N77" s="6" t="s">
@@ -10654,19 +10662,19 @@
       <c r="H78" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I78" s="6">
+      <c r="I78" s="12">
         <v>47.5</v>
       </c>
-      <c r="J78" s="6">
+      <c r="J78" s="12">
         <v>44</v>
       </c>
-      <c r="K78" s="6">
+      <c r="K78" s="12">
         <v>11</v>
       </c>
-      <c r="L78" s="6">
+      <c r="L78" s="12">
         <v>22.8</v>
       </c>
-      <c r="M78" s="6">
+      <c r="M78" s="12">
         <v>135.1</v>
       </c>
       <c r="N78" s="6" t="s">
@@ -10788,19 +10796,19 @@
       <c r="H79" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I79" s="6">
+      <c r="I79" s="12">
         <v>65.400000000000006</v>
       </c>
-      <c r="J79" s="6">
+      <c r="J79" s="12">
         <v>32.700000000000003</v>
       </c>
-      <c r="K79" s="6">
+      <c r="K79" s="12">
         <v>19.399999999999999</v>
       </c>
-      <c r="L79" s="6">
+      <c r="L79" s="12">
         <v>51.4</v>
       </c>
-      <c r="M79" s="6">
+      <c r="M79" s="12">
         <v>147.79000000000002</v>
       </c>
       <c r="R79" s="6" t="s">
@@ -10885,19 +10893,19 @@
       <c r="H80" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I80" s="6">
+      <c r="I80" s="12">
         <v>41.66</v>
       </c>
-      <c r="J80" s="6">
+      <c r="J80" s="12">
         <v>41.2</v>
       </c>
-      <c r="K80" s="6">
+      <c r="K80" s="12">
         <v>13.1</v>
       </c>
-      <c r="L80" s="6">
+      <c r="L80" s="12">
         <v>29</v>
       </c>
-      <c r="M80" s="6">
+      <c r="M80" s="12">
         <v>123.41999999999999</v>
       </c>
       <c r="R80" s="6" t="s">
@@ -10980,19 +10988,19 @@
       <c r="H81" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I81" s="6">
+      <c r="I81" s="12">
         <v>57.47</v>
       </c>
-      <c r="J81" s="6">
+      <c r="J81" s="12">
         <v>50.6</v>
       </c>
-      <c r="K81" s="6">
+      <c r="K81" s="12">
         <v>19.78</v>
       </c>
-      <c r="L81" s="6">
+      <c r="L81" s="12">
         <v>57.5</v>
       </c>
-      <c r="M81" s="6">
+      <c r="M81" s="12">
         <v>153.11000000000001</v>
       </c>
       <c r="N81" s="6" t="s">
@@ -11092,19 +11100,19 @@
       <c r="H82" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I82" s="6">
+      <c r="I82" s="12">
         <v>44.6</v>
       </c>
-      <c r="J82" s="6">
+      <c r="J82" s="12">
         <v>35.28</v>
       </c>
-      <c r="K82" s="6">
+      <c r="K82" s="12">
         <v>19.399999999999999</v>
       </c>
-      <c r="L82" s="6">
+      <c r="L82" s="12">
         <v>32.4</v>
       </c>
-      <c r="M82" s="6">
+      <c r="M82" s="12">
         <v>118.35</v>
       </c>
       <c r="R82" s="6" t="s">
@@ -11215,19 +11223,19 @@
       <c r="H83" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I83" s="6">
+      <c r="I83" s="12">
         <v>38.9</v>
       </c>
-      <c r="J83" s="6">
+      <c r="J83" s="12">
         <v>27</v>
       </c>
-      <c r="K83" s="6">
+      <c r="K83" s="12">
         <v>16.12</v>
       </c>
-      <c r="L83" s="6">
+      <c r="L83" s="12">
         <v>17.2</v>
       </c>
-      <c r="M83" s="6">
+      <c r="M83" s="12">
         <v>101.85999999999999</v>
       </c>
       <c r="R83" s="6" t="s">
@@ -11338,19 +11346,19 @@
       <c r="H84" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I84" s="6">
+      <c r="I84" s="12">
         <v>102.28</v>
       </c>
-      <c r="J84" s="6">
+      <c r="J84" s="12">
         <v>74.099999999999994</v>
       </c>
-      <c r="K84" s="6">
+      <c r="K84" s="12">
         <v>36.799999999999997</v>
       </c>
-      <c r="L84" s="6">
+      <c r="L84" s="12">
         <v>244.9</v>
       </c>
-      <c r="M84" s="6">
+      <c r="M84" s="12">
         <v>288.97999999999996</v>
       </c>
       <c r="R84" s="6" t="s">
@@ -11438,19 +11446,19 @@
       <c r="H85" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I85" s="6">
+      <c r="I85" s="12">
         <v>68.150000000000006</v>
       </c>
-      <c r="J85" s="6">
+      <c r="J85" s="12">
         <v>57.35</v>
       </c>
-      <c r="K85" s="6">
+      <c r="K85" s="12">
         <v>24.9</v>
       </c>
-      <c r="L85" s="6">
+      <c r="L85" s="12">
         <v>89.7</v>
       </c>
-      <c r="M85" s="6">
+      <c r="M85" s="12">
         <v>183.54</v>
       </c>
       <c r="R85" s="6" t="s">
@@ -11535,19 +11543,19 @@
       <c r="H86" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I86" s="6">
+      <c r="I86" s="12">
         <v>52.66</v>
       </c>
-      <c r="J86" s="6">
+      <c r="J86" s="12">
         <v>48.2</v>
       </c>
-      <c r="K86" s="6">
+      <c r="K86" s="12">
         <v>29.64</v>
       </c>
-      <c r="L86" s="6">
+      <c r="L86" s="12">
         <v>58.8</v>
       </c>
-      <c r="M86" s="6">
+      <c r="M86" s="12">
         <v>141.04000000000002</v>
       </c>
       <c r="R86" s="6" t="s">
@@ -11635,19 +11643,19 @@
       <c r="H87" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I87" s="6">
+      <c r="I87" s="12">
         <v>49.48</v>
       </c>
-      <c r="J87" s="6">
+      <c r="J87" s="12">
         <v>32.35</v>
       </c>
-      <c r="K87" s="6">
+      <c r="K87" s="12">
         <v>12.66</v>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="12">
         <v>24.5</v>
       </c>
-      <c r="M87" s="6">
+      <c r="M87" s="12">
         <v>125.63</v>
       </c>
       <c r="R87" s="6" t="s">
@@ -11758,19 +11766,19 @@
       <c r="H88" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I88" s="6">
+      <c r="I88" s="12">
         <v>53.9</v>
       </c>
-      <c r="J88" s="6">
+      <c r="J88" s="12">
         <v>33.1</v>
       </c>
-      <c r="K88" s="6">
+      <c r="K88" s="12">
         <v>27.38</v>
       </c>
-      <c r="L88" s="6">
+      <c r="L88" s="12">
         <v>35.9</v>
       </c>
-      <c r="M88" s="6">
+      <c r="M88" s="12">
         <v>144.91</v>
       </c>
       <c r="N88" s="6" t="s">
@@ -11868,19 +11876,19 @@
       <c r="H89" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I89" s="6">
+      <c r="I89" s="12">
         <v>46.9</v>
       </c>
-      <c r="J89" s="6">
+      <c r="J89" s="12">
         <v>34.090000000000003</v>
       </c>
-      <c r="K89" s="6">
+      <c r="K89" s="12">
         <v>16.899999999999999</v>
       </c>
-      <c r="L89" s="6">
+      <c r="L89" s="12">
         <v>31.6</v>
       </c>
-      <c r="M89" s="6">
+      <c r="M89" s="12">
         <v>134.49</v>
       </c>
       <c r="R89" s="6" t="s">
@@ -11966,19 +11974,19 @@
       <c r="H90" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I90" s="6">
+      <c r="I90" s="12">
         <v>43.97</v>
       </c>
-      <c r="J90" s="6">
+      <c r="J90" s="12">
         <v>27.06</v>
       </c>
-      <c r="K90" s="6">
+      <c r="K90" s="12">
         <v>14.65</v>
       </c>
-      <c r="L90" s="6">
+      <c r="L90" s="12">
         <v>13.8</v>
       </c>
-      <c r="M90" s="6">
+      <c r="M90" s="12">
         <v>109.05999999999999</v>
       </c>
       <c r="R90" s="6" t="s">
@@ -12066,19 +12074,19 @@
       <c r="H91" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I91" s="6">
+      <c r="I91" s="12">
         <v>38.4</v>
       </c>
-      <c r="J91" s="6">
+      <c r="J91" s="12">
         <v>33.24</v>
       </c>
-      <c r="K91" s="6">
+      <c r="K91" s="12">
         <v>18.37</v>
       </c>
-      <c r="L91" s="6">
+      <c r="L91" s="12">
         <v>19.899999999999999</v>
       </c>
-      <c r="M91" s="6">
+      <c r="M91" s="12">
         <v>100.21</v>
       </c>
       <c r="N91" s="6" t="s">
@@ -12178,19 +12186,19 @@
       <c r="H92" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I92" s="6">
+      <c r="I92" s="12">
         <v>44.8</v>
       </c>
-      <c r="J92" s="6">
+      <c r="J92" s="12">
         <v>23.5</v>
       </c>
-      <c r="K92" s="6">
+      <c r="K92" s="12">
         <v>17.260000000000002</v>
       </c>
-      <c r="L92" s="6">
+      <c r="L92" s="12">
         <v>19.600000000000001</v>
       </c>
-      <c r="M92" s="6">
+      <c r="M92" s="12">
         <v>102.42000000000002</v>
       </c>
       <c r="R92" s="6" t="s">
@@ -12278,19 +12286,19 @@
       <c r="H93" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I93" s="6">
+      <c r="I93" s="12">
         <v>45.35</v>
       </c>
-      <c r="J93" s="6">
+      <c r="J93" s="12">
         <v>34.67</v>
       </c>
-      <c r="K93" s="6">
+      <c r="K93" s="12">
         <v>16.59</v>
       </c>
-      <c r="L93" s="6">
+      <c r="L93" s="12">
         <v>24.6</v>
       </c>
-      <c r="M93" s="6">
+      <c r="M93" s="12">
         <v>126.56</v>
       </c>
       <c r="R93" s="6" t="s">
@@ -12373,19 +12381,19 @@
       <c r="H94" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I94" s="6">
+      <c r="I94" s="12">
         <v>44.37</v>
       </c>
-      <c r="J94" s="6">
+      <c r="J94" s="12">
         <v>40.89</v>
       </c>
-      <c r="K94" s="6">
+      <c r="K94" s="12">
         <v>14.04</v>
       </c>
-      <c r="L94" s="6">
+      <c r="L94" s="12">
         <v>24.8</v>
       </c>
-      <c r="M94" s="6">
+      <c r="M94" s="12">
         <v>112.82</v>
       </c>
       <c r="R94" s="6" t="s">
@@ -12468,19 +12476,19 @@
       <c r="H95" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I95" s="6">
+      <c r="I95" s="12">
         <v>93.95</v>
       </c>
-      <c r="J95" s="6">
+      <c r="J95" s="12">
         <v>70.55</v>
       </c>
-      <c r="K95" s="6">
+      <c r="K95" s="12">
         <v>51.12</v>
       </c>
-      <c r="L95" s="6">
+      <c r="L95" s="12">
         <v>505.6</v>
       </c>
-      <c r="M95" s="6">
+      <c r="M95" s="12">
         <v>262.13</v>
       </c>
       <c r="R95" s="6" t="s">
@@ -12565,19 +12573,19 @@
       <c r="H96" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I96" s="6">
+      <c r="I96" s="12">
         <v>39.6</v>
       </c>
-      <c r="J96" s="6">
+      <c r="J96" s="12">
         <v>30.26</v>
       </c>
-      <c r="K96" s="6">
+      <c r="K96" s="12">
         <v>20</v>
       </c>
-      <c r="L96" s="6">
+      <c r="L96" s="12">
         <v>20</v>
       </c>
-      <c r="M96" s="6">
+      <c r="M96" s="12">
         <v>111.59</v>
       </c>
       <c r="R96" s="6" t="s">
@@ -12665,19 +12673,19 @@
       <c r="H97" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I97" s="12">
         <v>54.67</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J97" s="12">
         <v>39.75</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K97" s="12">
         <v>29.98</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L97" s="12">
         <v>45.5</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M97" s="12">
         <v>153.86999999999998</v>
       </c>
       <c r="N97" s="6" t="s">
@@ -12777,19 +12785,19 @@
       <c r="H98" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I98" s="6">
+      <c r="I98" s="12">
         <v>55.1</v>
       </c>
-      <c r="J98" s="6">
+      <c r="J98" s="12">
         <v>44.63</v>
       </c>
-      <c r="K98" s="6">
+      <c r="K98" s="12">
         <v>23.97</v>
       </c>
-      <c r="L98" s="6">
+      <c r="L98" s="12">
         <v>62.6</v>
       </c>
-      <c r="M98" s="6">
+      <c r="M98" s="12">
         <v>156.32</v>
       </c>
       <c r="R98" s="6" t="s">
@@ -12897,19 +12905,19 @@
       <c r="H99" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I99" s="6">
+      <c r="I99" s="12">
         <v>45.95</v>
       </c>
-      <c r="J99" s="6">
+      <c r="J99" s="12">
         <v>44.61</v>
       </c>
-      <c r="K99" s="6">
+      <c r="K99" s="12">
         <v>20.58</v>
       </c>
-      <c r="L99" s="6">
+      <c r="L99" s="12">
         <v>36.299999999999997</v>
       </c>
-      <c r="M99" s="6">
+      <c r="M99" s="12">
         <v>143.1</v>
       </c>
       <c r="N99" s="6" t="s">
@@ -13034,19 +13042,19 @@
       <c r="H100" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I100" s="6">
+      <c r="I100" s="12">
         <v>63.84</v>
       </c>
-      <c r="J100" s="6">
+      <c r="J100" s="12">
         <v>50</v>
       </c>
-      <c r="K100" s="6">
+      <c r="K100" s="12">
         <v>13.7</v>
       </c>
-      <c r="L100" s="6">
+      <c r="L100" s="12">
         <v>51</v>
       </c>
-      <c r="M100" s="6">
+      <c r="M100" s="12">
         <v>179.26000000000005</v>
       </c>
       <c r="R100" s="6" t="s">
@@ -13132,19 +13140,19 @@
       <c r="H101" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I101" s="6">
+      <c r="I101" s="12">
         <v>58.95</v>
       </c>
-      <c r="J101" s="6">
+      <c r="J101" s="12">
         <v>48.3</v>
       </c>
-      <c r="K101" s="6">
+      <c r="K101" s="12">
         <v>17.47</v>
       </c>
-      <c r="L101" s="6">
+      <c r="L101" s="12">
         <v>77.599999999999994</v>
       </c>
-      <c r="M101" s="6">
+      <c r="M101" s="12">
         <v>159.19</v>
       </c>
       <c r="R101" s="6" t="s">
@@ -13227,19 +13235,19 @@
       <c r="H102" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I102" s="6">
+      <c r="I102" s="12">
         <v>83.05</v>
       </c>
-      <c r="J102" s="6">
+      <c r="J102" s="12">
         <v>62.56</v>
       </c>
-      <c r="K102" s="6">
+      <c r="K102" s="12">
         <v>42.9</v>
       </c>
-      <c r="L102" s="6">
+      <c r="L102" s="12">
         <v>232</v>
       </c>
-      <c r="M102" s="6">
+      <c r="M102" s="12">
         <v>200.05</v>
       </c>
       <c r="R102" s="6" t="s">
@@ -13327,19 +13335,19 @@
       <c r="H103" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I103" s="6">
+      <c r="I103" s="12">
         <v>97.37</v>
       </c>
-      <c r="J103" s="6">
+      <c r="J103" s="12">
         <v>57.42</v>
       </c>
-      <c r="K103" s="6">
+      <c r="K103" s="12">
         <v>27.42</v>
       </c>
-      <c r="L103" s="6">
+      <c r="L103" s="12">
         <v>158.19999999999999</v>
       </c>
-      <c r="M103" s="6">
+      <c r="M103" s="12">
         <v>205.82999999999998</v>
       </c>
       <c r="R103" s="6" t="s">
@@ -13425,19 +13433,19 @@
       <c r="H104" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I104" s="6">
+      <c r="I104" s="12">
         <v>75.599999999999994</v>
       </c>
-      <c r="J104" s="6">
+      <c r="J104" s="12">
         <v>66.930000000000007</v>
       </c>
-      <c r="K104" s="6">
+      <c r="K104" s="12">
         <v>42.4</v>
       </c>
-      <c r="L104" s="6">
+      <c r="L104" s="12">
         <v>192</v>
       </c>
-      <c r="M104" s="6">
+      <c r="M104" s="12">
         <v>213.57999999999998</v>
       </c>
       <c r="R104" s="6" t="s">
@@ -13547,19 +13555,19 @@
       <c r="H105" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I105" s="6">
+      <c r="I105" s="12">
         <v>65.52</v>
       </c>
-      <c r="J105" s="6">
+      <c r="J105" s="12">
         <v>43.68</v>
       </c>
-      <c r="K105" s="6">
+      <c r="K105" s="12">
         <v>18.25</v>
       </c>
-      <c r="L105" s="6">
+      <c r="L105" s="12">
         <v>58.6</v>
       </c>
-      <c r="M105" s="6">
+      <c r="M105" s="12">
         <v>154.88</v>
       </c>
       <c r="N105" s="6" t="s">
@@ -13659,19 +13667,19 @@
       <c r="H106" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I106" s="6">
+      <c r="I106" s="12">
         <v>62.14</v>
       </c>
-      <c r="J106" s="6">
+      <c r="J106" s="12">
         <v>56.77</v>
       </c>
-      <c r="K106" s="6">
+      <c r="K106" s="12">
         <v>24</v>
       </c>
-      <c r="L106" s="6">
+      <c r="L106" s="12">
         <v>78.8</v>
       </c>
-      <c r="M106" s="6">
+      <c r="M106" s="12">
         <v>179.59</v>
       </c>
       <c r="R106" s="6" t="s">
@@ -13781,19 +13789,19 @@
       <c r="H107" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I107" s="6">
+      <c r="I107" s="12">
         <v>55.2</v>
       </c>
-      <c r="J107" s="6">
+      <c r="J107" s="12">
         <v>46.34</v>
       </c>
-      <c r="K107" s="6">
+      <c r="K107" s="12">
         <v>19.5</v>
       </c>
-      <c r="L107" s="6">
+      <c r="L107" s="12">
         <v>72.3</v>
       </c>
-      <c r="M107" s="6">
+      <c r="M107" s="12">
         <v>147.94999999999999</v>
       </c>
       <c r="R107" s="6" t="s">
@@ -13901,19 +13909,19 @@
       <c r="H108" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I108" s="6">
+      <c r="I108" s="12">
         <v>47.89</v>
       </c>
-      <c r="J108" s="6">
+      <c r="J108" s="12">
         <v>38.770000000000003</v>
       </c>
-      <c r="K108" s="6">
+      <c r="K108" s="12">
         <v>19.8</v>
       </c>
-      <c r="L108" s="6">
+      <c r="L108" s="12">
         <v>42.4</v>
       </c>
-      <c r="M108" s="6">
+      <c r="M108" s="12">
         <v>134.72</v>
       </c>
       <c r="N108" s="6" t="s">
@@ -14013,19 +14021,19 @@
       <c r="H109" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="I109" s="6">
+      <c r="I109" s="12">
         <v>48.61</v>
       </c>
-      <c r="J109" s="6">
+      <c r="J109" s="12">
         <v>38.82</v>
       </c>
-      <c r="K109" s="6">
+      <c r="K109" s="12">
         <v>19.88</v>
       </c>
-      <c r="L109" s="6">
+      <c r="L109" s="12">
         <v>41.7</v>
       </c>
-      <c r="M109" s="6">
+      <c r="M109" s="12">
         <v>141.75</v>
       </c>
       <c r="N109" s="6" t="s">
@@ -14125,19 +14133,19 @@
       <c r="H110" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I110" s="6">
+      <c r="I110" s="12">
         <v>52.2</v>
       </c>
-      <c r="J110" s="6">
+      <c r="J110" s="12">
         <v>51.37</v>
       </c>
-      <c r="K110" s="6">
+      <c r="K110" s="12">
         <v>17.53</v>
       </c>
-      <c r="L110" s="6">
+      <c r="L110" s="12">
         <v>51.4</v>
       </c>
-      <c r="M110" s="6">
+      <c r="M110" s="12">
         <v>164.24</v>
       </c>
       <c r="R110" s="6" t="s">
@@ -14245,19 +14253,19 @@
       <c r="H111" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I111" s="6">
+      <c r="I111" s="12">
         <v>53.45</v>
       </c>
-      <c r="J111" s="6">
+      <c r="J111" s="12">
         <v>39.85</v>
       </c>
-      <c r="K111" s="6">
+      <c r="K111" s="12">
         <v>17.399999999999999</v>
       </c>
-      <c r="L111" s="6">
+      <c r="L111" s="12">
         <v>45.9</v>
       </c>
-      <c r="M111" s="6">
+      <c r="M111" s="12">
         <v>147.34</v>
       </c>
       <c r="R111" s="6" t="s">
@@ -14340,19 +14348,19 @@
       <c r="H112" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I112" s="6">
+      <c r="I112" s="12">
         <v>50.3</v>
       </c>
-      <c r="J112" s="6">
+      <c r="J112" s="12">
         <v>44.66</v>
       </c>
-      <c r="K112" s="6">
+      <c r="K112" s="12">
         <v>24.6</v>
       </c>
-      <c r="L112" s="6">
+      <c r="L112" s="12">
         <v>35.200000000000003</v>
       </c>
-      <c r="M112" s="6">
+      <c r="M112" s="12">
         <v>134.24</v>
       </c>
       <c r="R112" s="6" t="s">
@@ -14435,19 +14443,19 @@
       <c r="H113" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I113" s="6">
+      <c r="I113" s="12">
         <v>47.12</v>
       </c>
-      <c r="J113" s="6">
+      <c r="J113" s="12">
         <v>45.25</v>
       </c>
-      <c r="K113" s="6">
+      <c r="K113" s="12">
         <v>15.66</v>
       </c>
-      <c r="L113" s="6">
+      <c r="L113" s="12">
         <v>29</v>
       </c>
-      <c r="M113" s="6">
+      <c r="M113" s="12">
         <v>134.88999999999999</v>
       </c>
       <c r="R113" s="6" t="s">
@@ -14535,19 +14543,19 @@
       <c r="H114" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I114" s="6">
+      <c r="I114" s="12">
         <v>34.5</v>
       </c>
-      <c r="J114" s="6">
+      <c r="J114" s="12">
         <v>27.43</v>
       </c>
-      <c r="K114" s="6">
+      <c r="K114" s="12">
         <v>11.5</v>
       </c>
-      <c r="L114" s="6">
+      <c r="L114" s="12">
         <v>11.1</v>
       </c>
-      <c r="M114" s="6">
+      <c r="M114" s="12">
         <v>91.73</v>
       </c>
       <c r="R114" s="6" t="s">
@@ -14658,19 +14666,19 @@
       <c r="H115" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I115" s="6">
+      <c r="I115" s="12">
         <v>37.1</v>
       </c>
-      <c r="J115" s="6">
+      <c r="J115" s="12">
         <v>21.78</v>
       </c>
-      <c r="K115" s="6">
+      <c r="K115" s="12">
         <v>15.3</v>
       </c>
-      <c r="L115" s="6">
+      <c r="L115" s="12">
         <v>14.4</v>
       </c>
-      <c r="M115" s="6">
+      <c r="M115" s="12">
         <v>97.609999999999985</v>
       </c>
       <c r="R115" s="6" t="s">
@@ -14758,19 +14766,19 @@
       <c r="H116" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I116" s="6">
+      <c r="I116" s="12">
         <v>39.9</v>
       </c>
-      <c r="J116" s="6">
+      <c r="J116" s="12">
         <v>25.87</v>
       </c>
-      <c r="K116" s="6">
+      <c r="K116" s="12">
         <v>17.100000000000001</v>
       </c>
-      <c r="L116" s="6">
+      <c r="L116" s="12">
         <v>19.3</v>
       </c>
-      <c r="M116" s="6">
+      <c r="M116" s="12">
         <v>93.46</v>
       </c>
       <c r="R116" s="6" t="s">
@@ -14856,19 +14864,19 @@
       <c r="H117" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I117" s="6">
+      <c r="I117" s="12">
         <v>65.900000000000006</v>
       </c>
-      <c r="J117" s="6">
+      <c r="J117" s="12">
         <v>48.3</v>
       </c>
-      <c r="K117" s="6">
+      <c r="K117" s="12">
         <v>20</v>
       </c>
-      <c r="L117" s="6">
+      <c r="L117" s="12">
         <v>63</v>
       </c>
-      <c r="M117" s="6">
+      <c r="M117" s="12">
         <v>183.87</v>
       </c>
       <c r="N117" s="6" t="s">
@@ -14991,19 +14999,19 @@
       <c r="H118" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I118" s="6">
+      <c r="I118" s="12">
         <v>65.95</v>
       </c>
-      <c r="J118" s="6">
+      <c r="J118" s="12">
         <v>58.4</v>
       </c>
-      <c r="K118" s="6">
+      <c r="K118" s="12">
         <v>20.76</v>
       </c>
-      <c r="L118" s="6">
+      <c r="L118" s="12">
         <v>80</v>
       </c>
-      <c r="M118" s="6">
+      <c r="M118" s="12">
         <v>175.46</v>
       </c>
       <c r="N118" s="6" t="s">
@@ -15103,19 +15111,19 @@
       <c r="H119" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I119" s="6">
+      <c r="I119" s="12">
         <v>57.65</v>
       </c>
-      <c r="J119" s="6">
+      <c r="J119" s="12">
         <v>37.72</v>
       </c>
-      <c r="K119" s="6">
+      <c r="K119" s="12">
         <v>23.63</v>
       </c>
-      <c r="L119" s="6">
+      <c r="L119" s="12">
         <v>67.900000000000006</v>
       </c>
-      <c r="M119" s="6">
+      <c r="M119" s="12">
         <v>169.14999999999998</v>
       </c>
       <c r="N119" s="6" t="s">
@@ -15215,19 +15223,19 @@
       <c r="H120" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I120" s="6">
+      <c r="I120" s="12">
         <v>59.7</v>
       </c>
-      <c r="J120" s="6">
+      <c r="J120" s="12">
         <v>53.43</v>
       </c>
-      <c r="K120" s="6">
+      <c r="K120" s="12">
         <v>18.7</v>
       </c>
-      <c r="L120" s="6">
+      <c r="L120" s="12">
         <v>62.1</v>
       </c>
-      <c r="M120" s="6">
+      <c r="M120" s="12">
         <v>177.74</v>
       </c>
       <c r="N120" s="6" t="s">
@@ -15352,19 +15360,19 @@
       <c r="H121" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I121" s="6">
+      <c r="I121" s="12">
         <v>70.510000000000005</v>
       </c>
-      <c r="J121" s="6">
+      <c r="J121" s="12">
         <v>65.7</v>
       </c>
-      <c r="K121" s="6">
+      <c r="K121" s="12">
         <v>28.4</v>
       </c>
-      <c r="L121" s="6">
+      <c r="L121" s="12">
         <v>113.2</v>
       </c>
-      <c r="M121" s="6">
+      <c r="M121" s="12">
         <v>202.67</v>
       </c>
       <c r="N121" s="6" t="s">
@@ -15464,19 +15472,19 @@
       <c r="H122" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I122" s="6">
+      <c r="I122" s="12">
         <v>63.98</v>
       </c>
-      <c r="J122" s="6">
+      <c r="J122" s="12">
         <v>51.3</v>
       </c>
-      <c r="K122" s="6">
+      <c r="K122" s="12">
         <v>37.26</v>
       </c>
-      <c r="L122" s="6">
+      <c r="L122" s="12">
         <v>165.4</v>
       </c>
-      <c r="M122" s="6">
+      <c r="M122" s="12">
         <v>191.82</v>
       </c>
       <c r="R122" s="6" t="s">
@@ -15561,19 +15569,19 @@
       <c r="H123" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I123" s="6">
+      <c r="I123" s="12">
         <v>54.1</v>
       </c>
-      <c r="J123" s="6">
+      <c r="J123" s="12">
         <v>44.3</v>
       </c>
-      <c r="K123" s="6">
+      <c r="K123" s="12">
         <v>28.6</v>
       </c>
-      <c r="L123" s="6">
+      <c r="L123" s="12">
         <v>70</v>
       </c>
-      <c r="M123" s="6">
+      <c r="M123" s="12">
         <v>154.54</v>
       </c>
       <c r="N123" s="6" t="s">
@@ -15670,19 +15678,19 @@
       <c r="H124" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I124" s="6">
+      <c r="I124" s="12">
         <v>53.3</v>
       </c>
-      <c r="J124" s="6">
+      <c r="J124" s="12">
         <v>52.5</v>
       </c>
-      <c r="K124" s="6">
+      <c r="K124" s="12">
         <v>25.3</v>
       </c>
-      <c r="L124" s="6">
+      <c r="L124" s="12">
         <v>89.8</v>
       </c>
-      <c r="M124" s="6">
+      <c r="M124" s="12">
         <v>158.82</v>
       </c>
       <c r="R124" s="6" t="s">
@@ -15768,19 +15776,19 @@
       <c r="H125" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I125" s="6">
+      <c r="I125" s="12">
         <v>37</v>
       </c>
-      <c r="J125" s="6">
+      <c r="J125" s="12">
         <v>23.2</v>
       </c>
-      <c r="K125" s="6">
+      <c r="K125" s="12">
         <v>21.21</v>
       </c>
-      <c r="L125" s="6">
+      <c r="L125" s="12">
         <v>23.7</v>
       </c>
-      <c r="M125" s="6">
+      <c r="M125" s="12">
         <v>98.789999999999992</v>
       </c>
       <c r="R125" s="6" t="s">
@@ -15868,19 +15876,19 @@
       <c r="H126" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I126" s="6">
+      <c r="I126" s="12">
         <v>71.099999999999994</v>
       </c>
-      <c r="J126" s="6">
+      <c r="J126" s="12">
         <v>58.2</v>
       </c>
-      <c r="K126" s="6">
+      <c r="K126" s="12">
         <v>32.200000000000003</v>
       </c>
-      <c r="L126" s="6">
+      <c r="L126" s="12">
         <v>137</v>
       </c>
-      <c r="M126" s="6">
+      <c r="M126" s="12">
         <v>180.51999999999998</v>
       </c>
       <c r="R126" s="6" t="s">
@@ -15968,19 +15976,19 @@
       <c r="H127" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I127" s="6">
+      <c r="I127" s="12">
         <v>51.56</v>
       </c>
-      <c r="J127" s="6">
+      <c r="J127" s="12">
         <v>39.93</v>
       </c>
-      <c r="K127" s="6">
+      <c r="K127" s="12">
         <v>20.6</v>
       </c>
-      <c r="L127" s="6">
+      <c r="L127" s="12">
         <v>51.4</v>
       </c>
-      <c r="M127" s="6">
+      <c r="M127" s="12">
         <v>161.92999999999998</v>
       </c>
       <c r="R127" s="6" t="s">
@@ -16118,19 +16126,19 @@
       <c r="H128" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I128" s="6">
+      <c r="I128" s="12">
         <v>54.86</v>
       </c>
-      <c r="J128" s="6">
+      <c r="J128" s="12">
         <v>45.94</v>
       </c>
-      <c r="K128" s="6">
+      <c r="K128" s="12">
         <v>29.79</v>
       </c>
-      <c r="L128" s="6">
+      <c r="L128" s="12">
         <v>93.3</v>
       </c>
-      <c r="M128" s="6">
+      <c r="M128" s="12">
         <v>177.07</v>
       </c>
       <c r="N128" s="6" t="s">
@@ -16278,19 +16286,19 @@
       <c r="H129" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I129" s="6">
+      <c r="I129" s="12">
         <v>48.5</v>
       </c>
-      <c r="J129" s="6">
+      <c r="J129" s="12">
         <v>42.82</v>
       </c>
-      <c r="K129" s="6">
+      <c r="K129" s="12">
         <v>21.87</v>
       </c>
-      <c r="L129" s="6">
+      <c r="L129" s="12">
         <v>43.5</v>
       </c>
-      <c r="M129" s="6">
+      <c r="M129" s="12">
         <v>135.01</v>
       </c>
       <c r="N129" s="6" t="s">
@@ -16437,19 +16445,19 @@
       <c r="H130" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I130" s="6">
+      <c r="I130" s="12">
         <v>72.31</v>
       </c>
-      <c r="J130" s="6">
+      <c r="J130" s="12">
         <v>71.89</v>
       </c>
-      <c r="K130" s="6">
+      <c r="K130" s="12">
         <v>24.3</v>
       </c>
-      <c r="L130" s="6">
+      <c r="L130" s="12">
         <v>150</v>
       </c>
-      <c r="M130" s="6">
+      <c r="M130" s="12">
         <v>220.98000000000002</v>
       </c>
       <c r="R130" s="6" t="s">
@@ -16587,19 +16595,19 @@
       <c r="H131" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I131" s="6">
+      <c r="I131" s="12">
         <v>76.510000000000005</v>
       </c>
-      <c r="J131" s="6">
+      <c r="J131" s="12">
         <v>54.85</v>
       </c>
-      <c r="K131" s="6">
+      <c r="K131" s="12">
         <v>27.66</v>
       </c>
-      <c r="L131" s="6">
+      <c r="L131" s="12">
         <v>150.9</v>
       </c>
-      <c r="M131" s="6">
+      <c r="M131" s="12">
         <v>213.77</v>
       </c>
       <c r="R131" s="6" t="s">
@@ -16710,19 +16718,19 @@
       <c r="H132" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I132" s="6">
+      <c r="I132" s="12">
         <v>43.76</v>
       </c>
-      <c r="J132" s="6">
+      <c r="J132" s="12">
         <v>30.24</v>
       </c>
-      <c r="K132" s="6">
+      <c r="K132" s="12">
         <v>23.5</v>
       </c>
-      <c r="L132" s="6">
+      <c r="L132" s="12">
         <v>24.1</v>
       </c>
-      <c r="M132" s="6">
+      <c r="M132" s="12">
         <v>100.07</v>
       </c>
       <c r="R132" s="6" t="s">
@@ -16858,19 +16866,19 @@
       <c r="H133" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I133" s="6">
+      <c r="I133" s="12">
         <v>80.53</v>
       </c>
-      <c r="J133" s="6">
+      <c r="J133" s="12">
         <v>66.02</v>
       </c>
-      <c r="K133" s="6">
+      <c r="K133" s="12">
         <v>36.5</v>
       </c>
-      <c r="L133" s="6">
+      <c r="L133" s="12">
         <v>239.2</v>
       </c>
-      <c r="M133" s="6">
+      <c r="M133" s="12">
         <v>231.53999999999996</v>
       </c>
       <c r="N133" s="6" t="s">
@@ -16995,19 +17003,19 @@
       <c r="H134" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I134" s="6">
+      <c r="I134" s="12">
         <v>60.43</v>
       </c>
-      <c r="J134" s="6">
+      <c r="J134" s="12">
         <v>59.05</v>
       </c>
-      <c r="K134" s="6">
+      <c r="K134" s="12">
         <v>31.87</v>
       </c>
-      <c r="L134" s="6">
+      <c r="L134" s="12">
         <v>129.4</v>
       </c>
-      <c r="M134" s="6">
+      <c r="M134" s="12">
         <v>155.94</v>
       </c>
       <c r="N134" s="6" t="s">
@@ -17130,19 +17138,19 @@
       <c r="H135" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I135" s="6">
+      <c r="I135" s="12">
         <v>60.09</v>
       </c>
-      <c r="J135" s="6">
+      <c r="J135" s="12">
         <v>49.5</v>
       </c>
-      <c r="K135" s="6">
+      <c r="K135" s="12">
         <v>26.76</v>
       </c>
-      <c r="L135" s="6">
+      <c r="L135" s="12">
         <v>88.2</v>
       </c>
-      <c r="M135" s="6">
+      <c r="M135" s="12">
         <v>148.70999999999998</v>
       </c>
       <c r="N135" s="6" t="s">
@@ -17292,19 +17300,19 @@
       <c r="H136" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I136" s="6">
+      <c r="I136" s="12">
         <v>54.76</v>
       </c>
-      <c r="J136" s="6">
+      <c r="J136" s="12">
         <v>48.76</v>
       </c>
-      <c r="K136" s="6">
+      <c r="K136" s="12">
         <v>26.7</v>
       </c>
-      <c r="L136" s="6">
+      <c r="L136" s="12">
         <v>95</v>
       </c>
-      <c r="M136" s="6">
+      <c r="M136" s="12">
         <v>146.15</v>
       </c>
       <c r="R136" s="6" t="s">
@@ -17414,19 +17422,19 @@
       <c r="H137" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I137" s="6">
+      <c r="I137" s="12">
         <v>64.13</v>
       </c>
-      <c r="J137" s="6">
+      <c r="J137" s="12">
         <v>38.130000000000003</v>
       </c>
-      <c r="K137" s="6">
+      <c r="K137" s="12">
         <v>30.01</v>
       </c>
-      <c r="L137" s="6">
+      <c r="L137" s="12">
         <v>93.4</v>
       </c>
-      <c r="M137" s="6">
+      <c r="M137" s="12">
         <v>160.4</v>
       </c>
       <c r="R137" s="6" t="s">
@@ -17564,19 +17572,19 @@
       <c r="H138" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I138" s="6">
+      <c r="I138" s="12">
         <v>74.3</v>
       </c>
-      <c r="J138" s="6">
+      <c r="J138" s="12">
         <v>47.32</v>
       </c>
-      <c r="K138" s="6">
+      <c r="K138" s="12">
         <v>31.21</v>
       </c>
-      <c r="L138" s="6">
+      <c r="L138" s="12">
         <v>114</v>
       </c>
-      <c r="M138" s="6">
+      <c r="M138" s="12">
         <v>176.94</v>
       </c>
       <c r="R138" s="6" t="s">
@@ -17661,19 +17669,19 @@
       <c r="H139" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I139" s="6">
+      <c r="I139" s="12">
         <v>69.62</v>
       </c>
-      <c r="J139" s="6">
+      <c r="J139" s="12">
         <v>57.11</v>
       </c>
-      <c r="K139" s="6">
+      <c r="K139" s="12">
         <v>31.94</v>
       </c>
-      <c r="L139" s="6">
+      <c r="L139" s="12">
         <v>136.5</v>
       </c>
-      <c r="M139" s="6">
+      <c r="M139" s="12">
         <v>201.3</v>
       </c>
       <c r="N139" s="6" t="s">
@@ -17771,19 +17779,19 @@
       <c r="H140" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I140" s="6">
+      <c r="I140" s="12">
         <v>42.3</v>
       </c>
-      <c r="J140" s="6">
+      <c r="J140" s="12">
         <v>38.68</v>
       </c>
-      <c r="K140" s="6">
+      <c r="K140" s="12">
         <v>23.08</v>
       </c>
-      <c r="L140" s="6">
+      <c r="L140" s="12">
         <v>54.9</v>
       </c>
-      <c r="M140" s="6">
+      <c r="M140" s="12">
         <v>123.83</v>
       </c>
       <c r="R140" s="6" t="s">
@@ -17869,19 +17877,19 @@
       <c r="H141" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I141" s="6">
+      <c r="I141" s="12">
         <v>50.1</v>
       </c>
-      <c r="J141" s="6">
+      <c r="J141" s="12">
         <v>49.3</v>
       </c>
-      <c r="K141" s="6">
+      <c r="K141" s="12">
         <v>31.8</v>
       </c>
-      <c r="L141" s="6">
+      <c r="L141" s="12">
         <v>89.4</v>
       </c>
-      <c r="M141" s="6">
+      <c r="M141" s="12">
         <v>124.75</v>
       </c>
       <c r="R141" s="6" t="s">
@@ -17992,19 +18000,19 @@
       <c r="H142" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I142" s="6">
+      <c r="I142" s="12">
         <v>61.22</v>
       </c>
-      <c r="J142" s="6">
+      <c r="J142" s="12">
         <v>43.26</v>
       </c>
-      <c r="K142" s="6">
+      <c r="K142" s="12">
         <v>24.97</v>
       </c>
-      <c r="L142" s="6">
+      <c r="L142" s="12">
         <v>65.8</v>
       </c>
-      <c r="M142" s="6">
+      <c r="M142" s="12">
         <v>172</v>
       </c>
       <c r="R142" s="6" t="s">
@@ -18090,19 +18098,19 @@
       <c r="H143" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I143" s="6">
+      <c r="I143" s="12">
         <v>53.77</v>
       </c>
-      <c r="J143" s="6">
+      <c r="J143" s="12">
         <v>52.1</v>
       </c>
-      <c r="K143" s="6">
+      <c r="K143" s="12">
         <v>27.3</v>
       </c>
-      <c r="L143" s="6">
+      <c r="L143" s="12">
         <v>69.2</v>
       </c>
-      <c r="M143" s="6">
+      <c r="M143" s="12">
         <v>166.45</v>
       </c>
       <c r="R143" s="6" t="s">
@@ -18190,19 +18198,19 @@
       <c r="H144" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I144" s="6">
+      <c r="I144" s="12">
         <v>40.29</v>
       </c>
-      <c r="J144" s="6">
+      <c r="J144" s="12">
         <v>36.68</v>
       </c>
-      <c r="K144" s="6">
+      <c r="K144" s="12">
         <v>26.7</v>
       </c>
-      <c r="L144" s="6">
+      <c r="L144" s="12">
         <v>44</v>
       </c>
-      <c r="M144" s="6">
+      <c r="M144" s="12">
         <v>130.08999999999997</v>
       </c>
       <c r="N144" s="6" t="s">
@@ -18302,19 +18310,19 @@
       <c r="H145" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I145" s="6">
+      <c r="I145" s="12">
         <v>48.42</v>
       </c>
-      <c r="J145" s="6">
+      <c r="J145" s="12">
         <v>34.119999999999997</v>
       </c>
-      <c r="K145" s="6">
+      <c r="K145" s="12">
         <v>23.63</v>
       </c>
-      <c r="L145" s="6">
+      <c r="L145" s="12">
         <v>54.8</v>
       </c>
-      <c r="M145" s="6">
+      <c r="M145" s="12">
         <v>127.92</v>
       </c>
       <c r="R145" s="6" t="s">
@@ -18450,19 +18458,19 @@
       <c r="H146" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I146" s="6">
+      <c r="I146" s="12">
         <v>52.8</v>
       </c>
-      <c r="J146" s="6">
+      <c r="J146" s="12">
         <v>45.26</v>
       </c>
-      <c r="K146" s="6">
+      <c r="K146" s="12">
         <v>24.06</v>
       </c>
-      <c r="L146" s="6">
+      <c r="L146" s="12">
         <v>58.7</v>
       </c>
-      <c r="M146" s="6">
+      <c r="M146" s="12">
         <v>162.23000000000002</v>
       </c>
       <c r="N146" s="6" t="s">
@@ -18562,19 +18570,19 @@
       <c r="H147" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I147" s="6">
+      <c r="I147" s="12">
         <v>38.47</v>
       </c>
-      <c r="J147" s="6">
+      <c r="J147" s="12">
         <v>34.9</v>
       </c>
-      <c r="K147" s="6">
+      <c r="K147" s="12">
         <v>19.02</v>
       </c>
-      <c r="L147" s="6">
+      <c r="L147" s="12">
         <v>23.5</v>
       </c>
-      <c r="M147" s="6">
+      <c r="M147" s="12">
         <v>117.15</v>
       </c>
       <c r="N147" s="6" t="s">
@@ -18672,19 +18680,19 @@
       <c r="H148" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I148" s="6">
+      <c r="I148" s="12">
         <v>27.9</v>
       </c>
-      <c r="J148" s="6">
+      <c r="J148" s="12">
         <v>22.26</v>
       </c>
-      <c r="K148" s="6">
+      <c r="K148" s="12">
         <v>18.940000000000001</v>
       </c>
-      <c r="L148" s="6">
+      <c r="L148" s="12">
         <v>12.7</v>
       </c>
-      <c r="M148" s="6">
+      <c r="M148" s="12">
         <v>84.15</v>
       </c>
       <c r="R148" s="6" t="s">
@@ -18770,19 +18778,19 @@
       <c r="H149" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I149" s="6">
+      <c r="I149" s="12">
         <v>43.73</v>
       </c>
-      <c r="J149" s="6">
+      <c r="J149" s="12">
         <v>28.6</v>
       </c>
-      <c r="K149" s="6">
+      <c r="K149" s="12">
         <v>14.8</v>
       </c>
-      <c r="L149" s="6">
+      <c r="L149" s="12">
         <v>21</v>
       </c>
-      <c r="M149" s="6">
+      <c r="M149" s="12">
         <v>113.3</v>
       </c>
       <c r="R149" s="6" t="s">
@@ -18868,19 +18876,19 @@
       <c r="H150" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I150" s="6">
+      <c r="I150" s="12">
         <v>86.27</v>
       </c>
-      <c r="J150" s="6">
+      <c r="J150" s="12">
         <v>51.39</v>
       </c>
-      <c r="K150" s="6">
+      <c r="K150" s="12">
         <v>47.3</v>
       </c>
-      <c r="L150" s="6">
+      <c r="L150" s="12">
         <v>163.69999999999999</v>
       </c>
-      <c r="M150" s="6">
+      <c r="M150" s="12">
         <v>222.47000000000003</v>
       </c>
       <c r="R150" s="6" t="s">
@@ -18963,19 +18971,19 @@
       <c r="H151" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I151" s="6">
+      <c r="I151" s="12">
         <v>69.83</v>
       </c>
-      <c r="J151" s="6">
+      <c r="J151" s="12">
         <v>44.19</v>
       </c>
-      <c r="K151" s="6">
+      <c r="K151" s="12">
         <v>33.15</v>
       </c>
-      <c r="L151" s="6">
+      <c r="L151" s="12">
         <v>92.1</v>
       </c>
-      <c r="M151" s="6">
+      <c r="M151" s="12">
         <v>167.64</v>
       </c>
       <c r="R151" s="6" t="s">
@@ -19060,19 +19068,19 @@
       <c r="H152" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I152" s="6">
+      <c r="I152" s="12">
         <v>56.24</v>
       </c>
-      <c r="J152" s="6">
+      <c r="J152" s="12">
         <v>54.02</v>
       </c>
-      <c r="K152" s="6">
+      <c r="K152" s="12">
         <v>30.46</v>
       </c>
-      <c r="L152" s="6">
+      <c r="L152" s="12">
         <v>119</v>
       </c>
-      <c r="M152" s="6">
+      <c r="M152" s="12">
         <v>182.89</v>
       </c>
       <c r="R152" s="6" t="s">
@@ -19208,19 +19216,19 @@
       <c r="H153" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I153" s="6">
+      <c r="I153" s="12">
         <v>56.62</v>
       </c>
-      <c r="J153" s="6">
+      <c r="J153" s="12">
         <v>41.51</v>
       </c>
-      <c r="K153" s="6">
+      <c r="K153" s="12">
         <v>22.88</v>
       </c>
-      <c r="L153" s="6">
+      <c r="L153" s="12">
         <v>81.5</v>
       </c>
-      <c r="M153" s="6">
+      <c r="M153" s="12">
         <v>154.46</v>
       </c>
       <c r="R153" s="6" t="s">
@@ -19355,19 +19363,19 @@
       <c r="H154" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I154" s="6">
+      <c r="I154" s="12">
         <v>59.07</v>
       </c>
-      <c r="J154" s="6">
+      <c r="J154" s="12">
         <v>54.35</v>
       </c>
-      <c r="K154" s="6">
+      <c r="K154" s="12">
         <v>31.34</v>
       </c>
-      <c r="L154" s="6">
+      <c r="L154" s="12">
         <v>121.9</v>
       </c>
-      <c r="M154" s="6">
+      <c r="M154" s="12">
         <v>181</v>
       </c>
       <c r="N154" s="6" t="s">
@@ -19490,19 +19498,19 @@
       <c r="H155" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="I155" s="6">
+      <c r="I155" s="12">
         <v>73.8</v>
       </c>
-      <c r="J155" s="6">
+      <c r="J155" s="12">
         <v>55.5</v>
       </c>
-      <c r="K155" s="6">
+      <c r="K155" s="12">
         <v>35.61</v>
       </c>
-      <c r="L155" s="6">
+      <c r="L155" s="12">
         <v>162.80000000000001</v>
       </c>
-      <c r="M155" s="6">
+      <c r="M155" s="12">
         <v>206.94</v>
       </c>
       <c r="R155" s="6" t="s">
@@ -19637,19 +19645,19 @@
       <c r="H156" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I156" s="6">
+      <c r="I156" s="12">
         <v>53.5</v>
       </c>
-      <c r="J156" s="6">
+      <c r="J156" s="12">
         <v>41.45</v>
       </c>
-      <c r="K156" s="6">
+      <c r="K156" s="12">
         <v>24.54</v>
       </c>
-      <c r="L156" s="6">
+      <c r="L156" s="12">
         <v>54.3</v>
       </c>
-      <c r="M156" s="6">
+      <c r="M156" s="12">
         <v>149.23000000000002</v>
       </c>
       <c r="R156" s="6" t="s">
@@ -19762,19 +19770,19 @@
       <c r="H157" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I157" s="6">
+      <c r="I157" s="12">
         <v>48.42</v>
       </c>
-      <c r="J157" s="6">
+      <c r="J157" s="12">
         <v>48.34</v>
       </c>
-      <c r="K157" s="6">
+      <c r="K157" s="12">
         <v>32.78</v>
       </c>
-      <c r="L157" s="6">
+      <c r="L157" s="12">
         <v>83.8</v>
       </c>
-      <c r="M157" s="6">
+      <c r="M157" s="12">
         <v>149.83000000000001</v>
       </c>
       <c r="R157" s="6" t="s">
@@ -19887,19 +19895,19 @@
       <c r="H158" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I158" s="6">
+      <c r="I158" s="12">
         <v>55.32</v>
       </c>
-      <c r="J158" s="6">
+      <c r="J158" s="12">
         <v>31.38</v>
       </c>
-      <c r="K158" s="6">
+      <c r="K158" s="12">
         <v>27.46</v>
       </c>
-      <c r="L158" s="6">
+      <c r="L158" s="12">
         <v>53.9</v>
       </c>
-      <c r="M158" s="6">
+      <c r="M158" s="12">
         <v>147.13999999999999</v>
       </c>
       <c r="R158" s="6" t="s">
@@ -19987,19 +19995,19 @@
       <c r="H159" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I159" s="6">
+      <c r="I159" s="12">
         <v>48.38</v>
       </c>
-      <c r="J159" s="6">
+      <c r="J159" s="12">
         <v>45.1</v>
       </c>
-      <c r="K159" s="6">
+      <c r="K159" s="12">
         <v>31.27</v>
       </c>
-      <c r="L159" s="6">
+      <c r="L159" s="12">
         <v>72.400000000000006</v>
       </c>
-      <c r="M159" s="6">
+      <c r="M159" s="12">
         <v>139.88</v>
       </c>
       <c r="R159" s="6" t="s">
@@ -20087,19 +20095,19 @@
       <c r="H160" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I160" s="6">
+      <c r="I160" s="12">
         <v>53.4</v>
       </c>
-      <c r="J160" s="6">
+      <c r="J160" s="12">
         <v>44.6</v>
       </c>
-      <c r="K160" s="6">
+      <c r="K160" s="12">
         <v>18.899999999999999</v>
       </c>
-      <c r="L160" s="6">
+      <c r="L160" s="12">
         <v>41.2</v>
       </c>
-      <c r="M160" s="6">
+      <c r="M160" s="12">
         <v>152.47</v>
       </c>
       <c r="R160" s="6" t="s">
@@ -20185,19 +20193,19 @@
       <c r="H161" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I161" s="6">
+      <c r="I161" s="12">
         <v>51.6</v>
       </c>
-      <c r="J161" s="6">
+      <c r="J161" s="12">
         <v>41.41</v>
       </c>
-      <c r="K161" s="6">
+      <c r="K161" s="12">
         <v>30.98</v>
       </c>
-      <c r="L161" s="6">
+      <c r="L161" s="12">
         <v>68.5</v>
       </c>
-      <c r="M161" s="6">
+      <c r="M161" s="12">
         <v>146.16000000000003</v>
       </c>
       <c r="R161" s="6" t="s">
@@ -20308,19 +20316,19 @@
       <c r="H162" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I162" s="6">
+      <c r="I162" s="12">
         <v>59.67</v>
       </c>
-      <c r="J162" s="6">
+      <c r="J162" s="12">
         <v>39.6</v>
       </c>
-      <c r="K162" s="6">
+      <c r="K162" s="12">
         <v>38.1</v>
       </c>
-      <c r="L162" s="6">
+      <c r="L162" s="12">
         <v>96.7</v>
       </c>
-      <c r="M162" s="6">
+      <c r="M162" s="12">
         <v>146.68</v>
       </c>
       <c r="R162" s="6" t="s">
@@ -20408,19 +20416,19 @@
       <c r="H163" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I163" s="6">
+      <c r="I163" s="12">
         <v>60.2</v>
       </c>
-      <c r="J163" s="6">
+      <c r="J163" s="12">
         <v>35.549999999999997</v>
       </c>
-      <c r="K163" s="6">
+      <c r="K163" s="12">
         <v>28.06</v>
       </c>
-      <c r="L163" s="6">
+      <c r="L163" s="12">
         <v>61.5</v>
       </c>
-      <c r="M163" s="6">
+      <c r="M163" s="12">
         <v>156.59</v>
       </c>
       <c r="R163" s="6" t="s">
@@ -20508,19 +20516,19 @@
       <c r="H164" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I164" s="6">
+      <c r="I164" s="12">
         <v>67.78</v>
       </c>
-      <c r="J164" s="6">
+      <c r="J164" s="12">
         <v>35.17</v>
       </c>
-      <c r="K164" s="6">
+      <c r="K164" s="12">
         <v>30.33</v>
       </c>
-      <c r="L164" s="6">
+      <c r="L164" s="12">
         <v>77.400000000000006</v>
       </c>
-      <c r="M164" s="6">
+      <c r="M164" s="12">
         <v>166.26999999999998</v>
       </c>
       <c r="R164" s="6" t="s">
@@ -20606,19 +20614,19 @@
       <c r="H165" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I165" s="6">
+      <c r="I165" s="12">
         <v>65.08</v>
       </c>
-      <c r="J165" s="6">
+      <c r="J165" s="12">
         <v>40.200000000000003</v>
       </c>
-      <c r="K165" s="6">
+      <c r="K165" s="12">
         <v>29.4</v>
       </c>
-      <c r="L165" s="6">
+      <c r="L165" s="12">
         <v>99.9</v>
       </c>
-      <c r="M165" s="6">
+      <c r="M165" s="12">
         <v>172.78</v>
       </c>
       <c r="R165" s="6" t="s">
@@ -20706,19 +20714,19 @@
       <c r="H166" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I166" s="6">
+      <c r="I166" s="12">
         <v>40.6</v>
       </c>
-      <c r="J166" s="6">
+      <c r="J166" s="12">
         <v>37.9</v>
       </c>
-      <c r="K166" s="6">
+      <c r="K166" s="12">
         <v>15.7</v>
       </c>
-      <c r="L166" s="6">
+      <c r="L166" s="12">
         <v>20.3</v>
       </c>
-      <c r="M166" s="6">
+      <c r="M166" s="12">
         <v>97.5</v>
       </c>
       <c r="N166" s="6" t="s">
@@ -20818,19 +20826,19 @@
       <c r="H167" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I167" s="6">
+      <c r="I167" s="12">
         <v>56.4</v>
       </c>
-      <c r="J167" s="6">
+      <c r="J167" s="12">
         <v>26.26</v>
       </c>
-      <c r="K167" s="6">
+      <c r="K167" s="12">
         <v>29.57</v>
       </c>
-      <c r="L167" s="6">
+      <c r="L167" s="12">
         <v>60.4</v>
       </c>
-      <c r="M167" s="6">
+      <c r="M167" s="12">
         <v>126.55000000000001</v>
       </c>
       <c r="R167" s="6" t="s">
@@ -23764,5 +23772,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Quina_scraper_surface.xlsx
+++ b/data/Quina_scraper_surface.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Quina_valleys\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FE25FC-BEC4-4E2A-B6DD-10EEB96ED384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086EB06C-5C6C-40D1-9213-1190BCEEFFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{51F75AC8-9BCC-468F-8814-35286D6AD1E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51F75AC8-9BCC-468F-8814-35286D6AD1E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Quina scraper" sheetId="5" r:id="rId1"/>
@@ -1569,7 +1569,37 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1923,30 +1953,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3B0A72-F028-47A8-9FE2-6569D238CC68}">
   <dimension ref="A1:AY167"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="16.5" style="7" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="7" customWidth="1"/>
     <col min="3" max="3" width="13" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="7"/>
-    <col min="7" max="7" width="8.88671875" style="6"/>
-    <col min="8" max="8" width="11.6640625" style="6" customWidth="1"/>
-    <col min="9" max="13" width="8.88671875" style="12"/>
-    <col min="14" max="24" width="8.88671875" style="6"/>
+    <col min="4" max="4" width="11.375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="27.625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="8.875" style="7"/>
+    <col min="7" max="7" width="8.875" style="6"/>
+    <col min="8" max="8" width="11.625" style="6" customWidth="1"/>
+    <col min="9" max="13" width="8.875" style="12"/>
+    <col min="14" max="24" width="8.875" style="6"/>
     <col min="25" max="25" width="12" style="6" customWidth="1"/>
-    <col min="26" max="38" width="8.88671875" style="6"/>
-    <col min="39" max="39" width="14.33203125" style="6" customWidth="1"/>
-    <col min="40" max="45" width="8.88671875" style="6"/>
-    <col min="46" max="47" width="14.33203125" style="6" customWidth="1"/>
-    <col min="48" max="48" width="7.21875" style="6" customWidth="1"/>
-    <col min="49" max="50" width="11.88671875" style="6" customWidth="1"/>
-    <col min="51" max="51" width="20.109375" style="6" customWidth="1"/>
-    <col min="52" max="16384" width="8.88671875" style="6"/>
+    <col min="26" max="38" width="8.875" style="6"/>
+    <col min="39" max="39" width="14.375" style="6" customWidth="1"/>
+    <col min="40" max="45" width="8.875" style="6"/>
+    <col min="46" max="47" width="14.375" style="6" customWidth="1"/>
+    <col min="48" max="48" width="7.25" style="6" customWidth="1"/>
+    <col min="49" max="49" width="11.875" style="6" customWidth="1"/>
+    <col min="50" max="50" width="14.375" style="6" customWidth="1"/>
+    <col min="51" max="51" width="20.125" style="6" customWidth="1"/>
+    <col min="52" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="4" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" s="4" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>264</v>
       </c>
@@ -2101,7 +2132,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2190,7 +2221,6 @@
         <v>0.68046934732939079</v>
       </c>
       <c r="AS2" s="6">
-        <f>AVERAGE(AP2:AR2)</f>
         <v>0.68046934732939079</v>
       </c>
       <c r="AT2" s="6">
@@ -2206,14 +2236,13 @@
         <v>231.50587900166866</v>
       </c>
       <c r="AX2" s="2">
-        <f>(W2+AD2+AK2)/M2</f>
         <v>0.44768489215638541</v>
       </c>
       <c r="AY2" s="6">
         <v>0.59077809798270886</v>
       </c>
     </row>
-    <row r="3" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -2290,7 +2319,6 @@
         <v>0.89402823933180575</v>
       </c>
       <c r="AS3" s="6">
-        <f t="shared" ref="AS3:AS66" si="3">AVERAGE(AP3:AR3)</f>
         <v>0.89402823933180575</v>
       </c>
       <c r="AT3" s="6">
@@ -2306,14 +2334,13 @@
         <v>82.364318410569126</v>
       </c>
       <c r="AX3" s="2">
-        <f t="shared" ref="AX3:AX66" si="4">(W3+AD3+AK3)/M3</f>
         <v>0.24059375946682823</v>
       </c>
       <c r="AY3" s="6">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="4" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -2397,11 +2424,10 @@
         <v>70.918969965926664</v>
       </c>
       <c r="AX4" s="2">
-        <f t="shared" si="4"/>
         <v>0.29601020480476226</v>
       </c>
     </row>
-    <row r="5" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -2503,7 +2529,6 @@
         <v>0.87378640776699024</v>
       </c>
       <c r="AS5" s="6">
-        <f t="shared" si="3"/>
         <v>0.70972697431778808</v>
       </c>
       <c r="AT5" s="6">
@@ -2519,11 +2544,10 @@
         <v>244.76301368896543</v>
       </c>
       <c r="AX5" s="2">
-        <f t="shared" si="4"/>
         <v>0.68110172245693845</v>
       </c>
     </row>
-    <row r="6" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -2612,7 +2636,6 @@
         <v>0.28678679803229357</v>
       </c>
       <c r="AS6" s="6">
-        <f t="shared" si="3"/>
         <v>0.28678679803229357</v>
       </c>
       <c r="AT6" s="6">
@@ -2628,14 +2651,13 @@
         <v>73.293987258394054</v>
       </c>
       <c r="AX6" s="2">
-        <f t="shared" si="4"/>
         <v>0.49296629337452424</v>
       </c>
       <c r="AY6" s="6">
         <v>0.69551282051282048</v>
       </c>
     </row>
-    <row r="7" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -2712,7 +2734,6 @@
         <v>0.50779195745317973</v>
       </c>
       <c r="AS7" s="6">
-        <f t="shared" si="3"/>
         <v>0.50779195745317973</v>
       </c>
       <c r="AT7" s="6">
@@ -2728,14 +2749,13 @@
         <v>46.970583415153598</v>
       </c>
       <c r="AX7" s="2">
-        <f t="shared" si="4"/>
         <v>0.18332437319779094</v>
       </c>
       <c r="AY7" s="6">
         <v>0.64355231143552305</v>
       </c>
     </row>
-    <row r="8" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -2804,7 +2824,7 @@
         <v>2</v>
       </c>
       <c r="AA8" s="6">
-        <f t="shared" ref="AA8:AA68" si="5">AB8+AC8</f>
+        <f t="shared" ref="AA8:AA68" si="3">AB8+AC8</f>
         <v>9</v>
       </c>
       <c r="AB8" s="6">
@@ -2837,7 +2857,6 @@
         <v>0.41014925373134331</v>
       </c>
       <c r="AS8" s="6">
-        <f t="shared" si="3"/>
         <v>0.68347880168383346</v>
       </c>
       <c r="AT8" s="6">
@@ -2853,14 +2872,13 @@
         <v>424.3981855494946</v>
       </c>
       <c r="AX8" s="2">
-        <f t="shared" si="4"/>
         <v>0.57495418448381197</v>
       </c>
       <c r="AY8" s="6">
         <v>0.36674951670809164</v>
       </c>
     </row>
-    <row r="9" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
@@ -2937,7 +2955,6 @@
         <v>0.75217909352810619</v>
       </c>
       <c r="AS9" s="6">
-        <f t="shared" si="3"/>
         <v>0.75217909352810619</v>
       </c>
       <c r="AT9" s="6">
@@ -2953,14 +2970,13 @@
         <v>115.79834753819871</v>
       </c>
       <c r="AX9" s="2">
-        <f t="shared" si="4"/>
         <v>0.39954038082731452</v>
       </c>
       <c r="AY9" s="6">
         <v>0.45576981940618305</v>
       </c>
     </row>
-    <row r="10" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -3049,7 +3065,6 @@
         <v>0.9998665833253999</v>
       </c>
       <c r="AS10" s="6">
-        <f t="shared" si="3"/>
         <v>0.9998665833253999</v>
       </c>
       <c r="AT10" s="6">
@@ -3063,14 +3078,13 @@
         <v>174.87426574381246</v>
       </c>
       <c r="AX10" s="2">
-        <f t="shared" si="4"/>
         <v>0.46083191182259547</v>
       </c>
       <c r="AY10" s="6">
         <v>0.70787401574803155</v>
       </c>
     </row>
-    <row r="11" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
@@ -3151,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="AA11" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AB11" s="6">
@@ -3184,7 +3198,6 @@
         <v>0.16209135726426385</v>
       </c>
       <c r="AS11" s="6">
-        <f t="shared" si="3"/>
         <v>0.36330540966969688</v>
       </c>
       <c r="AT11" s="6">
@@ -3200,14 +3213,13 @@
         <v>190.88160683452386</v>
       </c>
       <c r="AX11" s="2">
-        <f t="shared" si="4"/>
         <v>0.58687742320310154</v>
       </c>
       <c r="AY11" s="6">
         <v>0.72169128294236895</v>
       </c>
     </row>
-    <row r="12" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -3288,7 +3300,7 @@
         <v>1</v>
       </c>
       <c r="AA12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AB12" s="6">
@@ -3321,7 +3333,6 @@
         <v>0.54125006145799215</v>
       </c>
       <c r="AS12" s="6">
-        <f t="shared" si="3"/>
         <v>0.57898716503995817</v>
       </c>
       <c r="AT12" s="6">
@@ -3337,14 +3348,13 @@
         <v>300.34157868211418</v>
       </c>
       <c r="AX12" s="2">
-        <f t="shared" si="4"/>
         <v>0.77749891821722217</v>
       </c>
       <c r="AY12" s="6">
         <v>0.78860489882854101</v>
       </c>
     </row>
-    <row r="13" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
@@ -3413,7 +3423,7 @@
         <v>3</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="AB13" s="6">
@@ -3446,7 +3456,6 @@
         <v>0.74368247042624069</v>
       </c>
       <c r="AS13" s="6">
-        <f t="shared" si="3"/>
         <v>0.65361003886162528</v>
       </c>
       <c r="AT13" s="6">
@@ -3462,14 +3471,13 @@
         <v>356.33662428967017</v>
       </c>
       <c r="AX13" s="2">
-        <f t="shared" si="4"/>
         <v>0.55119502192052028</v>
       </c>
       <c r="AY13" s="6">
         <v>0.41070277240490005</v>
       </c>
     </row>
-    <row r="14" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
@@ -3558,7 +3566,6 @@
         <v>0.37420196162707059</v>
       </c>
       <c r="AS14" s="6">
-        <f t="shared" si="3"/>
         <v>0.37420196162707059</v>
       </c>
       <c r="AT14" s="6">
@@ -3574,14 +3581,13 @@
         <v>46.254281232406619</v>
       </c>
       <c r="AX14" s="2">
-        <f t="shared" si="4"/>
         <v>0.30535372848948378</v>
       </c>
       <c r="AY14" s="6">
         <v>9.1211037301992842E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
@@ -3658,7 +3664,6 @@
         <v>0.24785321057447834</v>
       </c>
       <c r="AS15" s="6">
-        <f t="shared" si="3"/>
         <v>0.24785321057447834</v>
       </c>
       <c r="AT15" s="6">
@@ -3674,14 +3679,13 @@
         <v>23.97434535244814</v>
       </c>
       <c r="AX15" s="2">
-        <f t="shared" si="4"/>
         <v>0.29572307054515301</v>
       </c>
       <c r="AY15" s="6">
         <v>0.60748792270531404</v>
       </c>
     </row>
-    <row r="16" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3750,7 +3754,7 @@
         <v>3</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="AB16" s="6">
@@ -3783,7 +3787,6 @@
         <v>1</v>
       </c>
       <c r="AS16" s="6">
-        <f t="shared" si="3"/>
         <v>0.99062009384765393</v>
       </c>
       <c r="AT16" s="6">
@@ -3797,11 +3800,10 @@
         <v>364.41304874588963</v>
       </c>
       <c r="AX16" s="2">
-        <f t="shared" si="4"/>
         <v>0.80715282855813331</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>15</v>
       </c>
@@ -3870,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="AA17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="AB17" s="6">
@@ -3903,7 +3905,6 @@
         <v>0.51613521430163423</v>
       </c>
       <c r="AS17" s="6">
-        <f t="shared" si="3"/>
         <v>0.51993949753266011</v>
       </c>
       <c r="AT17" s="6">
@@ -3919,14 +3920,13 @@
         <v>381.57652606205272</v>
       </c>
       <c r="AX17" s="2">
-        <f t="shared" si="4"/>
         <v>0.56736938588450958</v>
       </c>
       <c r="AY17" s="6">
         <v>0.77689486552567244</v>
       </c>
     </row>
-    <row r="18" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>2</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AB18" s="6">
@@ -4040,7 +4040,6 @@
         <v>0.51017578247436446</v>
       </c>
       <c r="AS18" s="6">
-        <f t="shared" si="3"/>
         <v>0.49870672803252575</v>
       </c>
       <c r="AT18" s="6">
@@ -4056,14 +4055,13 @@
         <v>172.64935679756871</v>
       </c>
       <c r="AX18" s="2">
-        <f t="shared" si="4"/>
         <v>0.63886955311151317</v>
       </c>
       <c r="AY18" s="6">
         <v>0.77516339869281037</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
@@ -4140,7 +4138,6 @@
         <v>0.59677262610929338</v>
       </c>
       <c r="AS19" s="6">
-        <f t="shared" si="3"/>
         <v>0.59677262610929338</v>
       </c>
       <c r="AT19" s="6">
@@ -4156,11 +4153,10 @@
         <v>109.82740830959946</v>
       </c>
       <c r="AX19" s="2">
-        <f t="shared" si="4"/>
         <v>0.25119766715267661</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
@@ -4237,7 +4233,6 @@
         <v>0.76528742352635748</v>
       </c>
       <c r="AS20" s="6">
-        <f t="shared" si="3"/>
         <v>0.76528742352635748</v>
       </c>
       <c r="AT20" s="6">
@@ -4253,14 +4248,13 @@
         <v>77.070871963461826</v>
       </c>
       <c r="AX20" s="2">
-        <f t="shared" si="4"/>
         <v>0.31978798586572438</v>
       </c>
       <c r="AY20" s="6">
         <v>0.73050224581461831</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
@@ -4337,7 +4331,6 @@
         <v>0.76321529638246133</v>
       </c>
       <c r="AS21" s="6">
-        <f t="shared" si="3"/>
         <v>0.76321529638246133</v>
       </c>
       <c r="AT21" s="6">
@@ -4353,11 +4346,10 @@
         <v>79.336230058956858</v>
       </c>
       <c r="AX21" s="2">
-        <f t="shared" si="4"/>
         <v>0.28067111582361376</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4434,7 +4426,6 @@
         <v>0.45123439701810236</v>
       </c>
       <c r="AS22" s="6">
-        <f t="shared" si="3"/>
         <v>0.45123439701810236</v>
       </c>
       <c r="AT22" s="6">
@@ -4450,14 +4441,13 @@
         <v>46.318200088858887</v>
       </c>
       <c r="AX22" s="2">
-        <f t="shared" si="4"/>
         <v>0.42258487780875842</v>
       </c>
       <c r="AY22" s="6">
         <v>0.40869086908690866</v>
       </c>
     </row>
-    <row r="23" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4526,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="AA23" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AB23" s="6">
@@ -4559,7 +4549,6 @@
         <v>0.41700473487718265</v>
       </c>
       <c r="AS23" s="6">
-        <f t="shared" si="3"/>
         <v>0.52092991387579646</v>
       </c>
       <c r="AT23" s="6">
@@ -4575,14 +4564,13 @@
         <v>249.77927789353816</v>
       </c>
       <c r="AX23" s="2">
-        <f t="shared" si="4"/>
         <v>0.5112218023588686</v>
       </c>
       <c r="AY23" s="6">
         <v>0.99689226519337015</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
@@ -4659,7 +4647,6 @@
         <v>0.69331364664988215</v>
       </c>
       <c r="AS24" s="6">
-        <f t="shared" si="3"/>
         <v>0.69331364664988215</v>
       </c>
       <c r="AT24" s="6">
@@ -4675,11 +4662,10 @@
         <v>31.121462970819909</v>
       </c>
       <c r="AX24" s="2">
-        <f t="shared" si="4"/>
         <v>0.28023998451712795</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
@@ -4748,7 +4734,7 @@
         <v>2</v>
       </c>
       <c r="AA25" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="AB25" s="6">
@@ -4781,7 +4767,6 @@
         <v>0.52842133131001057</v>
       </c>
       <c r="AS25" s="6">
-        <f t="shared" si="3"/>
         <v>0.53929451602715206</v>
       </c>
       <c r="AT25" s="6">
@@ -4797,11 +4782,10 @@
         <v>701.85125766173303</v>
       </c>
       <c r="AX25" s="2">
-        <f t="shared" si="4"/>
         <v>0.55756703529768215</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
@@ -4890,7 +4874,6 @@
         <v>0.21443770792905542</v>
       </c>
       <c r="AS26" s="6">
-        <f t="shared" si="3"/>
         <v>0.21443770792905542</v>
       </c>
       <c r="AT26" s="6">
@@ -4906,14 +4889,13 @@
         <v>27.405550793732505</v>
       </c>
       <c r="AX26" s="2">
-        <f t="shared" si="4"/>
         <v>0.35946364105208867</v>
       </c>
       <c r="AY26" s="6">
         <v>0.49516008935219663</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>25</v>
       </c>
@@ -4990,7 +4972,6 @@
         <v>0.27742559224075924</v>
       </c>
       <c r="AS27" s="6">
-        <f t="shared" si="3"/>
         <v>0.27742559224075924</v>
       </c>
       <c r="AT27" s="6">
@@ -5006,14 +4987,13 @@
         <v>36.994869180660594</v>
       </c>
       <c r="AX27" s="2">
-        <f t="shared" si="4"/>
         <v>0.23941760112722366</v>
       </c>
       <c r="AY27" s="6">
         <v>0.24809160305343514</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
@@ -5090,7 +5070,6 @@
         <v>0.99113004325760001</v>
       </c>
       <c r="AS28" s="6">
-        <f t="shared" si="3"/>
         <v>0.99113004325760001</v>
       </c>
       <c r="AT28" s="6">
@@ -5104,11 +5083,10 @@
         <v>107.19796925022611</v>
       </c>
       <c r="AX28" s="2">
-        <f t="shared" si="4"/>
         <v>0.20040048479738631</v>
       </c>
     </row>
-    <row r="29" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -5197,7 +5175,6 @@
         <v>0.36877563125812873</v>
       </c>
       <c r="AS29" s="6">
-        <f t="shared" si="3"/>
         <v>0.36877563125812873</v>
       </c>
       <c r="AT29" s="6">
@@ -5213,14 +5190,13 @@
         <v>30.868179826646031</v>
       </c>
       <c r="AX29" s="2">
-        <f t="shared" si="4"/>
         <v>0.26794674516625411</v>
       </c>
       <c r="AY29" s="6">
         <v>0.46031128404669264</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
@@ -5297,7 +5273,6 @@
         <v>1</v>
       </c>
       <c r="AS30" s="6">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AT30" s="6">
@@ -5311,11 +5286,10 @@
         <v>315.26228229268946</v>
       </c>
       <c r="AX30" s="2">
-        <f t="shared" si="4"/>
         <v>0.32855766411126475</v>
       </c>
     </row>
-    <row r="31" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>29</v>
       </c>
@@ -5404,7 +5378,6 @@
         <v>0.60906013919463442</v>
       </c>
       <c r="AS31" s="6">
-        <f t="shared" si="3"/>
         <v>0.60906013919463442</v>
       </c>
       <c r="AT31" s="6">
@@ -5420,11 +5393,10 @@
         <v>169.18320281513755</v>
       </c>
       <c r="AX31" s="2">
-        <f t="shared" si="4"/>
         <v>0.53177151882074225</v>
       </c>
     </row>
-    <row r="32" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
@@ -5501,7 +5473,6 @@
         <v>0.79154169377212724</v>
       </c>
       <c r="AS32" s="6">
-        <f t="shared" si="3"/>
         <v>0.79154169377212724</v>
       </c>
       <c r="AT32" s="6">
@@ -5517,14 +5488,13 @@
         <v>118.23669881555027</v>
       </c>
       <c r="AX32" s="2">
-        <f t="shared" si="4"/>
         <v>0.27692926045016075</v>
       </c>
       <c r="AY32" s="6">
         <v>0.75942350332594244</v>
       </c>
     </row>
-    <row r="33" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>31</v>
       </c>
@@ -5605,7 +5575,7 @@
         <v>3</v>
       </c>
       <c r="AA33" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AB33" s="6">
@@ -5638,7 +5608,6 @@
         <v>0.62734348737373591</v>
       </c>
       <c r="AS33" s="6">
-        <f t="shared" si="3"/>
         <v>0.61402518270479289</v>
       </c>
       <c r="AT33" s="6">
@@ -5654,14 +5623,13 @@
         <v>364.86358796611114</v>
       </c>
       <c r="AX33" s="2">
-        <f t="shared" si="4"/>
         <v>0.44969962811099456</v>
       </c>
       <c r="AY33" s="6">
         <v>0.75294867708001278</v>
       </c>
     </row>
-    <row r="34" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>32</v>
       </c>
@@ -5738,7 +5706,6 @@
         <v>0.98141181129835309</v>
       </c>
       <c r="AS34" s="6">
-        <f t="shared" si="3"/>
         <v>0.98141181129835309</v>
       </c>
       <c r="AT34" s="6">
@@ -5754,14 +5721,13 @@
         <v>324.29693379597882</v>
       </c>
       <c r="AX34" s="2">
-        <f t="shared" si="4"/>
         <v>0.44697701371450643</v>
       </c>
       <c r="AY34" s="6">
         <v>0.27421171171171171</v>
       </c>
     </row>
-    <row r="35" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>33</v>
       </c>
@@ -5850,7 +5816,6 @@
         <v>0.78667885167516349</v>
       </c>
       <c r="AS35" s="6">
-        <f t="shared" si="3"/>
         <v>0.78667885167516349</v>
       </c>
       <c r="AT35" s="6">
@@ -5866,14 +5831,13 @@
         <v>102.44512759078188</v>
       </c>
       <c r="AX35" s="2">
-        <f t="shared" si="4"/>
         <v>0.38458188153310108</v>
       </c>
       <c r="AY35" s="6">
         <v>0.72767075306479867</v>
       </c>
     </row>
-    <row r="36" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
@@ -5950,7 +5914,6 @@
         <v>0.61391187379547452</v>
       </c>
       <c r="AS36" s="6">
-        <f t="shared" si="3"/>
         <v>0.61391187379547452</v>
       </c>
       <c r="AT36" s="6">
@@ -5966,14 +5929,13 @@
         <v>135.45597148172868</v>
       </c>
       <c r="AX36" s="2">
-        <f t="shared" si="4"/>
         <v>0.37956339990710636</v>
       </c>
       <c r="AY36" s="6">
         <v>0.21847470425371257</v>
       </c>
     </row>
-    <row r="37" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>35</v>
       </c>
@@ -6054,7 +6016,7 @@
         <v>3</v>
       </c>
       <c r="AA37" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="AB37" s="6">
@@ -6087,7 +6049,6 @@
         <v>0.47732326914178352</v>
       </c>
       <c r="AS37" s="6">
-        <f t="shared" si="3"/>
         <v>0.72620085935074574</v>
       </c>
       <c r="AT37" s="6">
@@ -6103,14 +6064,13 @@
         <v>329.27896086069313</v>
       </c>
       <c r="AX37" s="2">
-        <f t="shared" si="4"/>
         <v>0.54756743737957614</v>
       </c>
       <c r="AY37" s="6">
         <v>0.64818699430626314</v>
       </c>
     </row>
-    <row r="38" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>36</v>
       </c>
@@ -6191,7 +6151,7 @@
         <v>3</v>
       </c>
       <c r="AA38" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="AB38" s="6">
@@ -6224,7 +6184,6 @@
         <v>0.48674753702955709</v>
       </c>
       <c r="AS38" s="6">
-        <f t="shared" si="3"/>
         <v>0.53162275685044835</v>
       </c>
       <c r="AT38" s="6">
@@ -6240,14 +6199,13 @@
         <v>229.53701400267568</v>
       </c>
       <c r="AX38" s="2">
-        <f t="shared" si="4"/>
         <v>0.65683510446034843</v>
       </c>
       <c r="AY38" s="6">
         <v>0.8812709030100333</v>
       </c>
     </row>
-    <row r="39" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
@@ -6324,7 +6282,6 @@
         <v>0.46293731398945043</v>
       </c>
       <c r="AS39" s="6">
-        <f t="shared" si="3"/>
         <v>0.46293731398945043</v>
       </c>
       <c r="AT39" s="6">
@@ -6340,14 +6297,13 @@
         <v>37.993820883890983</v>
       </c>
       <c r="AX39" s="2">
-        <f t="shared" si="4"/>
         <v>0.37112517430011799</v>
       </c>
       <c r="AY39" s="6">
         <v>0.85402455661664389</v>
       </c>
     </row>
-    <row r="40" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
@@ -6424,7 +6380,6 @@
         <v>0.9887067428154912</v>
       </c>
       <c r="AS40" s="6">
-        <f t="shared" si="3"/>
         <v>0.9887067428154912</v>
       </c>
       <c r="AT40" s="6">
@@ -6438,14 +6393,13 @@
         <v>192.08909008163576</v>
       </c>
       <c r="AX40" s="2">
-        <f t="shared" si="4"/>
         <v>0.50183823529411753</v>
       </c>
       <c r="AY40" s="6">
         <v>0.87868162692847118</v>
       </c>
     </row>
-    <row r="41" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
@@ -6522,7 +6476,6 @@
         <v>0.83171493560742304</v>
       </c>
       <c r="AS41" s="6">
-        <f t="shared" si="3"/>
         <v>0.83171493560742304</v>
       </c>
       <c r="AT41" s="6">
@@ -6538,14 +6491,13 @@
         <v>121.67971210208017</v>
       </c>
       <c r="AX41" s="2">
-        <f t="shared" si="4"/>
         <v>0.4890029325513196</v>
       </c>
       <c r="AY41" s="6">
         <v>0.31892461781760678</v>
       </c>
     </row>
-    <row r="42" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
@@ -6622,7 +6574,6 @@
         <v>0.74980356106808377</v>
       </c>
       <c r="AS42" s="6">
-        <f t="shared" si="3"/>
         <v>0.74980356106808377</v>
       </c>
       <c r="AT42" s="6">
@@ -6638,14 +6589,13 @@
         <v>97.14700872766123</v>
       </c>
       <c r="AX42" s="2">
-        <f t="shared" si="4"/>
         <v>0.62040816326530612</v>
       </c>
       <c r="AY42" s="6">
         <v>0.38601532567049812</v>
       </c>
     </row>
-    <row r="43" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
@@ -6734,7 +6684,6 @@
         <v>1</v>
       </c>
       <c r="AS43" s="6">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AT43" s="6">
@@ -6748,14 +6697,13 @@
         <v>72.805473384226957</v>
       </c>
       <c r="AX43" s="2">
-        <f t="shared" si="4"/>
         <v>0.20633981903128507</v>
       </c>
       <c r="AY43" s="6">
         <v>0.45691056910569106</v>
       </c>
     </row>
-    <row r="44" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>42</v>
       </c>
@@ -6824,7 +6772,7 @@
         <v>2</v>
       </c>
       <c r="AA44" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="AB44" s="6">
@@ -6857,7 +6805,6 @@
         <v>0.6407329326406308</v>
       </c>
       <c r="AS44" s="6">
-        <f t="shared" si="3"/>
         <v>0.67264358705684391</v>
       </c>
       <c r="AT44" s="6">
@@ -6873,14 +6820,13 @@
         <v>670.43026678650517</v>
       </c>
       <c r="AX44" s="2">
-        <f t="shared" si="4"/>
         <v>0.71446742356432835</v>
       </c>
       <c r="AY44" s="6">
         <v>0.84220753983676644</v>
       </c>
     </row>
-    <row r="45" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
@@ -6969,7 +6915,6 @@
         <v>0.70424258696368103</v>
       </c>
       <c r="AS45" s="6">
-        <f t="shared" si="3"/>
         <v>0.70424258696368103</v>
       </c>
       <c r="AT45" s="6">
@@ -6985,14 +6930,13 @@
         <v>244.25273813364825</v>
       </c>
       <c r="AX45" s="2">
-        <f t="shared" si="4"/>
         <v>0.51815799326095091</v>
       </c>
       <c r="AY45" s="6">
         <v>0.40554241297735721</v>
       </c>
     </row>
-    <row r="46" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>44</v>
       </c>
@@ -7069,7 +7013,6 @@
         <v>0.98299881160189351</v>
       </c>
       <c r="AS46" s="6">
-        <f t="shared" si="3"/>
         <v>0.98299881160189351</v>
       </c>
       <c r="AT46" s="6">
@@ -7083,11 +7026,10 @@
         <v>375.38807767393689</v>
       </c>
       <c r="AX46" s="2">
-        <f t="shared" si="4"/>
         <v>0.55231774861533856</v>
       </c>
     </row>
-    <row r="47" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>265</v>
       </c>
@@ -7164,7 +7106,6 @@
         <v>0.90409667440102726</v>
       </c>
       <c r="AS47" s="6">
-        <f t="shared" si="3"/>
         <v>0.90409667440102726</v>
       </c>
       <c r="AT47" s="6">
@@ -7180,11 +7121,10 @@
         <v>53.83732958656725</v>
       </c>
       <c r="AX47" s="2">
-        <f t="shared" si="4"/>
         <v>0.37745041178517569</v>
       </c>
     </row>
-    <row r="48" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>45</v>
       </c>
@@ -7261,7 +7201,6 @@
         <v>0.98407006093423899</v>
       </c>
       <c r="AS48" s="6">
-        <f t="shared" si="3"/>
         <v>0.98407006093423899</v>
       </c>
       <c r="AT48" s="6">
@@ -7275,11 +7214,10 @@
         <v>132.91539092020486</v>
       </c>
       <c r="AX48" s="2">
-        <f t="shared" si="4"/>
         <v>0.21891172185097724</v>
       </c>
     </row>
-    <row r="49" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>46</v>
       </c>
@@ -7368,7 +7306,6 @@
         <v>0.83822318905912763</v>
       </c>
       <c r="AS49" s="6">
-        <f t="shared" si="3"/>
         <v>0.83822318905912763</v>
       </c>
       <c r="AT49" s="6">
@@ -7384,14 +7321,13 @@
         <v>54.151732682786829</v>
       </c>
       <c r="AX49" s="2">
-        <f t="shared" si="4"/>
         <v>0.25638674978608972</v>
       </c>
       <c r="AY49" s="6">
         <v>3.1592689295039167E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>47</v>
       </c>
@@ -7472,7 +7408,7 @@
         <v>3</v>
       </c>
       <c r="AA50" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="AB50" s="6">
@@ -7505,7 +7441,6 @@
         <v>1</v>
       </c>
       <c r="AS50" s="6">
-        <f t="shared" si="3"/>
         <v>0.90321766778279189</v>
       </c>
       <c r="AT50" s="6">
@@ -7519,14 +7454,13 @@
         <v>773.69770205944985</v>
       </c>
       <c r="AX50" s="2">
-        <f t="shared" si="4"/>
         <v>0.68328752781049606</v>
       </c>
       <c r="AY50" s="6">
         <v>0.66780383795309173</v>
       </c>
     </row>
-    <row r="51" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>48</v>
       </c>
@@ -7595,7 +7529,7 @@
         <v>3</v>
       </c>
       <c r="AA51" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="AB51" s="6">
@@ -7628,7 +7562,6 @@
         <v>0.98056238296283305</v>
       </c>
       <c r="AS51" s="6">
-        <f t="shared" si="3"/>
         <v>0.7187539155010102</v>
       </c>
       <c r="AT51" s="6">
@@ -7642,14 +7575,13 @@
         <v>425.674013911933</v>
       </c>
       <c r="AX51" s="2">
-        <f t="shared" si="4"/>
         <v>0.8494141750432167</v>
       </c>
       <c r="AY51" s="6">
         <v>0.58646902318510075</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>49</v>
       </c>
@@ -7718,7 +7650,7 @@
         <v>2</v>
       </c>
       <c r="AA52" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="AB52" s="6">
@@ -7751,7 +7683,6 @@
         <v>0.53245138792912849</v>
       </c>
       <c r="AS52" s="6">
-        <f t="shared" si="3"/>
         <v>0.59652533947192721</v>
       </c>
       <c r="AT52" s="6">
@@ -7767,14 +7698,13 @@
         <v>359.60229664825084</v>
       </c>
       <c r="AX52" s="2">
-        <f t="shared" si="4"/>
         <v>0.67330611344074143</v>
       </c>
       <c r="AY52" s="6">
         <v>0.37138389366692731</v>
       </c>
     </row>
-    <row r="53" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>50</v>
       </c>
@@ -7855,7 +7785,7 @@
         <v>2</v>
       </c>
       <c r="AA53" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="AB53" s="6">
@@ -7888,7 +7818,6 @@
         <v>0.57659374996753254</v>
       </c>
       <c r="AS53" s="6">
-        <f t="shared" si="3"/>
         <v>0.51004779783226195</v>
       </c>
       <c r="AT53" s="6">
@@ -7904,14 +7833,13 @@
         <v>313.34166241702854</v>
       </c>
       <c r="AX53" s="2">
-        <f t="shared" si="4"/>
         <v>0.58018073211824173</v>
       </c>
       <c r="AY53" s="6">
         <v>0.98367346938775502</v>
       </c>
     </row>
-    <row r="54" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>51</v>
       </c>
@@ -7992,7 +7920,7 @@
         <v>3</v>
       </c>
       <c r="AA54" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="AB54" s="6">
@@ -8025,7 +7953,6 @@
         <v>0.54755404079482817</v>
       </c>
       <c r="AS54" s="6">
-        <f t="shared" si="3"/>
         <v>0.5020713833058924</v>
       </c>
       <c r="AT54" s="6">
@@ -8041,14 +7968,13 @@
         <v>141.08105456618918</v>
       </c>
       <c r="AX54" s="2">
-        <f t="shared" si="4"/>
         <v>0.41290093921672877</v>
       </c>
       <c r="AY54" s="6">
         <v>0.22330097087378639</v>
       </c>
     </row>
-    <row r="55" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>52</v>
       </c>
@@ -8137,7 +8063,6 @@
         <v>0.644224713186896</v>
       </c>
       <c r="AS55" s="6">
-        <f t="shared" si="3"/>
         <v>0.644224713186896</v>
       </c>
       <c r="AT55" s="6">
@@ -8153,14 +8078,13 @@
         <v>56.288490089991853</v>
       </c>
       <c r="AX55" s="2">
-        <f t="shared" si="4"/>
         <v>0.24310363776239147</v>
       </c>
       <c r="AY55" s="6">
         <v>0.6070520965692503</v>
       </c>
     </row>
-    <row r="56" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>53</v>
       </c>
@@ -8229,7 +8153,7 @@
         <v>3</v>
       </c>
       <c r="AA56" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="AB56" s="6">
@@ -8262,7 +8186,6 @@
         <v>1</v>
       </c>
       <c r="AS56" s="6">
-        <f t="shared" si="3"/>
         <v>0.80386043595569778</v>
       </c>
       <c r="AT56" s="6">
@@ -8276,11 +8199,10 @@
         <v>562.60854908950216</v>
       </c>
       <c r="AX56" s="2">
-        <f t="shared" si="4"/>
         <v>0.65492451473759894</v>
       </c>
     </row>
-    <row r="57" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>54</v>
       </c>
@@ -8357,7 +8279,6 @@
         <v>0.9248042196724322</v>
       </c>
       <c r="AS57" s="6">
-        <f t="shared" si="3"/>
         <v>0.9248042196724322</v>
       </c>
       <c r="AT57" s="6">
@@ -8373,11 +8294,10 @@
         <v>300.83627869588031</v>
       </c>
       <c r="AX57" s="2">
-        <f t="shared" si="4"/>
         <v>0.55272348508057112</v>
       </c>
     </row>
-    <row r="58" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>55</v>
       </c>
@@ -8454,7 +8374,6 @@
         <v>0.66994312811635848</v>
       </c>
       <c r="AS58" s="6">
-        <f t="shared" si="3"/>
         <v>0.66994312811635848</v>
       </c>
       <c r="AT58" s="6">
@@ -8470,14 +8389,13 @@
         <v>78.088242741109951</v>
       </c>
       <c r="AX58" s="2">
-        <f t="shared" si="4"/>
         <v>0.30976645435244154</v>
       </c>
       <c r="AY58" s="6">
         <v>0.11671087533156499</v>
       </c>
     </row>
-    <row r="59" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>56</v>
       </c>
@@ -8546,7 +8464,7 @@
         <v>2</v>
       </c>
       <c r="AA59" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="AB59" s="6">
@@ -8579,7 +8497,6 @@
         <v>1</v>
       </c>
       <c r="AS59" s="6">
-        <f t="shared" si="3"/>
         <v>0.91197909355132034</v>
       </c>
       <c r="AT59" s="6">
@@ -8593,11 +8510,10 @@
         <v>354.05128321826385</v>
       </c>
       <c r="AX59" s="2">
-        <f t="shared" si="4"/>
         <v>0.44475500541897212</v>
       </c>
     </row>
-    <row r="60" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>57</v>
       </c>
@@ -8666,7 +8582,7 @@
         <v>3</v>
       </c>
       <c r="AA60" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="AB60" s="6">
@@ -8699,7 +8615,6 @@
         <v>1</v>
       </c>
       <c r="AS60" s="6">
-        <f t="shared" si="3"/>
         <v>0.99424368999459833</v>
       </c>
       <c r="AT60" s="6">
@@ -8713,11 +8628,10 @@
         <v>378.04951665481224</v>
       </c>
       <c r="AX60" s="2">
-        <f t="shared" si="4"/>
         <v>0.46598082768295529</v>
       </c>
     </row>
-    <row r="61" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>58</v>
       </c>
@@ -8798,7 +8712,7 @@
         <v>3</v>
       </c>
       <c r="AA61" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="AB61" s="6">
@@ -8831,7 +8745,6 @@
         <v>1</v>
       </c>
       <c r="AS61" s="6">
-        <f t="shared" si="3"/>
         <v>0.95080478861194395</v>
       </c>
       <c r="AT61" s="6">
@@ -8845,11 +8758,10 @@
         <v>212.35108585726053</v>
       </c>
       <c r="AX61" s="2">
-        <f t="shared" si="4"/>
         <v>0.50241976566479873</v>
       </c>
     </row>
-    <row r="62" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>59</v>
       </c>
@@ -8926,7 +8838,6 @@
         <v>0.80596073510917976</v>
       </c>
       <c r="AS62" s="6">
-        <f t="shared" si="3"/>
         <v>0.80596073510917976</v>
       </c>
       <c r="AT62" s="6">
@@ -8942,11 +8853,10 @@
         <v>101.62117120771114</v>
       </c>
       <c r="AX62" s="2">
-        <f t="shared" si="4"/>
         <v>0.47213622291021667</v>
       </c>
     </row>
-    <row r="63" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>60</v>
       </c>
@@ -9035,7 +8945,6 @@
         <v>0.69116234639294571</v>
       </c>
       <c r="AS63" s="6">
-        <f t="shared" si="3"/>
         <v>0.69116234639294571</v>
       </c>
       <c r="AT63" s="6">
@@ -9051,14 +8960,13 @@
         <v>99.201342778543705</v>
       </c>
       <c r="AX63" s="2">
-        <f t="shared" si="4"/>
         <v>0.42561683599419442</v>
       </c>
       <c r="AY63" s="6">
         <v>0.95406162464985989</v>
       </c>
     </row>
-    <row r="64" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>61</v>
       </c>
@@ -9139,7 +9047,7 @@
         <v>3</v>
       </c>
       <c r="AA64" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AB64" s="6">
@@ -9172,7 +9080,6 @@
         <v>0.4668602282109256</v>
       </c>
       <c r="AS64" s="6">
-        <f t="shared" si="3"/>
         <v>0.5290861941090671</v>
       </c>
       <c r="AT64" s="6">
@@ -9188,14 +9095,13 @@
         <v>223.00737585703109</v>
       </c>
       <c r="AX64" s="2">
-        <f t="shared" si="4"/>
         <v>0.6841032075915614</v>
       </c>
       <c r="AY64" s="6">
         <v>0.67002518891687657</v>
       </c>
     </row>
-    <row r="65" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>62</v>
       </c>
@@ -9272,7 +9178,6 @@
         <v>0.44768503448996605</v>
       </c>
       <c r="AS65" s="6">
-        <f t="shared" si="3"/>
         <v>0.44768503448996605</v>
       </c>
       <c r="AT65" s="6">
@@ -9288,14 +9193,13 @@
         <v>38.320048212203133</v>
       </c>
       <c r="AX65" s="2">
-        <f t="shared" si="4"/>
         <v>0.27379592933431851</v>
       </c>
       <c r="AY65" s="6">
         <v>0.29352566252935258</v>
       </c>
     </row>
-    <row r="66" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>63</v>
       </c>
@@ -9364,7 +9268,7 @@
         <v>2</v>
       </c>
       <c r="AA66" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AB66" s="6">
@@ -9397,7 +9301,6 @@
         <v>0.35294009414057503</v>
       </c>
       <c r="AS66" s="6">
-        <f t="shared" si="3"/>
         <v>0.2831457351228856</v>
       </c>
       <c r="AT66" s="6">
@@ -9413,14 +9316,13 @@
         <v>101.2547270126487</v>
       </c>
       <c r="AX66" s="2">
-        <f t="shared" si="4"/>
         <v>0.57319042725003677</v>
       </c>
       <c r="AY66" s="6">
         <v>0.37865259740259738</v>
       </c>
     </row>
-    <row r="67" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>64</v>
       </c>
@@ -9467,7 +9369,7 @@
         <v>2</v>
       </c>
       <c r="T67" s="6">
-        <f t="shared" ref="T67:T130" si="6">U67+V67</f>
+        <f t="shared" ref="T67:T130" si="4">U67+V67</f>
         <v>11</v>
       </c>
       <c r="U67" s="6">
@@ -9486,18 +9388,17 @@
         <v>314</v>
       </c>
       <c r="AN67" s="6">
-        <f t="shared" ref="AN67:AN130" si="7">AVERAGE(S67,Z67,AG67)</f>
+        <f t="shared" ref="AN67:AN130" si="5">AVERAGE(S67,Z67,AG67)</f>
         <v>2</v>
       </c>
       <c r="AO67" s="6">
-        <f t="shared" ref="AO67:AO130" si="8">T67+AA67+AH67</f>
+        <f t="shared" ref="AO67:AO130" si="6">T67+AA67+AH67</f>
         <v>11</v>
       </c>
       <c r="AP67" s="6">
         <v>0.30901470704057743</v>
       </c>
       <c r="AS67" s="6">
-        <f t="shared" ref="AS67:AS130" si="9">AVERAGE(AP67:AR67)</f>
         <v>0.30901470704057743</v>
       </c>
       <c r="AT67" s="6">
@@ -9513,14 +9414,13 @@
         <v>52.952760198473356</v>
       </c>
       <c r="AX67" s="2">
-        <f t="shared" ref="AX67:AX130" si="10">(W67+AD67+AK67)/M67</f>
         <v>0.3850237100997948</v>
       </c>
       <c r="AY67" s="6">
         <v>0.66302447552447552</v>
       </c>
     </row>
-    <row r="68" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>65</v>
       </c>
@@ -9567,7 +9467,7 @@
         <v>3</v>
       </c>
       <c r="T68" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="U68" s="6">
@@ -9586,7 +9486,7 @@
         <v>4</v>
       </c>
       <c r="AA68" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="AB68" s="6">
@@ -9605,11 +9505,11 @@
         <v>314</v>
       </c>
       <c r="AN68" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
       <c r="AO68" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="AP68" s="6">
@@ -9619,7 +9519,6 @@
         <v>1</v>
       </c>
       <c r="AS68" s="6">
-        <f t="shared" si="9"/>
         <v>0.80054884033260842</v>
       </c>
       <c r="AT68" s="6">
@@ -9633,11 +9532,10 @@
         <v>388.20241201768312</v>
       </c>
       <c r="AX68" s="2">
-        <f t="shared" si="10"/>
         <v>0.69454949944382649</v>
       </c>
     </row>
-    <row r="69" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>66</v>
       </c>
@@ -9684,37 +9582,36 @@
         <v>3</v>
       </c>
       <c r="T69" s="6">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="U69" s="6">
+        <v>3</v>
+      </c>
+      <c r="V69" s="6">
+        <v>11</v>
+      </c>
+      <c r="W69" s="6">
+        <v>62.99</v>
+      </c>
+      <c r="X69" s="6">
+        <v>17.277471752066514</v>
+      </c>
+      <c r="AM69" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN69" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO69" s="6">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="U69" s="6">
-        <v>3</v>
-      </c>
-      <c r="V69" s="6">
-        <v>11</v>
-      </c>
-      <c r="W69" s="6">
-        <v>62.99</v>
-      </c>
-      <c r="X69" s="6">
-        <v>17.277471752066514</v>
-      </c>
-      <c r="AM69" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN69" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO69" s="6">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
       <c r="AP69" s="6">
         <v>1</v>
       </c>
       <c r="AS69" s="6">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AT69" s="6">
@@ -9728,11 +9625,10 @@
         <v>108.83079456626697</v>
       </c>
       <c r="AX69" s="2">
-        <f t="shared" si="10"/>
         <v>0.32095179863446449</v>
       </c>
     </row>
-    <row r="70" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>67</v>
       </c>
@@ -9779,7 +9675,7 @@
         <v>3</v>
       </c>
       <c r="T70" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="U70" s="6">
@@ -9801,7 +9697,7 @@
         <v>3</v>
       </c>
       <c r="AA70" s="6">
-        <f t="shared" ref="AA70:AA133" si="11">AB70+AC70</f>
+        <f t="shared" ref="AA70:AA133" si="7">AB70+AC70</f>
         <v>11</v>
       </c>
       <c r="AB70" s="6">
@@ -9820,11 +9716,11 @@
         <v>314</v>
       </c>
       <c r="AN70" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AO70" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="AP70" s="6">
@@ -9834,8 +9730,7 @@
         <v>1.0022659709902535</v>
       </c>
       <c r="AS70" s="6">
-        <f t="shared" si="9"/>
-        <v>1.0011329854951267</v>
+        <v>1</v>
       </c>
       <c r="AT70" s="6">
         <v>69.016666666666666</v>
@@ -9848,11 +9743,10 @@
         <v>376.17612051446184</v>
       </c>
       <c r="AX70" s="2">
-        <f t="shared" si="10"/>
         <v>0.61510509440684003</v>
       </c>
     </row>
-    <row r="71" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>68</v>
       </c>
@@ -9899,37 +9793,36 @@
         <v>2</v>
       </c>
       <c r="T71" s="6">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="U71" s="6">
+        <v>4</v>
+      </c>
+      <c r="V71" s="6">
+        <v>8</v>
+      </c>
+      <c r="W71" s="6">
+        <v>50.95</v>
+      </c>
+      <c r="X71" s="6">
+        <v>20.673237657289985</v>
+      </c>
+      <c r="AM71" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN71" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO71" s="6">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="U71" s="6">
-        <v>4</v>
-      </c>
-      <c r="V71" s="6">
-        <v>8</v>
-      </c>
-      <c r="W71" s="6">
-        <v>50.95</v>
-      </c>
-      <c r="X71" s="6">
-        <v>20.673237657289985</v>
-      </c>
-      <c r="AM71" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN71" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO71" s="6">
-        <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
       <c r="AP71" s="6">
         <v>1</v>
       </c>
       <c r="AS71" s="6">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AT71" s="6">
@@ -9943,14 +9836,13 @@
         <v>105.33014586389247</v>
       </c>
       <c r="AX71" s="2">
-        <f t="shared" si="10"/>
         <v>0.24159514438806964</v>
       </c>
       <c r="AY71" s="6">
         <v>0.11896431070678797</v>
       </c>
     </row>
-    <row r="72" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>69</v>
       </c>
@@ -9997,7 +9889,7 @@
         <v>4</v>
       </c>
       <c r="T72" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="U72" s="6">
@@ -10019,7 +9911,7 @@
         <v>3</v>
       </c>
       <c r="AA72" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="AB72" s="6">
@@ -10038,11 +9930,11 @@
         <v>314</v>
       </c>
       <c r="AN72" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
       <c r="AO72" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="AP72" s="6">
@@ -10052,7 +9944,6 @@
         <v>0.98315783336989848</v>
       </c>
       <c r="AS72" s="6">
-        <f t="shared" si="9"/>
         <v>0.98401881203413444</v>
       </c>
       <c r="AT72" s="6">
@@ -10066,11 +9957,10 @@
         <v>326.90580963991994</v>
       </c>
       <c r="AX72" s="2">
-        <f t="shared" si="10"/>
         <v>0.46581699799127241</v>
       </c>
     </row>
-    <row r="73" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>70</v>
       </c>
@@ -10117,37 +10007,36 @@
         <v>4</v>
       </c>
       <c r="T73" s="6">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="U73" s="6">
+        <v>4</v>
+      </c>
+      <c r="V73" s="6">
+        <v>12</v>
+      </c>
+      <c r="W73" s="6">
+        <v>47.660000000000004</v>
+      </c>
+      <c r="X73" s="6">
+        <v>15.914163842325291</v>
+      </c>
+      <c r="AM73" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN73" s="6">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AO73" s="6">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="U73" s="6">
-        <v>4</v>
-      </c>
-      <c r="V73" s="6">
-        <v>12</v>
-      </c>
-      <c r="W73" s="6">
-        <v>47.660000000000004</v>
-      </c>
-      <c r="X73" s="6">
-        <v>15.914163842325291</v>
-      </c>
-      <c r="AM73" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN73" s="6">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="AO73" s="6">
-        <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
       <c r="AP73" s="6">
         <v>0.71268087068183128</v>
       </c>
       <c r="AS73" s="6">
-        <f t="shared" si="9"/>
         <v>0.71268087068183128</v>
       </c>
       <c r="AT73" s="6">
@@ -10163,14 +10052,13 @@
         <v>75.846904872522344</v>
       </c>
       <c r="AX73" s="2">
-        <f t="shared" si="10"/>
         <v>0.39812881129396044</v>
       </c>
       <c r="AY73" s="6">
         <v>0.21082089552238803</v>
       </c>
     </row>
-    <row r="74" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>71</v>
       </c>
@@ -10217,7 +10105,7 @@
         <v>2</v>
       </c>
       <c r="T74" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="U74" s="6">
@@ -10239,7 +10127,7 @@
         <v>2</v>
       </c>
       <c r="AA74" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="AB74" s="6">
@@ -10258,11 +10146,11 @@
         <v>314</v>
       </c>
       <c r="AN74" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AO74" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="AP74" s="6">
@@ -10272,7 +10160,6 @@
         <v>0.76915226239465118</v>
       </c>
       <c r="AS74" s="6">
-        <f t="shared" si="9"/>
         <v>0.59096754416112729</v>
       </c>
       <c r="AT74" s="6">
@@ -10288,14 +10175,13 @@
         <v>162.58970920031246</v>
       </c>
       <c r="AX74" s="2">
-        <f t="shared" si="10"/>
         <v>0.51642664266426641</v>
       </c>
       <c r="AY74" s="6">
         <v>0.59708958617553443</v>
       </c>
     </row>
-    <row r="75" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>72</v>
       </c>
@@ -10342,37 +10228,36 @@
         <v>3</v>
       </c>
       <c r="T75" s="6">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="U75" s="6">
+        <v>2</v>
+      </c>
+      <c r="V75" s="6">
+        <v>15</v>
+      </c>
+      <c r="W75" s="6">
+        <v>43.33</v>
+      </c>
+      <c r="X75" s="6">
+        <v>13.904358261314172</v>
+      </c>
+      <c r="AM75" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN75" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO75" s="6">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="U75" s="6">
-        <v>2</v>
-      </c>
-      <c r="V75" s="6">
-        <v>15</v>
-      </c>
-      <c r="W75" s="6">
-        <v>43.33</v>
-      </c>
-      <c r="X75" s="6">
-        <v>13.904358261314172</v>
-      </c>
-      <c r="AM75" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN75" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO75" s="6">
-        <f t="shared" si="8"/>
-        <v>17</v>
-      </c>
       <c r="AP75" s="6">
         <v>1</v>
       </c>
       <c r="AS75" s="6">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AT75" s="6">
@@ -10386,14 +10271,13 @@
         <v>60.247584346274309</v>
       </c>
       <c r="AX75" s="2">
-        <f t="shared" si="10"/>
         <v>0.31170419394288174</v>
       </c>
       <c r="AY75" s="6">
         <v>0.24007936507936509</v>
       </c>
     </row>
-    <row r="76" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>73</v>
       </c>
@@ -10452,37 +10336,36 @@
         <v>3</v>
       </c>
       <c r="T76" s="6">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="U76" s="6">
+        <v>6</v>
+      </c>
+      <c r="V76" s="6">
+        <v>18</v>
+      </c>
+      <c r="W76" s="6">
+        <v>41.08</v>
+      </c>
+      <c r="X76" s="6">
+        <v>8.7615300382978507</v>
+      </c>
+      <c r="AM76" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN76" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO76" s="6">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="U76" s="6">
-        <v>6</v>
-      </c>
-      <c r="V76" s="6">
-        <v>18</v>
-      </c>
-      <c r="W76" s="6">
-        <v>41.08</v>
-      </c>
-      <c r="X76" s="6">
-        <v>8.7615300382978507</v>
-      </c>
-      <c r="AM76" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN76" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO76" s="6">
-        <f t="shared" si="8"/>
-        <v>24</v>
-      </c>
       <c r="AP76" s="6">
         <v>0.51751506428221206</v>
       </c>
       <c r="AS76" s="6">
-        <f t="shared" si="9"/>
         <v>0.51751506428221206</v>
       </c>
       <c r="AT76" s="6">
@@ -10498,14 +10381,13 @@
         <v>35.992365397327568</v>
       </c>
       <c r="AX76" s="2">
-        <f t="shared" si="10"/>
         <v>0.35033259423503321</v>
       </c>
       <c r="AY76" s="6">
         <v>0.86282394995531719</v>
       </c>
     </row>
-    <row r="77" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>74</v>
       </c>
@@ -10564,7 +10446,7 @@
         <v>3</v>
       </c>
       <c r="T77" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="U77" s="6">
@@ -10586,7 +10468,7 @@
         <v>4</v>
       </c>
       <c r="AA77" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="AB77" s="6">
@@ -10605,11 +10487,11 @@
         <v>314</v>
       </c>
       <c r="AN77" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
       <c r="AO77" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="AP77" s="6">
@@ -10619,7 +10501,6 @@
         <v>0.95701130470077778</v>
       </c>
       <c r="AS77" s="6">
-        <f t="shared" si="9"/>
         <v>0.96628930311653227</v>
       </c>
       <c r="AT77" s="6">
@@ -10633,11 +10514,10 @@
         <v>514.61213327526082</v>
       </c>
       <c r="AX77" s="2">
-        <f t="shared" si="10"/>
         <v>0.63176514399205552</v>
       </c>
     </row>
-    <row r="78" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>75</v>
       </c>
@@ -10696,7 +10576,7 @@
         <v>2</v>
       </c>
       <c r="T78" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="U78" s="6">
@@ -10718,7 +10598,7 @@
         <v>2</v>
       </c>
       <c r="AA78" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AB78" s="6">
@@ -10737,11 +10617,11 @@
         <v>314</v>
       </c>
       <c r="AN78" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AO78" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="AP78" s="6">
@@ -10751,7 +10631,6 @@
         <v>0.78327554455392634</v>
       </c>
       <c r="AS78" s="6">
-        <f t="shared" si="9"/>
         <v>0.66253879567776219</v>
       </c>
       <c r="AT78" s="6">
@@ -10767,11 +10646,10 @@
         <v>89.772681736745426</v>
       </c>
       <c r="AX78" s="2">
-        <f t="shared" si="10"/>
         <v>0.45588452997779427</v>
       </c>
     </row>
-    <row r="79" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>76</v>
       </c>
@@ -10818,37 +10696,36 @@
         <v>2</v>
       </c>
       <c r="T79" s="6">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="U79" s="6">
+        <v>3</v>
+      </c>
+      <c r="V79" s="6">
+        <v>6</v>
+      </c>
+      <c r="W79" s="6">
+        <v>67.13</v>
+      </c>
+      <c r="X79" s="6">
+        <v>12.202448686088331</v>
+      </c>
+      <c r="AM79" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN79" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO79" s="6">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="U79" s="6">
-        <v>3</v>
-      </c>
-      <c r="V79" s="6">
-        <v>6</v>
-      </c>
-      <c r="W79" s="6">
-        <v>67.13</v>
-      </c>
-      <c r="X79" s="6">
-        <v>12.202448686088331</v>
-      </c>
-      <c r="AM79" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN79" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO79" s="6">
-        <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
       <c r="AP79" s="6">
         <v>0.62899220031383152</v>
       </c>
       <c r="AS79" s="6">
-        <f t="shared" si="9"/>
         <v>0.62899220031383152</v>
       </c>
       <c r="AT79" s="6">
@@ -10864,11 +10741,10 @@
         <v>81.915038029710971</v>
       </c>
       <c r="AX79" s="2">
-        <f t="shared" si="10"/>
         <v>0.45422559036470661</v>
       </c>
     </row>
-    <row r="80" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>77</v>
       </c>
@@ -10915,37 +10791,36 @@
         <v>2</v>
       </c>
       <c r="T80" s="6">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="U80" s="6">
+        <v>4</v>
+      </c>
+      <c r="V80" s="6">
+        <v>6</v>
+      </c>
+      <c r="W80" s="6">
+        <v>42.6</v>
+      </c>
+      <c r="X80" s="6">
+        <v>12.97251170051457</v>
+      </c>
+      <c r="AM80" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN80" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO80" s="6">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="U80" s="6">
-        <v>4</v>
-      </c>
-      <c r="V80" s="6">
-        <v>6</v>
-      </c>
-      <c r="W80" s="6">
-        <v>42.6</v>
-      </c>
-      <c r="X80" s="6">
-        <v>12.97251170051457</v>
-      </c>
-      <c r="AM80" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN80" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO80" s="6">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
       <c r="AP80" s="6">
         <v>0.99026806874157025</v>
       </c>
       <c r="AS80" s="6">
-        <f t="shared" si="9"/>
         <v>0.99026806874157025</v>
       </c>
       <c r="AT80" s="6">
@@ -10959,11 +10834,10 @@
         <v>55.262899844192063</v>
       </c>
       <c r="AX80" s="2">
-        <f t="shared" si="10"/>
         <v>0.34516285853184253</v>
       </c>
     </row>
-    <row r="81" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>78</v>
       </c>
@@ -11022,37 +10896,36 @@
         <v>2</v>
       </c>
       <c r="T81" s="6">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="U81" s="6">
+        <v>4</v>
+      </c>
+      <c r="V81" s="6">
+        <v>6</v>
+      </c>
+      <c r="W81" s="6">
+        <v>82.13</v>
+      </c>
+      <c r="X81" s="6">
+        <v>13.510982849600779</v>
+      </c>
+      <c r="AM81" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN81" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO81" s="6">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="U81" s="6">
-        <v>4</v>
-      </c>
-      <c r="V81" s="6">
-        <v>6</v>
-      </c>
-      <c r="W81" s="6">
-        <v>82.13</v>
-      </c>
-      <c r="X81" s="6">
-        <v>13.510982849600779</v>
-      </c>
-      <c r="AM81" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN81" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO81" s="6">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
       <c r="AP81" s="6">
         <v>0.68306283365019105</v>
       </c>
       <c r="AS81" s="6">
-        <f t="shared" si="9"/>
         <v>0.68306283365019105</v>
       </c>
       <c r="AT81" s="6">
@@ -11068,14 +10941,13 @@
         <v>110.96570214377121</v>
       </c>
       <c r="AX81" s="2">
-        <f t="shared" si="10"/>
         <v>0.53641173012866561</v>
       </c>
       <c r="AY81" s="6">
         <v>0.25042506679621085</v>
       </c>
     </row>
-    <row r="82" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>79</v>
       </c>
@@ -11122,7 +10994,7 @@
         <v>2</v>
       </c>
       <c r="T82" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="U82" s="6">
@@ -11144,7 +11016,7 @@
         <v>2</v>
       </c>
       <c r="AA82" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="AB82" s="6">
@@ -11163,11 +11035,11 @@
         <v>314</v>
       </c>
       <c r="AN82" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AO82" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="AP82" s="6">
@@ -11177,7 +11049,6 @@
         <v>0.54689443864873211</v>
       </c>
       <c r="AS82" s="6">
-        <f t="shared" si="9"/>
         <v>0.773447219324366</v>
       </c>
       <c r="AT82" s="6">
@@ -11191,14 +11062,13 @@
         <v>220.33108184722437</v>
       </c>
       <c r="AX82" s="2">
-        <f t="shared" si="10"/>
         <v>0.61512463033375597</v>
       </c>
       <c r="AY82" s="6">
         <v>0.36359199609565646</v>
       </c>
     </row>
-    <row r="83" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>80</v>
       </c>
@@ -11245,7 +11115,7 @@
         <v>3</v>
       </c>
       <c r="T83" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="U83" s="6">
@@ -11267,7 +11137,7 @@
         <v>3</v>
       </c>
       <c r="AA83" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AB83" s="6">
@@ -11286,11 +11156,11 @@
         <v>314</v>
       </c>
       <c r="AN83" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AO83" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="AP83" s="6">
@@ -11300,7 +11170,6 @@
         <v>0.85019714378309086</v>
       </c>
       <c r="AS83" s="6">
-        <f t="shared" si="9"/>
         <v>0.92509857189154543</v>
       </c>
       <c r="AT83" s="6">
@@ -11314,14 +11183,13 @@
         <v>208.72211301834773</v>
       </c>
       <c r="AX83" s="2">
-        <f t="shared" si="10"/>
         <v>0.62733163165128614</v>
       </c>
       <c r="AY83" s="6">
         <v>0.50122649223221583</v>
       </c>
     </row>
-    <row r="84" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>81</v>
       </c>
@@ -11368,37 +11236,36 @@
         <v>2</v>
       </c>
       <c r="T84" s="6">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="U84" s="6">
+        <v>1</v>
+      </c>
+      <c r="V84" s="6">
+        <v>10</v>
+      </c>
+      <c r="W84" s="6">
+        <v>105.76</v>
+      </c>
+      <c r="X84" s="6">
+        <v>16.493832990870189</v>
+      </c>
+      <c r="AM84" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN84" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO84" s="6">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="U84" s="6">
-        <v>1</v>
-      </c>
-      <c r="V84" s="6">
-        <v>10</v>
-      </c>
-      <c r="W84" s="6">
-        <v>105.76</v>
-      </c>
-      <c r="X84" s="6">
-        <v>16.493832990870189</v>
-      </c>
-      <c r="AM84" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN84" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO84" s="6">
-        <f t="shared" si="8"/>
-        <v>11</v>
-      </c>
       <c r="AP84" s="6">
         <v>0.44820198344755952</v>
       </c>
       <c r="AS84" s="6">
-        <f t="shared" si="9"/>
         <v>0.44820198344755952</v>
       </c>
       <c r="AT84" s="6">
@@ -11414,14 +11281,13 @@
         <v>174.43877771144312</v>
       </c>
       <c r="AX84" s="2">
-        <f t="shared" si="10"/>
         <v>0.36597688421344043</v>
       </c>
       <c r="AY84" s="6">
         <v>0.76047230812482436</v>
       </c>
     </row>
-    <row r="85" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>82</v>
       </c>
@@ -11468,37 +11334,36 @@
         <v>2</v>
       </c>
       <c r="T85" s="6">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="U85" s="6">
+        <v>4</v>
+      </c>
+      <c r="V85" s="6">
+        <v>9</v>
+      </c>
+      <c r="W85" s="6">
+        <v>94.85</v>
+      </c>
+      <c r="X85" s="6">
+        <v>19.236627439141742</v>
+      </c>
+      <c r="AM85" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AN85" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO85" s="6">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="U85" s="6">
-        <v>4</v>
-      </c>
-      <c r="V85" s="6">
-        <v>9</v>
-      </c>
-      <c r="W85" s="6">
-        <v>94.85</v>
-      </c>
-      <c r="X85" s="6">
-        <v>19.236627439141742</v>
-      </c>
-      <c r="AM85" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="AN85" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO85" s="6">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
       <c r="AP85" s="6">
         <v>0.7725553188410339</v>
       </c>
       <c r="AS85" s="6">
-        <f t="shared" si="9"/>
         <v>0.7725553188410339</v>
       </c>
       <c r="AT85" s="6">
@@ -11514,11 +11379,10 @@
         <v>182.4594112602594</v>
       </c>
       <c r="AX85" s="2">
-        <f t="shared" si="10"/>
         <v>0.51678108314263915</v>
       </c>
     </row>
-    <row r="86" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>83</v>
       </c>
@@ -11565,37 +11429,36 @@
         <v>2</v>
       </c>
       <c r="T86" s="6">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="U86" s="6">
+        <v>3</v>
+      </c>
+      <c r="V86" s="6">
+        <v>6</v>
+      </c>
+      <c r="W86" s="6">
+        <v>57.62</v>
+      </c>
+      <c r="X86" s="6">
+        <v>19.63254054252539</v>
+      </c>
+      <c r="AM86" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN86" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO86" s="6">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="U86" s="6">
-        <v>3</v>
-      </c>
-      <c r="V86" s="6">
-        <v>6</v>
-      </c>
-      <c r="W86" s="6">
-        <v>57.62</v>
-      </c>
-      <c r="X86" s="6">
-        <v>19.63254054252539</v>
-      </c>
-      <c r="AM86" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN86" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO86" s="6">
-        <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
       <c r="AP86" s="6">
         <v>0.66236641506495919</v>
       </c>
       <c r="AS86" s="6">
-        <f t="shared" si="9"/>
         <v>0.66236641506495919</v>
       </c>
       <c r="AT86" s="6">
@@ -11611,14 +11474,13 @@
         <v>113.12269860603131</v>
       </c>
       <c r="AX86" s="2">
-        <f t="shared" si="10"/>
         <v>0.40853658536585358</v>
       </c>
       <c r="AY86" s="6">
         <v>0.23772893772893772</v>
       </c>
     </row>
-    <row r="87" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>84</v>
       </c>
@@ -11665,7 +11527,7 @@
         <v>3</v>
       </c>
       <c r="T87" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="U87" s="6">
@@ -11687,7 +11549,7 @@
         <v>3</v>
       </c>
       <c r="AA87" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="AB87" s="6">
@@ -11706,11 +11568,11 @@
         <v>324</v>
       </c>
       <c r="AN87" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AO87" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="AP87" s="6">
@@ -11720,7 +11582,6 @@
         <v>0.69563800126427477</v>
       </c>
       <c r="AS87" s="6">
-        <f t="shared" si="9"/>
         <v>0.81418941883035534</v>
       </c>
       <c r="AT87" s="6">
@@ -11734,14 +11595,13 @@
         <v>140.49310651780704</v>
       </c>
       <c r="AX87" s="2">
-        <f t="shared" si="10"/>
         <v>0.54246597150362186</v>
       </c>
       <c r="AY87" s="6">
         <v>0.31912013536379019</v>
       </c>
     </row>
-    <row r="88" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>85</v>
       </c>
@@ -11800,37 +11660,36 @@
         <v>4</v>
       </c>
       <c r="T88" s="6">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="U88" s="6">
+        <v>6</v>
+      </c>
+      <c r="V88" s="6">
+        <v>12</v>
+      </c>
+      <c r="W88" s="6">
+        <v>51.37</v>
+      </c>
+      <c r="X88" s="6">
+        <v>27.090609082310138</v>
+      </c>
+      <c r="AM88" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN88" s="6">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AO88" s="6">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="U88" s="6">
-        <v>6</v>
-      </c>
-      <c r="V88" s="6">
-        <v>12</v>
-      </c>
-      <c r="W88" s="6">
-        <v>51.37</v>
-      </c>
-      <c r="X88" s="6">
-        <v>27.090609082310138</v>
-      </c>
-      <c r="AM88" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN88" s="6">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="AO88" s="6">
-        <f t="shared" si="8"/>
-        <v>18</v>
-      </c>
       <c r="AP88" s="6">
         <v>0.98943057276516211</v>
       </c>
       <c r="AS88" s="6">
-        <f t="shared" si="9"/>
         <v>0.98943057276516211</v>
       </c>
       <c r="AT88" s="6">
@@ -11844,14 +11703,13 @@
         <v>139.16445885582715</v>
       </c>
       <c r="AX88" s="2">
-        <f t="shared" si="10"/>
         <v>0.35449589400317438</v>
       </c>
       <c r="AY88" s="6">
         <v>0.11122697254084116</v>
       </c>
     </row>
-    <row r="89" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>86</v>
       </c>
@@ -11898,37 +11756,36 @@
         <v>2</v>
       </c>
       <c r="T89" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="U89" s="6">
+        <v>7</v>
+      </c>
+      <c r="V89" s="6">
+        <v>8</v>
+      </c>
+      <c r="W89" s="6">
+        <v>69.7</v>
+      </c>
+      <c r="X89" s="6">
+        <v>20.219226588887881</v>
+      </c>
+      <c r="AM89" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN89" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO89" s="6">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="U89" s="6">
-        <v>7</v>
-      </c>
-      <c r="V89" s="6">
-        <v>8</v>
-      </c>
-      <c r="W89" s="6">
-        <v>69.7</v>
-      </c>
-      <c r="X89" s="6">
-        <v>20.219226588887881</v>
-      </c>
-      <c r="AM89" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN89" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO89" s="6">
-        <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
       <c r="AP89" s="6">
         <v>1</v>
       </c>
       <c r="AS89" s="6">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AT89" s="6">
@@ -11942,14 +11799,13 @@
         <v>140.92800932454855</v>
       </c>
       <c r="AX89" s="2">
-        <f t="shared" si="10"/>
         <v>0.51825414528961256</v>
       </c>
       <c r="AY89" s="6">
         <v>0.29712322885358522</v>
       </c>
     </row>
-    <row r="90" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>87</v>
       </c>
@@ -11996,37 +11852,36 @@
         <v>3</v>
       </c>
       <c r="T90" s="6">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="U90" s="6">
+        <v>3</v>
+      </c>
+      <c r="V90" s="6">
+        <v>11</v>
+      </c>
+      <c r="W90" s="6">
+        <v>40.01</v>
+      </c>
+      <c r="X90" s="6">
+        <v>9.5901917683953588</v>
+      </c>
+      <c r="AM90" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN90" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO90" s="6">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="U90" s="6">
-        <v>3</v>
-      </c>
-      <c r="V90" s="6">
-        <v>11</v>
-      </c>
-      <c r="W90" s="6">
-        <v>40.01</v>
-      </c>
-      <c r="X90" s="6">
-        <v>9.5901917683953588</v>
-      </c>
-      <c r="AM90" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN90" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO90" s="6">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
       <c r="AP90" s="6">
         <v>0.65462059852528043</v>
       </c>
       <c r="AS90" s="6">
-        <f t="shared" si="9"/>
         <v>0.65462059852528043</v>
       </c>
       <c r="AT90" s="6">
@@ -12042,14 +11897,13 @@
         <v>38.370357265349824</v>
       </c>
       <c r="AX90" s="2">
-        <f t="shared" si="10"/>
         <v>0.36686227764533286</v>
       </c>
       <c r="AY90" s="6">
         <v>0.30665425779432298</v>
       </c>
     </row>
-    <row r="91" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>88</v>
       </c>
@@ -12108,37 +11962,36 @@
         <v>3</v>
       </c>
       <c r="T91" s="6">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="U91" s="6">
+        <v>7</v>
+      </c>
+      <c r="V91" s="6">
+        <v>13</v>
+      </c>
+      <c r="W91" s="6">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="X91" s="6">
+        <v>15.798808758283929</v>
+      </c>
+      <c r="AM91" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN91" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO91" s="6">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="U91" s="6">
-        <v>7</v>
-      </c>
-      <c r="V91" s="6">
-        <v>13</v>
-      </c>
-      <c r="W91" s="6">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="X91" s="6">
-        <v>15.798808758283929</v>
-      </c>
-      <c r="AM91" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN91" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO91" s="6">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
       <c r="AP91" s="6">
         <v>0.86003313871986542</v>
       </c>
       <c r="AS91" s="6">
-        <f t="shared" si="9"/>
         <v>0.86003313871986542</v>
       </c>
       <c r="AT91" s="6">
@@ -12154,14 +12007,13 @@
         <v>51.820092727171286</v>
       </c>
       <c r="AX91" s="2">
-        <f t="shared" si="10"/>
         <v>0.3273126434487576</v>
       </c>
       <c r="AY91" s="6">
         <v>0.59766454352441611</v>
       </c>
     </row>
-    <row r="92" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>89</v>
       </c>
@@ -12208,37 +12060,36 @@
         <v>2</v>
       </c>
       <c r="T92" s="6">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="U92" s="6">
+        <v>0</v>
+      </c>
+      <c r="V92" s="6">
+        <v>7</v>
+      </c>
+      <c r="W92" s="6">
+        <v>30.44</v>
+      </c>
+      <c r="X92" s="6">
+        <v>14.895636945092344</v>
+      </c>
+      <c r="AM92" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN92" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO92" s="6">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="U92" s="6">
-        <v>0</v>
-      </c>
-      <c r="V92" s="6">
-        <v>7</v>
-      </c>
-      <c r="W92" s="6">
-        <v>30.44</v>
-      </c>
-      <c r="X92" s="6">
-        <v>14.895636945092344</v>
-      </c>
-      <c r="AM92" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN92" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO92" s="6">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
       <c r="AP92" s="6">
         <v>0.86301488673767912</v>
       </c>
       <c r="AS92" s="6">
-        <f t="shared" si="9"/>
         <v>0.86301488673767912</v>
       </c>
       <c r="AT92" s="6">
@@ -12254,14 +12105,13 @@
         <v>45.342318860861099</v>
       </c>
       <c r="AX92" s="2">
-        <f t="shared" si="10"/>
         <v>0.29720757664518643</v>
       </c>
       <c r="AY92" s="6">
         <v>0.95045045045045029</v>
       </c>
     </row>
-    <row r="93" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>90</v>
       </c>
@@ -12308,37 +12158,36 @@
         <v>3</v>
       </c>
       <c r="T93" s="6">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="U93" s="6">
+        <v>6</v>
+      </c>
+      <c r="V93" s="6">
+        <v>14</v>
+      </c>
+      <c r="W93" s="6">
+        <v>36.74</v>
+      </c>
+      <c r="X93" s="6">
+        <v>16.233634350032396</v>
+      </c>
+      <c r="AM93" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN93" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO93" s="6">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="U93" s="6">
-        <v>6</v>
-      </c>
-      <c r="V93" s="6">
-        <v>14</v>
-      </c>
-      <c r="W93" s="6">
-        <v>36.74</v>
-      </c>
-      <c r="X93" s="6">
-        <v>16.233634350032396</v>
-      </c>
-      <c r="AM93" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN93" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO93" s="6">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
       <c r="AP93" s="6">
         <v>0.97851924954987324</v>
       </c>
       <c r="AS93" s="6">
-        <f t="shared" si="9"/>
         <v>0.97851924954987324</v>
       </c>
       <c r="AT93" s="6">
@@ -12352,11 +12201,10 @@
         <v>59.64237260201903</v>
       </c>
       <c r="AX93" s="2">
-        <f t="shared" si="10"/>
         <v>0.29029709228824274</v>
       </c>
     </row>
-    <row r="94" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>91</v>
       </c>
@@ -12403,37 +12251,36 @@
         <v>2</v>
       </c>
       <c r="T94" s="6">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="U94" s="6">
+        <v>5</v>
+      </c>
+      <c r="V94" s="6">
+        <v>7</v>
+      </c>
+      <c r="W94" s="6">
+        <v>32.659999999999997</v>
+      </c>
+      <c r="X94" s="6">
+        <v>12.453495055824163</v>
+      </c>
+      <c r="AM94" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN94" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO94" s="6">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="U94" s="6">
-        <v>5</v>
-      </c>
-      <c r="V94" s="6">
-        <v>7</v>
-      </c>
-      <c r="W94" s="6">
-        <v>32.659999999999997</v>
-      </c>
-      <c r="X94" s="6">
-        <v>12.453495055824163</v>
-      </c>
-      <c r="AM94" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN94" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO94" s="6">
-        <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
       <c r="AP94" s="6">
         <v>1</v>
       </c>
       <c r="AS94" s="6">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AT94" s="6">
@@ -12447,11 +12294,10 @@
         <v>40.673114852321717</v>
       </c>
       <c r="AX94" s="2">
-        <f t="shared" si="10"/>
         <v>0.2894876794894522</v>
       </c>
     </row>
-    <row r="95" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>92</v>
       </c>
@@ -12498,37 +12344,36 @@
         <v>4</v>
       </c>
       <c r="T95" s="6">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="U95" s="6">
+        <v>6</v>
+      </c>
+      <c r="V95" s="6">
+        <v>29</v>
+      </c>
+      <c r="W95" s="6">
+        <v>130.75</v>
+      </c>
+      <c r="X95" s="6">
+        <v>40.286132340769697</v>
+      </c>
+      <c r="AM95" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN95" s="6">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AO95" s="6">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="U95" s="6">
-        <v>6</v>
-      </c>
-      <c r="V95" s="6">
-        <v>29</v>
-      </c>
-      <c r="W95" s="6">
-        <v>130.75</v>
-      </c>
-      <c r="X95" s="6">
-        <v>40.286132340769697</v>
-      </c>
-      <c r="AM95" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN95" s="6">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="AO95" s="6">
-        <f t="shared" si="8"/>
-        <v>35</v>
-      </c>
       <c r="AP95" s="6">
         <v>0.78806988147045576</v>
       </c>
       <c r="AS95" s="6">
-        <f t="shared" si="9"/>
         <v>0.78806988147045576</v>
       </c>
       <c r="AT95" s="6">
@@ -12544,11 +12389,10 @@
         <v>526.74118035556376</v>
       </c>
       <c r="AX95" s="2">
-        <f t="shared" si="10"/>
         <v>0.49879830618395454</v>
       </c>
     </row>
-    <row r="96" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>93</v>
       </c>
@@ -12595,37 +12439,36 @@
         <v>3</v>
       </c>
       <c r="T96" s="6">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="U96" s="6">
+        <v>2</v>
+      </c>
+      <c r="V96" s="6">
+        <v>9</v>
+      </c>
+      <c r="W96" s="6">
+        <v>37.67</v>
+      </c>
+      <c r="X96" s="6">
+        <v>15.546778903660144</v>
+      </c>
+      <c r="AM96" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN96" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO96" s="6">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="U96" s="6">
-        <v>2</v>
-      </c>
-      <c r="V96" s="6">
-        <v>9</v>
-      </c>
-      <c r="W96" s="6">
-        <v>37.67</v>
-      </c>
-      <c r="X96" s="6">
-        <v>15.546778903660144</v>
-      </c>
-      <c r="AM96" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN96" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO96" s="6">
-        <f t="shared" si="8"/>
-        <v>11</v>
-      </c>
       <c r="AP96" s="6">
         <v>0.77733894518300717</v>
       </c>
       <c r="AS96" s="6">
-        <f t="shared" si="9"/>
         <v>0.77733894518300717</v>
       </c>
       <c r="AT96" s="6">
@@ -12641,14 +12484,13 @@
         <v>58.564716130087767</v>
       </c>
       <c r="AX96" s="2">
-        <f t="shared" si="10"/>
         <v>0.33757505152791467</v>
       </c>
       <c r="AY96" s="6">
         <v>0.82773409578270196</v>
       </c>
     </row>
-    <row r="97" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>94</v>
       </c>
@@ -12707,37 +12549,36 @@
         <v>3</v>
       </c>
       <c r="T97" s="6">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="U97" s="6">
+        <v>5</v>
+      </c>
+      <c r="V97" s="6">
+        <v>11</v>
+      </c>
+      <c r="W97" s="6">
+        <v>50.010000000000005</v>
+      </c>
+      <c r="X97" s="6">
+        <v>12.164572889883988</v>
+      </c>
+      <c r="AM97" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN97" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO97" s="6">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="U97" s="6">
-        <v>5</v>
-      </c>
-      <c r="V97" s="6">
-        <v>11</v>
-      </c>
-      <c r="W97" s="6">
-        <v>50.010000000000005</v>
-      </c>
-      <c r="X97" s="6">
-        <v>12.164572889883988</v>
-      </c>
-      <c r="AM97" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN97" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO97" s="6">
-        <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
       <c r="AP97" s="6">
         <v>0.40575626717424912</v>
       </c>
       <c r="AS97" s="6">
-        <f t="shared" si="9"/>
         <v>0.40575626717424912</v>
       </c>
       <c r="AT97" s="6">
@@ -12753,14 +12594,13 @@
         <v>60.835029022309833</v>
       </c>
       <c r="AX97" s="2">
-        <f t="shared" si="10"/>
         <v>0.32501462273347642</v>
       </c>
       <c r="AY97" s="6">
         <v>7.5440067057837387E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>95</v>
       </c>
@@ -12807,7 +12647,7 @@
         <v>3</v>
       </c>
       <c r="T98" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="U98" s="6">
@@ -12829,7 +12669,7 @@
         <v>4</v>
       </c>
       <c r="AA98" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="AB98" s="6">
@@ -12848,11 +12688,11 @@
         <v>314</v>
       </c>
       <c r="AN98" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
       <c r="AO98" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="AP98" s="6">
@@ -12862,7 +12702,6 @@
         <v>0.59470742834051848</v>
       </c>
       <c r="AS98" s="6">
-        <f t="shared" si="9"/>
         <v>0.79735371417025924</v>
       </c>
       <c r="AT98" s="6">
@@ -12876,11 +12715,10 @@
         <v>242.81864961332184</v>
       </c>
       <c r="AX98" s="2">
-        <f t="shared" si="10"/>
         <v>0.40154810644831113</v>
       </c>
     </row>
-    <row r="99" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>96</v>
       </c>
@@ -12939,7 +12777,7 @@
         <v>2</v>
       </c>
       <c r="T99" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="U99" s="6">
@@ -12961,7 +12799,7 @@
         <v>2</v>
       </c>
       <c r="AA99" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="AB99" s="6">
@@ -12980,11 +12818,11 @@
         <v>314</v>
       </c>
       <c r="AN99" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AO99" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="AP99" s="6">
@@ -12994,7 +12832,6 @@
         <v>0.67420937248526491</v>
       </c>
       <c r="AS99" s="6">
-        <f t="shared" si="9"/>
         <v>0.5723397436878449</v>
       </c>
       <c r="AT99" s="6">
@@ -13010,14 +12847,13 @@
         <v>136.63352233111181</v>
       </c>
       <c r="AX99" s="2">
-        <f t="shared" si="10"/>
         <v>0.40531097134870719</v>
       </c>
       <c r="AY99" s="6">
         <v>0.52299117510450532</v>
       </c>
     </row>
-    <row r="100" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>97</v>
       </c>
@@ -13064,37 +12900,36 @@
         <v>3</v>
       </c>
       <c r="T100" s="6">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="U100" s="6">
+        <v>5</v>
+      </c>
+      <c r="V100" s="6">
+        <v>11</v>
+      </c>
+      <c r="W100" s="6">
+        <v>39.58</v>
+      </c>
+      <c r="X100" s="6">
+        <v>13.667455695918255</v>
+      </c>
+      <c r="AM100" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN100" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO100" s="6">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="U100" s="6">
-        <v>5</v>
-      </c>
-      <c r="V100" s="6">
-        <v>11</v>
-      </c>
-      <c r="W100" s="6">
-        <v>39.58</v>
-      </c>
-      <c r="X100" s="6">
-        <v>13.667455695918255</v>
-      </c>
-      <c r="AM100" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN100" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO100" s="6">
-        <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
       <c r="AP100" s="6">
         <v>0.9976245033516975</v>
       </c>
       <c r="AS100" s="6">
-        <f t="shared" si="9"/>
         <v>0.9976245033516975</v>
       </c>
       <c r="AT100" s="6">
@@ -13108,14 +12943,13 @@
         <v>54.095789644444451</v>
       </c>
       <c r="AX100" s="2">
-        <f t="shared" si="10"/>
         <v>0.22079660827847811</v>
       </c>
       <c r="AY100" s="6">
         <v>0.38222605694564271</v>
       </c>
     </row>
-    <row r="101" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>98</v>
       </c>
@@ -13162,37 +12996,36 @@
         <v>2</v>
       </c>
       <c r="T101" s="6">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="U101" s="6">
+        <v>2</v>
+      </c>
+      <c r="V101" s="6">
+        <v>7</v>
+      </c>
+      <c r="W101" s="6">
+        <v>58.1</v>
+      </c>
+      <c r="X101" s="6">
+        <v>16.996741162534342</v>
+      </c>
+      <c r="AM101" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN101" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO101" s="6">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="U101" s="6">
-        <v>2</v>
-      </c>
-      <c r="V101" s="6">
-        <v>7</v>
-      </c>
-      <c r="W101" s="6">
-        <v>58.1</v>
-      </c>
-      <c r="X101" s="6">
-        <v>16.996741162534342</v>
-      </c>
-      <c r="AM101" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN101" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO101" s="6">
-        <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
       <c r="AP101" s="6">
         <v>0.97291019819887481</v>
       </c>
       <c r="AS101" s="6">
-        <f t="shared" si="9"/>
         <v>0.97291019819887481</v>
       </c>
       <c r="AT101" s="6">
@@ -13206,11 +13039,10 @@
         <v>98.751066154324533</v>
       </c>
       <c r="AX101" s="2">
-        <f t="shared" si="10"/>
         <v>0.36497267416294993</v>
       </c>
     </row>
-    <row r="102" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>99</v>
       </c>
@@ -13257,37 +13089,36 @@
         <v>2</v>
       </c>
       <c r="T102" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="U102" s="6">
+        <v>5</v>
+      </c>
+      <c r="V102" s="6">
+        <v>10</v>
+      </c>
+      <c r="W102" s="6">
+        <v>106.46000000000001</v>
+      </c>
+      <c r="X102" s="6">
+        <v>26.488901940201846</v>
+      </c>
+      <c r="AM102" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN102" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO102" s="6">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="U102" s="6">
-        <v>5</v>
-      </c>
-      <c r="V102" s="6">
-        <v>10</v>
-      </c>
-      <c r="W102" s="6">
-        <v>106.46000000000001</v>
-      </c>
-      <c r="X102" s="6">
-        <v>26.488901940201846</v>
-      </c>
-      <c r="AM102" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN102" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO102" s="6">
-        <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
       <c r="AP102" s="6">
         <v>0.61745692168302668</v>
       </c>
       <c r="AS102" s="6">
-        <f t="shared" si="9"/>
         <v>0.61745692168302668</v>
       </c>
       <c r="AT102" s="6">
@@ -13303,14 +13134,13 @@
         <v>282.00085005538887</v>
       </c>
       <c r="AX102" s="2">
-        <f t="shared" si="10"/>
         <v>0.53216695826043492</v>
       </c>
       <c r="AY102" s="6">
         <v>0.37904228855721395</v>
       </c>
     </row>
-    <row r="103" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>266</v>
       </c>
@@ -13357,37 +13187,36 @@
         <v>2</v>
       </c>
       <c r="T103" s="6">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="U103" s="6">
+        <v>2</v>
+      </c>
+      <c r="V103" s="6">
+        <v>11</v>
+      </c>
+      <c r="W103" s="6">
+        <v>74.77</v>
+      </c>
+      <c r="X103" s="6">
+        <v>27.988509377503501</v>
+      </c>
+      <c r="AM103" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN103" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO103" s="6">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="U103" s="6">
-        <v>2</v>
-      </c>
-      <c r="V103" s="6">
-        <v>11</v>
-      </c>
-      <c r="W103" s="6">
-        <v>74.77</v>
-      </c>
-      <c r="X103" s="6">
-        <v>27.988509377503501</v>
-      </c>
-      <c r="AM103" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN103" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO103" s="6">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
       <c r="AP103" s="6">
         <v>1</v>
       </c>
       <c r="AS103" s="6">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AT103" s="6">
@@ -13401,14 +13230,13 @@
         <v>209.27008461559367</v>
       </c>
       <c r="AX103" s="2">
-        <f t="shared" si="10"/>
         <v>0.36326094349706067</v>
       </c>
       <c r="AY103" s="6">
         <v>0.3242068665797479</v>
       </c>
     </row>
-    <row r="104" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>100</v>
       </c>
@@ -13455,7 +13283,7 @@
         <v>4</v>
       </c>
       <c r="T104" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="U104" s="6">
@@ -13477,7 +13305,7 @@
         <v>2</v>
       </c>
       <c r="AA104" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="AB104" s="6">
@@ -13496,11 +13324,11 @@
         <v>314</v>
       </c>
       <c r="AN104" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AO104" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="AP104" s="6">
@@ -13510,7 +13338,6 @@
         <v>0.61631611043376333</v>
       </c>
       <c r="AS104" s="6">
-        <f t="shared" si="9"/>
         <v>0.69960786039603484</v>
       </c>
       <c r="AT104" s="6">
@@ -13526,11 +13353,10 @@
         <v>515.9647148460939</v>
       </c>
       <c r="AX104" s="2">
-        <f t="shared" si="10"/>
         <v>0.40720104878733965</v>
       </c>
     </row>
-    <row r="105" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>101</v>
       </c>
@@ -13589,37 +13415,36 @@
         <v>2</v>
       </c>
       <c r="T105" s="6">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="U105" s="6">
+        <v>1</v>
+      </c>
+      <c r="V105" s="6">
+        <v>5</v>
+      </c>
+      <c r="W105" s="6">
+        <v>35.11</v>
+      </c>
+      <c r="X105" s="6">
+        <v>10.923299264545177</v>
+      </c>
+      <c r="AM105" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN105" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO105" s="6">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="U105" s="6">
-        <v>1</v>
-      </c>
-      <c r="V105" s="6">
-        <v>5</v>
-      </c>
-      <c r="W105" s="6">
-        <v>35.11</v>
-      </c>
-      <c r="X105" s="6">
-        <v>10.923299264545177</v>
-      </c>
-      <c r="AM105" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN105" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO105" s="6">
-        <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
       <c r="AP105" s="6">
         <v>0.59853694600247542</v>
       </c>
       <c r="AS105" s="6">
-        <f t="shared" si="9"/>
         <v>0.59853694600247542</v>
       </c>
       <c r="AT105" s="6">
@@ -13635,14 +13460,13 @@
         <v>38.351703717818118</v>
       </c>
       <c r="AX105" s="2">
-        <f t="shared" si="10"/>
         <v>0.22669163223140495</v>
       </c>
       <c r="AY105" s="6">
         <v>0.46245059288537549</v>
       </c>
     </row>
-    <row r="106" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>102</v>
       </c>
@@ -13689,7 +13513,7 @@
         <v>3</v>
       </c>
       <c r="T106" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="U106" s="6">
@@ -13711,7 +13535,7 @@
         <v>3</v>
       </c>
       <c r="AA106" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="AB106" s="6">
@@ -13730,11 +13554,11 @@
         <v>324</v>
       </c>
       <c r="AN106" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AO106" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="AP106" s="6">
@@ -13744,7 +13568,6 @@
         <v>0.66530585166717338</v>
       </c>
       <c r="AS106" s="6">
-        <f t="shared" si="9"/>
         <v>0.65294686239944544</v>
       </c>
       <c r="AT106" s="6">
@@ -13760,11 +13583,10 @@
         <v>253.86574010090439</v>
       </c>
       <c r="AX106" s="2">
-        <f t="shared" si="10"/>
         <v>0.45102734005234146</v>
       </c>
     </row>
-    <row r="107" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>103</v>
       </c>
@@ -13811,7 +13633,7 @@
         <v>2</v>
       </c>
       <c r="T107" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="U107" s="6">
@@ -13833,7 +13655,7 @@
         <v>3</v>
       </c>
       <c r="AA107" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="AB107" s="6">
@@ -13852,11 +13674,11 @@
         <v>314</v>
       </c>
       <c r="AN107" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
       <c r="AO107" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="AP107" s="6">
@@ -13866,7 +13688,6 @@
         <v>1</v>
       </c>
       <c r="AS107" s="6">
-        <f t="shared" si="9"/>
         <v>0.99945855566926234</v>
       </c>
       <c r="AT107" s="6">
@@ -13880,11 +13701,10 @@
         <v>285.94976276225452</v>
       </c>
       <c r="AX107" s="2">
-        <f t="shared" si="10"/>
         <v>0.49172017573504567</v>
       </c>
     </row>
-    <row r="108" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>104</v>
       </c>
@@ -13943,37 +13763,36 @@
         <v>2</v>
       </c>
       <c r="T108" s="6">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="U108" s="6">
+        <v>2</v>
+      </c>
+      <c r="V108" s="6">
+        <v>8</v>
+      </c>
+      <c r="W108" s="6">
+        <v>48.72</v>
+      </c>
+      <c r="X108" s="6">
+        <v>15.975377814185748</v>
+      </c>
+      <c r="AM108" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN108" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO108" s="6">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="U108" s="6">
-        <v>2</v>
-      </c>
-      <c r="V108" s="6">
-        <v>8</v>
-      </c>
-      <c r="W108" s="6">
-        <v>48.72</v>
-      </c>
-      <c r="X108" s="6">
-        <v>15.975377814185748</v>
-      </c>
-      <c r="AM108" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN108" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO108" s="6">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
       <c r="AP108" s="6">
         <v>0.80683726334271455</v>
       </c>
       <c r="AS108" s="6">
-        <f t="shared" si="9"/>
         <v>0.80683726334271455</v>
       </c>
       <c r="AT108" s="6">
@@ -13989,14 +13808,13 @@
         <v>77.83204071071296</v>
       </c>
       <c r="AX108" s="2">
-        <f t="shared" si="10"/>
         <v>0.36163895486935865</v>
       </c>
       <c r="AY108" s="6">
         <v>0.9723247232472324</v>
       </c>
     </row>
-    <row r="109" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>105</v>
       </c>
@@ -14055,37 +13873,36 @@
         <v>2</v>
       </c>
       <c r="T109" s="6">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="U109" s="6">
+        <v>0</v>
+      </c>
+      <c r="V109" s="6">
+        <v>9</v>
+      </c>
+      <c r="W109" s="6">
+        <v>48.879999999999995</v>
+      </c>
+      <c r="X109" s="6">
+        <v>9.8014294725450366</v>
+      </c>
+      <c r="AM109" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN109" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO109" s="6">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="U109" s="6">
-        <v>0</v>
-      </c>
-      <c r="V109" s="6">
-        <v>9</v>
-      </c>
-      <c r="W109" s="6">
-        <v>48.879999999999995</v>
-      </c>
-      <c r="X109" s="6">
-        <v>9.8014294725450366</v>
-      </c>
-      <c r="AM109" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN109" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO109" s="6">
-        <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
       <c r="AP109" s="6">
         <v>0.49302965153647066</v>
       </c>
       <c r="AS109" s="6">
-        <f t="shared" si="9"/>
         <v>0.49302965153647066</v>
       </c>
       <c r="AT109" s="6">
@@ -14101,14 +13918,13 @@
         <v>47.909387261800134</v>
       </c>
       <c r="AX109" s="2">
-        <f t="shared" si="10"/>
         <v>0.34483245149911812</v>
       </c>
       <c r="AY109" s="6">
         <v>0.39824945295404812</v>
       </c>
     </row>
-    <row r="110" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>106</v>
       </c>
@@ -14155,7 +13971,7 @@
         <v>3</v>
       </c>
       <c r="T110" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="U110" s="6">
@@ -14177,7 +13993,7 @@
         <v>3</v>
       </c>
       <c r="AA110" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="AB110" s="6">
@@ -14196,11 +14012,11 @@
         <v>315</v>
       </c>
       <c r="AN110" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AO110" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="AP110" s="6">
@@ -14210,7 +14026,6 @@
         <v>0.66365077433959341</v>
       </c>
       <c r="AS110" s="6">
-        <f t="shared" si="9"/>
         <v>0.82561062813280639</v>
       </c>
       <c r="AT110" s="6">
@@ -14224,11 +14039,10 @@
         <v>249.10848960382532</v>
       </c>
       <c r="AX110" s="2">
-        <f t="shared" si="10"/>
         <v>0.52398928397467115</v>
       </c>
     </row>
-    <row r="111" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>107</v>
       </c>
@@ -14275,37 +14089,36 @@
         <v>3</v>
       </c>
       <c r="T111" s="6">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="U111" s="6">
+        <v>5</v>
+      </c>
+      <c r="V111" s="6">
+        <v>17</v>
+      </c>
+      <c r="W111" s="6">
+        <v>59.650000000000006</v>
+      </c>
+      <c r="X111" s="6">
+        <v>17.697223598044278</v>
+      </c>
+      <c r="AM111" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN111" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO111" s="6">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="U111" s="6">
-        <v>5</v>
-      </c>
-      <c r="V111" s="6">
-        <v>17</v>
-      </c>
-      <c r="W111" s="6">
-        <v>59.650000000000006</v>
-      </c>
-      <c r="X111" s="6">
-        <v>17.697223598044278</v>
-      </c>
-      <c r="AM111" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN111" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO111" s="6">
-        <f t="shared" si="8"/>
-        <v>22</v>
-      </c>
       <c r="AP111" s="6">
         <v>0.99494888207834042</v>
       </c>
       <c r="AS111" s="6">
-        <f t="shared" si="9"/>
         <v>0.99494888207834042</v>
       </c>
       <c r="AT111" s="6">
@@ -14319,11 +14132,10 @@
         <v>105.56393876233412</v>
       </c>
       <c r="AX111" s="2">
-        <f t="shared" si="10"/>
         <v>0.40484593457309626</v>
       </c>
     </row>
-    <row r="112" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>108</v>
       </c>
@@ -14370,37 +14182,36 @@
         <v>3</v>
       </c>
       <c r="T112" s="6">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="U112" s="6">
+        <v>2</v>
+      </c>
+      <c r="V112" s="6">
+        <v>21</v>
+      </c>
+      <c r="W112" s="6">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="X112" s="6">
+        <v>24.087010291486969</v>
+      </c>
+      <c r="AM112" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN112" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO112" s="6">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="U112" s="6">
-        <v>2</v>
-      </c>
-      <c r="V112" s="6">
-        <v>21</v>
-      </c>
-      <c r="W112" s="6">
-        <v>36.590000000000003</v>
-      </c>
-      <c r="X112" s="6">
-        <v>24.087010291486969</v>
-      </c>
-      <c r="AM112" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN112" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO112" s="6">
-        <f t="shared" si="8"/>
-        <v>23</v>
-      </c>
       <c r="AP112" s="6">
         <v>0.97914675981654342</v>
       </c>
       <c r="AS112" s="6">
-        <f t="shared" si="9"/>
         <v>0.97914675981654342</v>
       </c>
       <c r="AT112" s="6">
@@ -14414,11 +14225,10 @@
         <v>88.134370656550828</v>
       </c>
       <c r="AX112" s="2">
-        <f t="shared" si="10"/>
         <v>0.27257151370679383</v>
       </c>
     </row>
-    <row r="113" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>109</v>
       </c>
@@ -14465,37 +14275,36 @@
         <v>2</v>
       </c>
       <c r="T113" s="6">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="U113" s="6">
+        <v>6</v>
+      </c>
+      <c r="V113" s="6">
+        <v>8</v>
+      </c>
+      <c r="W113" s="6">
+        <v>30.299999999999997</v>
+      </c>
+      <c r="X113" s="6">
+        <v>9.3809786483741231</v>
+      </c>
+      <c r="AM113" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN113" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO113" s="6">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="U113" s="6">
-        <v>6</v>
-      </c>
-      <c r="V113" s="6">
-        <v>8</v>
-      </c>
-      <c r="W113" s="6">
-        <v>30.299999999999997</v>
-      </c>
-      <c r="X113" s="6">
-        <v>9.3809786483741231</v>
-      </c>
-      <c r="AM113" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN113" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO113" s="6">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
       <c r="AP113" s="6">
         <v>0.59904078214394141</v>
       </c>
       <c r="AS113" s="6">
-        <f t="shared" si="9"/>
         <v>0.59904078214394141</v>
       </c>
       <c r="AT113" s="6">
@@ -14511,14 +14320,13 @@
         <v>28.424365304573591</v>
       </c>
       <c r="AX113" s="2">
-        <f t="shared" si="10"/>
         <v>0.22462747423826823</v>
       </c>
       <c r="AY113" s="6">
         <v>9.2432432432432432E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>110</v>
       </c>
@@ -14565,7 +14373,7 @@
         <v>3</v>
       </c>
       <c r="T114" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="U114" s="6">
@@ -14587,7 +14395,7 @@
         <v>3</v>
       </c>
       <c r="AA114" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="AB114" s="6">
@@ -14606,11 +14414,11 @@
         <v>314</v>
       </c>
       <c r="AN114" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AO114" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="AP114" s="6">
@@ -14620,7 +14428,6 @@
         <v>1</v>
       </c>
       <c r="AS114" s="6">
-        <f t="shared" si="9"/>
         <v>0.8543767340142534</v>
       </c>
       <c r="AT114" s="6">
@@ -14634,14 +14441,13 @@
         <v>148.50111059897185</v>
       </c>
       <c r="AX114" s="2">
-        <f t="shared" si="10"/>
         <v>0.76703368581707199</v>
       </c>
       <c r="AY114" s="6">
         <v>0.86842105263157898</v>
       </c>
     </row>
-    <row r="115" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
         <v>111</v>
       </c>
@@ -14688,37 +14494,36 @@
         <v>2</v>
       </c>
       <c r="T115" s="6">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="U115" s="6">
+        <v>2</v>
+      </c>
+      <c r="V115" s="6">
+        <v>11</v>
+      </c>
+      <c r="W115" s="6">
+        <v>32.619999999999997</v>
+      </c>
+      <c r="X115" s="6">
+        <v>13.229550300040245</v>
+      </c>
+      <c r="AM115" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN115" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO115" s="6">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="U115" s="6">
-        <v>2</v>
-      </c>
-      <c r="V115" s="6">
-        <v>11</v>
-      </c>
-      <c r="W115" s="6">
-        <v>32.619999999999997</v>
-      </c>
-      <c r="X115" s="6">
-        <v>13.229550300040245</v>
-      </c>
-      <c r="AM115" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN115" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO115" s="6">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
       <c r="AP115" s="6">
         <v>0.86467649019870874</v>
       </c>
       <c r="AS115" s="6">
-        <f t="shared" si="9"/>
         <v>0.86467649019870874</v>
       </c>
       <c r="AT115" s="6">
@@ -14734,14 +14539,13 @@
         <v>43.154793078731274</v>
       </c>
       <c r="AX115" s="2">
-        <f t="shared" si="10"/>
         <v>0.3341870709968241</v>
       </c>
       <c r="AY115" s="6">
         <v>4.9515058703420115E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>112</v>
       </c>
@@ -14788,37 +14592,36 @@
         <v>4</v>
       </c>
       <c r="T116" s="6">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="U116" s="6">
+        <v>5</v>
+      </c>
+      <c r="V116" s="6">
+        <v>21</v>
+      </c>
+      <c r="W116" s="6">
+        <v>45.7</v>
+      </c>
+      <c r="X116" s="6">
+        <v>16.932276742751501</v>
+      </c>
+      <c r="AM116" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AN116" s="6">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AO116" s="6">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="U116" s="6">
-        <v>5</v>
-      </c>
-      <c r="V116" s="6">
-        <v>21</v>
-      </c>
-      <c r="W116" s="6">
-        <v>45.7</v>
-      </c>
-      <c r="X116" s="6">
-        <v>16.932276742751501</v>
-      </c>
-      <c r="AM116" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="AN116" s="6">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="AO116" s="6">
-        <f t="shared" si="8"/>
-        <v>26</v>
-      </c>
       <c r="AP116" s="6">
         <v>0.99019162238312863</v>
       </c>
       <c r="AS116" s="6">
-        <f t="shared" si="9"/>
         <v>0.99019162238312863</v>
       </c>
       <c r="AT116" s="6">
@@ -14832,14 +14635,13 @@
         <v>77.380504714374368</v>
       </c>
       <c r="AX116" s="2">
-        <f t="shared" si="10"/>
         <v>0.48897924245666602</v>
       </c>
       <c r="AY116" s="6">
         <v>0.28636959370904325</v>
       </c>
     </row>
-    <row r="117" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
         <v>113</v>
       </c>
@@ -14898,7 +14700,7 @@
         <v>2</v>
       </c>
       <c r="T117" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="U117" s="6">
@@ -14920,7 +14722,7 @@
         <v>2</v>
       </c>
       <c r="AA117" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="AB117" s="6">
@@ -14939,11 +14741,11 @@
         <v>314</v>
       </c>
       <c r="AN117" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AO117" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="AP117" s="6">
@@ -14953,7 +14755,6 @@
         <v>0.5848860074375819</v>
       </c>
       <c r="AS117" s="6">
-        <f t="shared" si="9"/>
         <v>0.77090047312337251</v>
       </c>
       <c r="AT117" s="6">
@@ -14967,14 +14768,13 @@
         <v>308.73022147644826</v>
       </c>
       <c r="AX117" s="2">
-        <f t="shared" si="10"/>
         <v>0.54451514657094691</v>
       </c>
       <c r="AY117" s="6">
         <v>0.7728706624605679</v>
       </c>
     </row>
-    <row r="118" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
         <v>114</v>
       </c>
@@ -15033,37 +14833,36 @@
         <v>3</v>
       </c>
       <c r="T118" s="6">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="U118" s="6">
+        <v>3</v>
+      </c>
+      <c r="V118" s="6">
+        <v>16</v>
+      </c>
+      <c r="W118" s="6">
+        <v>41.76</v>
+      </c>
+      <c r="X118" s="6">
+        <v>14.185912974871849</v>
+      </c>
+      <c r="AM118" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN118" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO118" s="6">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="U118" s="6">
-        <v>3</v>
-      </c>
-      <c r="V118" s="6">
-        <v>16</v>
-      </c>
-      <c r="W118" s="6">
-        <v>41.76</v>
-      </c>
-      <c r="X118" s="6">
-        <v>14.185912974871849</v>
-      </c>
-      <c r="AM118" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN118" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO118" s="6">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
       <c r="AP118" s="6">
         <v>0.68332914137147627</v>
       </c>
       <c r="AS118" s="6">
-        <f t="shared" si="9"/>
         <v>0.68332914137147627</v>
       </c>
       <c r="AT118" s="6">
@@ -15079,14 +14878,13 @@
         <v>59.240372583064833</v>
       </c>
       <c r="AX118" s="2">
-        <f t="shared" si="10"/>
         <v>0.23800296363843609</v>
       </c>
       <c r="AY118" s="6">
         <v>0.78673437004125668</v>
       </c>
     </row>
-    <row r="119" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
         <v>115</v>
       </c>
@@ -15145,37 +14943,36 @@
         <v>2</v>
       </c>
       <c r="T119" s="6">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="U119" s="6">
+        <v>3</v>
+      </c>
+      <c r="V119" s="6">
+        <v>8</v>
+      </c>
+      <c r="W119" s="6">
+        <v>45.11</v>
+      </c>
+      <c r="X119" s="6">
+        <v>6.6488813318914346</v>
+      </c>
+      <c r="AM119" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN119" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO119" s="6">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="U119" s="6">
-        <v>3</v>
-      </c>
-      <c r="V119" s="6">
-        <v>8</v>
-      </c>
-      <c r="W119" s="6">
-        <v>45.11</v>
-      </c>
-      <c r="X119" s="6">
-        <v>6.6488813318914346</v>
-      </c>
-      <c r="AM119" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN119" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO119" s="6">
-        <f t="shared" si="8"/>
-        <v>11</v>
-      </c>
       <c r="AP119" s="6">
         <v>0.28137458027471157</v>
       </c>
       <c r="AS119" s="6">
-        <f t="shared" si="9"/>
         <v>0.28137458027471157</v>
       </c>
       <c r="AT119" s="6">
@@ -15191,14 +14988,13 @@
         <v>29.993103688162261</v>
       </c>
       <c r="AX119" s="2">
-        <f t="shared" si="10"/>
         <v>0.26668637304167903</v>
       </c>
       <c r="AY119" s="6">
         <v>0.11484879374787632</v>
       </c>
     </row>
-    <row r="120" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>116</v>
       </c>
@@ -15257,7 +15053,7 @@
         <v>2</v>
       </c>
       <c r="T120" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="U120" s="6">
@@ -15279,7 +15075,7 @@
         <v>2</v>
       </c>
       <c r="AA120" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="AB120" s="6">
@@ -15298,11 +15094,11 @@
         <v>314</v>
       </c>
       <c r="AN120" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AO120" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="AP120" s="6">
@@ -15312,7 +15108,6 @@
         <v>0.47652808117708012</v>
       </c>
       <c r="AS120" s="6">
-        <f t="shared" si="9"/>
         <v>0.42685289119661479</v>
       </c>
       <c r="AT120" s="6">
@@ -15328,14 +15123,13 @@
         <v>133.87660412449796</v>
       </c>
       <c r="AX120" s="2">
-        <f t="shared" si="10"/>
         <v>0.47181276021154495</v>
       </c>
       <c r="AY120" s="6">
         <v>0.71221281741233389</v>
       </c>
     </row>
-    <row r="121" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>117</v>
       </c>
@@ -15394,37 +15188,36 @@
         <v>3</v>
       </c>
       <c r="T121" s="6">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="U121" s="6">
+        <v>4</v>
+      </c>
+      <c r="V121" s="6">
+        <v>27</v>
+      </c>
+      <c r="W121" s="6">
+        <v>81.010000000000005</v>
+      </c>
+      <c r="X121" s="6">
+        <v>18.484892444644593</v>
+      </c>
+      <c r="AM121" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN121" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO121" s="6">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="U121" s="6">
-        <v>4</v>
-      </c>
-      <c r="V121" s="6">
-        <v>27</v>
-      </c>
-      <c r="W121" s="6">
-        <v>81.010000000000005</v>
-      </c>
-      <c r="X121" s="6">
-        <v>18.484892444644593</v>
-      </c>
-      <c r="AM121" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN121" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO121" s="6">
-        <f t="shared" si="8"/>
-        <v>31</v>
-      </c>
       <c r="AP121" s="6">
         <v>0.65087649452973928</v>
       </c>
       <c r="AS121" s="6">
-        <f t="shared" si="9"/>
         <v>0.65087649452973928</v>
       </c>
       <c r="AT121" s="6">
@@ -15440,14 +15233,13 @@
         <v>149.74611369406585</v>
       </c>
       <c r="AX121" s="2">
-        <f t="shared" si="10"/>
         <v>0.39971382049637344</v>
       </c>
       <c r="AY121" s="6">
         <v>0.17662037037037034</v>
       </c>
     </row>
-    <row r="122" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
         <v>118</v>
       </c>
@@ -15494,37 +15286,36 @@
         <v>4</v>
       </c>
       <c r="T122" s="6">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="U122" s="6">
+        <v>7</v>
+      </c>
+      <c r="V122" s="6">
+        <v>37</v>
+      </c>
+      <c r="W122" s="6">
+        <v>142.27799999999999</v>
+      </c>
+      <c r="X122" s="6">
+        <v>28.650890488652543</v>
+      </c>
+      <c r="AM122" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN122" s="6">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AO122" s="6">
         <f t="shared" si="6"/>
         <v>44</v>
       </c>
-      <c r="U122" s="6">
-        <v>7</v>
-      </c>
-      <c r="V122" s="6">
-        <v>37</v>
-      </c>
-      <c r="W122" s="6">
-        <v>142.27799999999999</v>
-      </c>
-      <c r="X122" s="6">
-        <v>28.650890488652543</v>
-      </c>
-      <c r="AM122" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN122" s="6">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="AO122" s="6">
-        <f t="shared" si="8"/>
-        <v>44</v>
-      </c>
       <c r="AP122" s="6">
         <v>0.76894499432776553</v>
       </c>
       <c r="AS122" s="6">
-        <f t="shared" si="9"/>
         <v>0.76894499432776553</v>
       </c>
       <c r="AT122" s="6">
@@ -15540,11 +15331,10 @@
         <v>407.63913969445059</v>
       </c>
       <c r="AX122" s="2">
-        <f t="shared" si="10"/>
         <v>0.74172661870503598</v>
       </c>
     </row>
-    <row r="123" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>119</v>
       </c>
@@ -15603,37 +15393,36 @@
         <v>3</v>
       </c>
       <c r="T123" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="U123" s="6">
+        <v>2</v>
+      </c>
+      <c r="V123" s="6">
+        <v>13</v>
+      </c>
+      <c r="W123" s="6">
+        <v>39.42</v>
+      </c>
+      <c r="X123" s="6">
+        <v>12.043187501813902</v>
+      </c>
+      <c r="AM123" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AN123" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO123" s="6">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="U123" s="6">
-        <v>2</v>
-      </c>
-      <c r="V123" s="6">
-        <v>13</v>
-      </c>
-      <c r="W123" s="6">
-        <v>39.42</v>
-      </c>
-      <c r="X123" s="6">
-        <v>12.043187501813902</v>
-      </c>
-      <c r="AM123" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="AN123" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO123" s="6">
-        <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
       <c r="AP123" s="6">
         <v>0.42109047209139516</v>
       </c>
       <c r="AS123" s="6">
-        <f t="shared" si="9"/>
         <v>0.42109047209139516</v>
       </c>
       <c r="AT123" s="6">
@@ -15649,11 +15438,10 @@
         <v>47.474245132150408</v>
       </c>
       <c r="AX123" s="2">
-        <f t="shared" si="10"/>
         <v>0.25507959104438982</v>
       </c>
     </row>
-    <row r="124" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>120</v>
       </c>
@@ -15700,37 +15488,36 @@
         <v>3</v>
       </c>
       <c r="T124" s="6">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="U124" s="6">
+        <v>4</v>
+      </c>
+      <c r="V124" s="6">
+        <v>12</v>
+      </c>
+      <c r="W124" s="6">
+        <v>52.47</v>
+      </c>
+      <c r="X124" s="6">
+        <v>25.249537227980749</v>
+      </c>
+      <c r="AM124" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN124" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO124" s="6">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="U124" s="6">
-        <v>4</v>
-      </c>
-      <c r="V124" s="6">
-        <v>12</v>
-      </c>
-      <c r="W124" s="6">
-        <v>52.47</v>
-      </c>
-      <c r="X124" s="6">
-        <v>25.249537227980749</v>
-      </c>
-      <c r="AM124" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN124" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO124" s="6">
-        <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
       <c r="AP124" s="6">
         <v>0.99800542403085957</v>
       </c>
       <c r="AS124" s="6">
-        <f t="shared" si="9"/>
         <v>0.99800542403085957</v>
       </c>
       <c r="AT124" s="6">
@@ -15744,14 +15531,13 @@
         <v>132.48432183521498</v>
       </c>
       <c r="AX124" s="2">
-        <f t="shared" si="10"/>
         <v>0.33037400831129582</v>
       </c>
       <c r="AY124" s="6">
         <v>0.22850729517396184</v>
       </c>
     </row>
-    <row r="125" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
         <v>267</v>
       </c>
@@ -15798,37 +15584,36 @@
         <v>2</v>
       </c>
       <c r="T125" s="6">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="U125" s="6">
+        <v>0</v>
+      </c>
+      <c r="V125" s="6">
+        <v>13</v>
+      </c>
+      <c r="W125" s="6">
+        <v>50.91</v>
+      </c>
+      <c r="X125" s="6">
+        <v>8.0598872825196981</v>
+      </c>
+      <c r="AM125" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN125" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AO125" s="6">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="U125" s="6">
-        <v>0</v>
-      </c>
-      <c r="V125" s="6">
-        <v>13</v>
-      </c>
-      <c r="W125" s="6">
-        <v>50.91</v>
-      </c>
-      <c r="X125" s="6">
-        <v>8.0598872825196981</v>
-      </c>
-      <c r="AM125" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN125" s="6">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AO125" s="6">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
       <c r="AP125" s="6">
         <v>0.38000411515887306</v>
       </c>
       <c r="AS125" s="6">
-        <f t="shared" si="9"/>
         <v>0.38000411515887306</v>
       </c>
       <c r="AT125" s="6">
@@ -15844,14 +15629,13 @@
         <v>41.032886155307779</v>
       </c>
       <c r="AX125" s="2">
-        <f t="shared" si="10"/>
         <v>0.51533556027938054</v>
       </c>
       <c r="AY125" s="6">
         <v>0.12589928057553956</v>
       </c>
     </row>
-    <row r="126" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>121</v>
       </c>
@@ -15898,37 +15682,36 @@
         <v>3</v>
       </c>
       <c r="T126" s="6">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="U126" s="6">
+        <v>2</v>
+      </c>
+      <c r="V126" s="6">
+        <v>17</v>
+      </c>
+      <c r="W126" s="6">
+        <v>68.66</v>
+      </c>
+      <c r="X126" s="6">
+        <v>14.318826673198785</v>
+      </c>
+      <c r="AM126" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AN126" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO126" s="6">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="U126" s="6">
-        <v>2</v>
-      </c>
-      <c r="V126" s="6">
-        <v>17</v>
-      </c>
-      <c r="W126" s="6">
-        <v>68.66</v>
-      </c>
-      <c r="X126" s="6">
-        <v>14.318826673198785</v>
-      </c>
-      <c r="AM126" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="AN126" s="6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AO126" s="6">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
       <c r="AP126" s="6">
         <v>0.4446840581738753</v>
       </c>
       <c r="AS126" s="6">
-        <f t="shared" si="9"/>
         <v>0.4446840581738753</v>
       </c>
       <c r="AT126" s="6">
@@ -15944,14 +15727,13 @@
         <v>98.313063938182864</v>
       </c>
       <c r="AX126" s="2">
-        <f t="shared" si="10"/>
         <v>0.38034566807001996</v>
       </c>
       <c r="AY126" s="6">
         <v>0.10566396953831508</v>
       </c>
     </row>
-    <row r="127" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
         <v>122</v>
       </c>
@@ -15998,7 +15780,7 @@
         <v>3</v>
       </c>
       <c r="T127" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="U127" s="6">
@@ -16020,7 +15802,7 @@
         <v>2</v>
       </c>
       <c r="AA127" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="AB127" s="6">
@@ -16061,11 +15843,11 @@
         <v>315</v>
       </c>
       <c r="AN127" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2.3333333333333335</v>
       </c>
       <c r="AO127" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="AP127" s="6">
@@ -16078,7 +15860,6 @@
         <v>0.75892130091677235</v>
       </c>
       <c r="AS127" s="6">
-        <f t="shared" si="9"/>
         <v>0.77543466226014213</v>
       </c>
       <c r="AT127" s="6">
@@ -16094,14 +15875,13 @@
         <v>481.85432369379004</v>
       </c>
       <c r="AX127" s="2">
-        <f t="shared" si="10"/>
         <v>0.62094732291730992</v>
       </c>
       <c r="AY127" s="6">
         <v>0.86737872719181131</v>
       </c>
     </row>
-    <row r="128" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
         <v>123</v>
       </c>
@@ -16160,7 +15940,7 @@
         <v>3</v>
       </c>
       <c r="T128" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="U128" s="6">
@@ -16182,7 +15962,7 @@
         <v>3</v>
       </c>
       <c r="AA128" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="AB128" s="6">
@@ -16204,7 +15984,7 @@
         <v>4</v>
       </c>
       <c r="AH128" s="6">
-        <f t="shared" ref="AH128:AH155" si="12">AI128+AJ128</f>
+        <f t="shared" ref="AH128:AH155" si="8">AI128+AJ128</f>
         <v>17</v>
       </c>
       <c r="AI128" s="6">
@@ -16223,11 +16003,11 @@
         <v>314</v>
       </c>
       <c r="AN128" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3.3333333333333335</v>
       </c>
       <c r="AO128" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>43</v>
       </c>
       <c r="AP128" s="6">
@@ -16240,7 +16020,6 @@
         <v>0.92695814902765339</v>
       </c>
       <c r="AS128" s="6">
-        <f t="shared" si="9"/>
         <v>0.88632139613932048</v>
       </c>
       <c r="AT128" s="6">
@@ -16254,14 +16033,13 @@
         <v>1220.6344702954843</v>
       </c>
       <c r="AX128" s="2">
-        <f t="shared" si="10"/>
         <v>0.87027729146665156</v>
       </c>
       <c r="AY128" s="6">
         <v>0.62002840909090917</v>
       </c>
     </row>
-    <row r="129" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
         <v>124</v>
       </c>
@@ -16320,7 +16098,7 @@
         <v>4</v>
       </c>
       <c r="T129" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="U129" s="6">
@@ -16342,7 +16120,7 @@
         <v>4</v>
       </c>
       <c r="AA129" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="AB129" s="6">
@@ -16364,7 +16142,7 @@
         <v>4</v>
       </c>
       <c r="AH129" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="AI129" s="6">
@@ -16383,265 +16161,261 @@
         <v>324</v>
       </c>
       <c r="AN129" s="6">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AO129" s="6">
+        <f t="shared" si="6"/>
+        <v>65</v>
+      </c>
+      <c r="AP129" s="6">
+        <v>0.90184983002642038</v>
+      </c>
+      <c r="AQ129" s="6">
+        <v>0.35241276691592183</v>
+      </c>
+      <c r="AR129" s="6">
+        <v>0.69323347179402672</v>
+      </c>
+      <c r="AS129" s="6">
+        <v>0.64916535624545635</v>
+      </c>
+      <c r="AT129" s="6">
+        <v>72.8888888888889</v>
+      </c>
+      <c r="AU129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="AV129" s="2">
+        <v>0.7929367016243033</v>
+      </c>
+      <c r="AW129" s="2">
+        <v>590.27891112342115</v>
+      </c>
+      <c r="AX129" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A130" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G130" s="6">
+        <v>0</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="I130" s="12">
+        <v>72.31</v>
+      </c>
+      <c r="J130" s="12">
+        <v>71.89</v>
+      </c>
+      <c r="K130" s="12">
+        <v>24.3</v>
+      </c>
+      <c r="L130" s="12">
+        <v>150</v>
+      </c>
+      <c r="M130" s="12">
+        <v>220.98000000000002</v>
+      </c>
+      <c r="R130" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="S130" s="6">
+        <v>3</v>
+      </c>
+      <c r="T130" s="6">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="U130" s="6">
+        <v>4</v>
+      </c>
+      <c r="V130" s="6">
+        <v>23</v>
+      </c>
+      <c r="W130" s="6">
+        <v>81.929999999999993</v>
+      </c>
+      <c r="X130" s="6">
+        <v>22.046368726195382</v>
+      </c>
+      <c r="Y130" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="Z130" s="6">
+        <v>3</v>
+      </c>
+      <c r="AA130" s="6">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="AB130" s="6">
+        <v>5</v>
+      </c>
+      <c r="AC130" s="6">
+        <v>19</v>
+      </c>
+      <c r="AD130" s="6">
+        <v>76.11</v>
+      </c>
+      <c r="AE130" s="6">
+        <v>18.246566222391351</v>
+      </c>
+      <c r="AF130" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AG130" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH130" s="6">
+        <f t="shared" si="8"/>
+        <v>26</v>
+      </c>
+      <c r="AI130" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ130" s="6">
+        <v>23</v>
+      </c>
+      <c r="AK130" s="6">
+        <v>71.61</v>
+      </c>
+      <c r="AL130" s="6">
+        <v>21.937802575723325</v>
+      </c>
+      <c r="AM130" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN130" s="6">
+        <f t="shared" si="5"/>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="AO130" s="6">
+        <f t="shared" si="6"/>
+        <v>77</v>
+      </c>
+      <c r="AP130" s="6">
+        <v>0.90725797227141491</v>
+      </c>
+      <c r="AQ130" s="6">
+        <v>0.75088749886384154</v>
+      </c>
+      <c r="AR130" s="6">
+        <v>0.90279022945363474</v>
+      </c>
+      <c r="AS130" s="6">
+        <v>0.8536452335296304</v>
+      </c>
+      <c r="AT130" s="6">
+        <v>63.788888888888891</v>
+      </c>
+      <c r="AU130" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="AV130" s="2">
+        <v>0.77365080998634783</v>
+      </c>
+      <c r="AW130" s="2">
+        <v>1429.1288872457803</v>
+      </c>
+      <c r="AX130" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY130" s="6">
+        <v>8.1050064553148768E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A131" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G131" s="6">
+        <v>0</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="I131" s="12">
+        <v>76.510000000000005</v>
+      </c>
+      <c r="J131" s="12">
+        <v>54.85</v>
+      </c>
+      <c r="K131" s="12">
+        <v>27.66</v>
+      </c>
+      <c r="L131" s="12">
+        <v>150.9</v>
+      </c>
+      <c r="M131" s="12">
+        <v>213.77</v>
+      </c>
+      <c r="R131" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="S131" s="6">
+        <v>3</v>
+      </c>
+      <c r="T131" s="6">
+        <f t="shared" ref="T131:T167" si="9">U131+V131</f>
+        <v>14</v>
+      </c>
+      <c r="U131" s="6">
+        <v>2</v>
+      </c>
+      <c r="V131" s="6">
+        <v>12</v>
+      </c>
+      <c r="W131" s="6">
+        <v>80.490000000000009</v>
+      </c>
+      <c r="X131" s="6">
+        <v>27.508686717113946</v>
+      </c>
+      <c r="Y131" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="Z131" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA131" s="6">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="AO129" s="6">
-        <f t="shared" si="8"/>
-        <v>65</v>
-      </c>
-      <c r="AP129" s="6">
-        <v>0.90184983002642038</v>
-      </c>
-      <c r="AQ129" s="6">
-        <v>0.35241276691592183</v>
-      </c>
-      <c r="AR129" s="6">
-        <v>0.69323347179402672</v>
-      </c>
-      <c r="AS129" s="6">
-        <f t="shared" si="9"/>
-        <v>0.64916535624545635</v>
-      </c>
-      <c r="AT129" s="6">
-        <v>72.8888888888889</v>
-      </c>
-      <c r="AU129" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="AV129" s="2">
-        <v>0.7929367016243033</v>
-      </c>
-      <c r="AW129" s="2">
-        <v>590.27891112342115</v>
-      </c>
-      <c r="AX129" s="2">
-        <f t="shared" si="10"/>
-        <v>1.0265165543293091</v>
-      </c>
-    </row>
-    <row r="130" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A130" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G130" s="6">
-        <v>0</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="I130" s="12">
-        <v>72.31</v>
-      </c>
-      <c r="J130" s="12">
-        <v>71.89</v>
-      </c>
-      <c r="K130" s="12">
-        <v>24.3</v>
-      </c>
-      <c r="L130" s="12">
-        <v>150</v>
-      </c>
-      <c r="M130" s="12">
-        <v>220.98000000000002</v>
-      </c>
-      <c r="R130" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="S130" s="6">
-        <v>3</v>
-      </c>
-      <c r="T130" s="6">
-        <f t="shared" si="6"/>
-        <v>27</v>
-      </c>
-      <c r="U130" s="6">
-        <v>4</v>
-      </c>
-      <c r="V130" s="6">
-        <v>23</v>
-      </c>
-      <c r="W130" s="6">
-        <v>81.929999999999993</v>
-      </c>
-      <c r="X130" s="6">
-        <v>22.046368726195382</v>
-      </c>
-      <c r="Y130" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="Z130" s="6">
-        <v>3</v>
-      </c>
-      <c r="AA130" s="6">
-        <f t="shared" si="11"/>
-        <v>24</v>
-      </c>
-      <c r="AB130" s="6">
-        <v>5</v>
-      </c>
-      <c r="AC130" s="6">
-        <v>19</v>
-      </c>
-      <c r="AD130" s="6">
-        <v>76.11</v>
-      </c>
-      <c r="AE130" s="6">
-        <v>18.246566222391351</v>
-      </c>
-      <c r="AF130" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="AG130" s="6">
-        <v>4</v>
-      </c>
-      <c r="AH130" s="6">
-        <f t="shared" si="12"/>
-        <v>26</v>
-      </c>
-      <c r="AI130" s="6">
-        <v>3</v>
-      </c>
-      <c r="AJ130" s="6">
-        <v>23</v>
-      </c>
-      <c r="AK130" s="6">
-        <v>71.61</v>
-      </c>
-      <c r="AL130" s="6">
-        <v>21.937802575723325</v>
-      </c>
-      <c r="AM130" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="AN130" s="6">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="AO130" s="6">
-        <f t="shared" si="8"/>
-        <v>77</v>
-      </c>
-      <c r="AP130" s="6">
-        <v>0.90725797227141491</v>
-      </c>
-      <c r="AQ130" s="6">
-        <v>0.75088749886384154</v>
-      </c>
-      <c r="AR130" s="6">
-        <v>0.90279022945363474</v>
-      </c>
-      <c r="AS130" s="6">
-        <f t="shared" si="9"/>
-        <v>0.8536452335296304</v>
-      </c>
-      <c r="AT130" s="6">
-        <v>63.788888888888891</v>
-      </c>
-      <c r="AU130" s="6">
-        <v>0.8125</v>
-      </c>
-      <c r="AV130" s="2">
-        <v>0.77365080998634783</v>
-      </c>
-      <c r="AW130" s="2">
-        <v>1429.1288872457803</v>
-      </c>
-      <c r="AX130" s="2">
-        <f t="shared" si="10"/>
-        <v>1.0392343198479499</v>
-      </c>
-      <c r="AY130" s="6">
-        <v>8.1050064553148768E-2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A131" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="G131" s="6">
-        <v>0</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="I131" s="12">
-        <v>76.510000000000005</v>
-      </c>
-      <c r="J131" s="12">
-        <v>54.85</v>
-      </c>
-      <c r="K131" s="12">
-        <v>27.66</v>
-      </c>
-      <c r="L131" s="12">
-        <v>150.9</v>
-      </c>
-      <c r="M131" s="12">
-        <v>213.77</v>
-      </c>
-      <c r="R131" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="S131" s="6">
-        <v>3</v>
-      </c>
-      <c r="T131" s="6">
-        <f t="shared" ref="T131:T167" si="13">U131+V131</f>
-        <v>14</v>
-      </c>
-      <c r="U131" s="6">
-        <v>2</v>
-      </c>
-      <c r="V131" s="6">
-        <v>12</v>
-      </c>
-      <c r="W131" s="6">
-        <v>80.490000000000009</v>
-      </c>
-      <c r="X131" s="6">
-        <v>27.508686717113946</v>
-      </c>
-      <c r="Y131" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="Z131" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA131" s="6">
-        <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
       <c r="AB131" s="6">
         <v>0</v>
       </c>
@@ -16658,11 +16432,11 @@
         <v>314</v>
       </c>
       <c r="AN131" s="6">
-        <f t="shared" ref="AN131:AN167" si="14">AVERAGE(S131,Z131,AG131)</f>
+        <f t="shared" ref="AN131:AN167" si="10">AVERAGE(S131,Z131,AG131)</f>
         <v>2.5</v>
       </c>
       <c r="AO131" s="6">
-        <f t="shared" ref="AO131:AO167" si="15">T131+AA131+AH131</f>
+        <f t="shared" ref="AO131:AO167" si="11">T131+AA131+AH131</f>
         <v>18</v>
       </c>
       <c r="AP131" s="6">
@@ -16672,7 +16446,6 @@
         <v>0.6938618873698198</v>
       </c>
       <c r="AS131" s="6">
-        <f t="shared" ref="AS131:AS167" si="16">AVERAGE(AP131:AR131)</f>
         <v>0.84419570719022352</v>
       </c>
       <c r="AT131" s="6">
@@ -16686,14 +16459,13 @@
         <v>629.06121084814981</v>
       </c>
       <c r="AX131" s="2">
-        <f t="shared" ref="AX131:AX167" si="17">(W131+AD131+AK131)/M131</f>
         <v>0.63011648032932599</v>
       </c>
       <c r="AY131" s="6">
         <v>0.26471618780658723</v>
       </c>
     </row>
-    <row r="132" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
         <v>127</v>
       </c>
@@ -16740,7 +16512,7 @@
         <v>3</v>
       </c>
       <c r="T132" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="U132" s="6">
@@ -16762,7 +16534,7 @@
         <v>4</v>
       </c>
       <c r="AA132" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="AB132" s="6">
@@ -16784,7 +16556,7 @@
         <v>4</v>
       </c>
       <c r="AH132" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="AI132" s="6">
@@ -16803,11 +16575,11 @@
         <v>314</v>
       </c>
       <c r="AN132" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3.6666666666666665</v>
       </c>
       <c r="AO132" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>46</v>
       </c>
       <c r="AP132" s="6">
@@ -16820,7 +16592,6 @@
         <v>0.77875617444967504</v>
       </c>
       <c r="AS132" s="6">
-        <f t="shared" si="16"/>
         <v>0.89296641021771161</v>
       </c>
       <c r="AT132" s="6">
@@ -16834,14 +16605,13 @@
         <v>687.14434991060557</v>
       </c>
       <c r="AX132" s="2">
-        <f t="shared" si="17"/>
-        <v>1.0907364844608773</v>
+        <v>1</v>
       </c>
       <c r="AY132" s="6">
         <v>0.37592501233349779</v>
       </c>
     </row>
-    <row r="133" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
         <v>128</v>
       </c>
@@ -16900,7 +16670,7 @@
         <v>2</v>
       </c>
       <c r="T133" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="U133" s="6">
@@ -16922,7 +16692,7 @@
         <v>2</v>
       </c>
       <c r="AA133" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="AB133" s="6">
@@ -16941,11 +16711,11 @@
         <v>314</v>
       </c>
       <c r="AN133" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="AO133" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="AP133" s="6">
@@ -16955,7 +16725,6 @@
         <v>0.84881052824286218</v>
       </c>
       <c r="AS133" s="6">
-        <f t="shared" si="16"/>
         <v>0.82679754978557785</v>
       </c>
       <c r="AT133" s="6">
@@ -16971,14 +16740,13 @@
         <v>802.85845352908632</v>
       </c>
       <c r="AX133" s="2">
-        <f t="shared" si="17"/>
         <v>0.57450116610520874</v>
       </c>
       <c r="AY133" s="6">
         <v>0.73844468784227824</v>
       </c>
     </row>
-    <row r="134" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
         <v>129</v>
       </c>
@@ -17037,7 +16805,7 @@
         <v>4</v>
       </c>
       <c r="T134" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="U134" s="6">
@@ -17059,7 +16827,7 @@
         <v>3</v>
       </c>
       <c r="AA134" s="6">
-        <f t="shared" ref="AA134:AA161" si="18">AB134+AC134</f>
+        <f t="shared" ref="AA134:AA161" si="12">AB134+AC134</f>
         <v>19</v>
       </c>
       <c r="AB134" s="6">
@@ -17078,11 +16846,11 @@
         <v>314</v>
       </c>
       <c r="AN134" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3.5</v>
       </c>
       <c r="AO134" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>39</v>
       </c>
       <c r="AP134" s="6">
@@ -17092,7 +16860,6 @@
         <v>0.62972864287831054</v>
       </c>
       <c r="AS134" s="6">
-        <f t="shared" si="16"/>
         <v>0.80226393876822322</v>
       </c>
       <c r="AT134" s="6">
@@ -17106,14 +16873,13 @@
         <v>530.59028467072994</v>
       </c>
       <c r="AX134" s="2">
-        <f t="shared" si="17"/>
         <v>0.66538412209824283</v>
       </c>
       <c r="AY134" s="6">
         <v>0.49126922074537405</v>
       </c>
     </row>
-    <row r="135" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
         <v>130</v>
       </c>
@@ -17172,7 +16938,7 @@
         <v>3</v>
       </c>
       <c r="T135" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="U135" s="6">
@@ -17194,7 +16960,7 @@
         <v>4</v>
       </c>
       <c r="AA135" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>17</v>
       </c>
       <c r="AB135" s="6">
@@ -17216,7 +16982,7 @@
         <v>3</v>
       </c>
       <c r="AH135" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="AI135" s="6">
@@ -17235,11 +17001,11 @@
         <v>314</v>
       </c>
       <c r="AN135" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3.3333333333333335</v>
       </c>
       <c r="AO135" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>52</v>
       </c>
       <c r="AP135" s="6">
@@ -17252,7 +17018,6 @@
         <v>0.71885349851089697</v>
       </c>
       <c r="AS135" s="6">
-        <f t="shared" si="16"/>
         <v>0.71320952385855352</v>
       </c>
       <c r="AT135" s="6">
@@ -17268,14 +17033,13 @@
         <v>756.47235712171812</v>
       </c>
       <c r="AX135" s="2">
-        <f t="shared" si="17"/>
         <v>0.88844058906596746</v>
       </c>
       <c r="AY135" s="6">
         <v>0.60609280906836693</v>
       </c>
     </row>
-    <row r="136" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
         <v>131</v>
       </c>
@@ -17322,7 +17086,7 @@
         <v>4</v>
       </c>
       <c r="T136" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>47</v>
       </c>
       <c r="U136" s="6">
@@ -17344,7 +17108,7 @@
         <v>4</v>
       </c>
       <c r="AA136" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>17</v>
       </c>
       <c r="AB136" s="6">
@@ -17363,11 +17127,11 @@
         <v>324</v>
       </c>
       <c r="AN136" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="AO136" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>64</v>
       </c>
       <c r="AP136" s="6">
@@ -17377,7 +17141,6 @@
         <v>0.80999316467015847</v>
       </c>
       <c r="AS136" s="6">
-        <f t="shared" si="16"/>
         <v>0.84263907471189281</v>
       </c>
       <c r="AT136" s="6">
@@ -17393,11 +17156,10 @@
         <v>429.04569503197973</v>
       </c>
       <c r="AX136" s="2">
-        <f t="shared" si="17"/>
         <v>0.65241190557646245</v>
       </c>
     </row>
-    <row r="137" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
         <v>132</v>
       </c>
@@ -17444,7 +17206,7 @@
         <v>2</v>
       </c>
       <c r="T137" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="U137" s="6">
@@ -17466,7 +17228,7 @@
         <v>4</v>
       </c>
       <c r="AA137" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
       <c r="AB137" s="6">
@@ -17488,7 +17250,7 @@
         <v>3</v>
       </c>
       <c r="AH137" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="AI137" s="6">
@@ -17507,11 +17269,11 @@
         <v>314</v>
       </c>
       <c r="AN137" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO137" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>52</v>
       </c>
       <c r="AP137" s="6">
@@ -17524,7 +17286,6 @@
         <v>0.67592944052540793</v>
       </c>
       <c r="AS137" s="6">
-        <f t="shared" si="16"/>
         <v>0.69746642607927922</v>
       </c>
       <c r="AT137" s="6">
@@ -17540,14 +17301,13 @@
         <v>772.91783490204466</v>
       </c>
       <c r="AX137" s="2">
-        <f t="shared" si="17"/>
         <v>0.76739401496259352</v>
       </c>
       <c r="AY137" s="6">
         <v>0.22387459807073956</v>
       </c>
     </row>
-    <row r="138" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
         <v>133</v>
       </c>
@@ -17594,7 +17354,7 @@
         <v>4</v>
       </c>
       <c r="T138" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="U138" s="6">
@@ -17613,18 +17373,17 @@
         <v>314</v>
       </c>
       <c r="AN138" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="AO138" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>27</v>
       </c>
       <c r="AP138" s="6">
         <v>0.79986868087960838</v>
       </c>
       <c r="AS138" s="6">
-        <f t="shared" si="16"/>
         <v>0.79986868087960838</v>
       </c>
       <c r="AT138" s="6">
@@ -17640,11 +17399,10 @@
         <v>238.25547620473057</v>
       </c>
       <c r="AX138" s="2">
-        <f t="shared" si="17"/>
         <v>0.53939188425454954</v>
       </c>
     </row>
-    <row r="139" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
         <v>134</v>
       </c>
@@ -17703,7 +17461,7 @@
         <v>3</v>
       </c>
       <c r="T139" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="U139" s="6">
@@ -17722,18 +17480,17 @@
         <v>314</v>
       </c>
       <c r="AN139" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO139" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="AP139" s="6">
         <v>1</v>
       </c>
       <c r="AS139" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT139" s="6">
@@ -17747,14 +17504,13 @@
         <v>201.80766494996902</v>
       </c>
       <c r="AX139" s="2">
-        <f t="shared" si="17"/>
         <v>0.31197218082463979</v>
       </c>
       <c r="AY139" s="6">
         <v>0.46256196190973131</v>
       </c>
     </row>
-    <row r="140" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
         <v>135</v>
       </c>
@@ -17801,7 +17557,7 @@
         <v>4</v>
       </c>
       <c r="T140" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="U140" s="6">
@@ -17820,18 +17576,17 @@
         <v>314</v>
       </c>
       <c r="AN140" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="AO140" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>32</v>
       </c>
       <c r="AP140" s="6">
         <v>0.98366570729580272</v>
       </c>
       <c r="AS140" s="6">
-        <f t="shared" si="16"/>
         <v>0.98366570729580272</v>
       </c>
       <c r="AT140" s="6">
@@ -17845,14 +17600,13 @@
         <v>213.81689661067799</v>
       </c>
       <c r="AX140" s="2">
-        <f t="shared" si="17"/>
         <v>0.76055883065493024</v>
       </c>
       <c r="AY140" s="6">
         <v>0.75419545903257645</v>
       </c>
     </row>
-    <row r="141" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
         <v>136</v>
       </c>
@@ -17899,7 +17653,7 @@
         <v>4</v>
       </c>
       <c r="T141" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="U141" s="6">
@@ -17921,7 +17675,7 @@
         <v>3</v>
       </c>
       <c r="AA141" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="AB141" s="6">
@@ -17940,11 +17694,11 @@
         <v>314</v>
       </c>
       <c r="AN141" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3.5</v>
       </c>
       <c r="AO141" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>32</v>
       </c>
       <c r="AP141" s="6">
@@ -17954,7 +17708,6 @@
         <v>0.78248931470543104</v>
       </c>
       <c r="AS141" s="6">
-        <f t="shared" si="16"/>
         <v>0.88365323965532516</v>
       </c>
       <c r="AT141" s="6">
@@ -17968,14 +17721,13 @@
         <v>432.29306175566927</v>
       </c>
       <c r="AX141" s="2">
-        <f t="shared" si="17"/>
         <v>0.61659318637274552</v>
       </c>
       <c r="AY141" s="6">
         <v>0.42687620269403465</v>
       </c>
     </row>
-    <row r="142" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
         <v>137</v>
       </c>
@@ -18022,7 +17774,7 @@
         <v>2</v>
       </c>
       <c r="T142" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="U142" s="6">
@@ -18041,18 +17793,17 @@
         <v>314</v>
       </c>
       <c r="AN142" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="AO142" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
       <c r="AP142" s="6">
         <v>1</v>
       </c>
       <c r="AS142" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT142" s="6">
@@ -18066,14 +17817,13 @@
         <v>293.89678226183776</v>
       </c>
       <c r="AX142" s="2">
-        <f t="shared" si="17"/>
         <v>0.65674418604651164</v>
       </c>
       <c r="AY142" s="6">
         <v>0.5458980044345898</v>
       </c>
     </row>
-    <row r="143" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
         <v>138</v>
       </c>
@@ -18120,7 +17870,7 @@
         <v>3</v>
       </c>
       <c r="T143" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="U143" s="6">
@@ -18139,18 +17889,17 @@
         <v>315</v>
       </c>
       <c r="AN143" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO143" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="AP143" s="6">
         <v>0.74688165307366483</v>
       </c>
       <c r="AS143" s="6">
-        <f t="shared" si="16"/>
         <v>0.74688165307366483</v>
       </c>
       <c r="AT143" s="6">
@@ -18166,14 +17915,13 @@
         <v>100.11425742295327</v>
       </c>
       <c r="AX143" s="2">
-        <f t="shared" si="17"/>
         <v>0.29498347852207873</v>
       </c>
       <c r="AY143" s="6">
         <v>0.99161887957653283</v>
       </c>
     </row>
-    <row r="144" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>139</v>
       </c>
@@ -18232,7 +17980,7 @@
         <v>2</v>
       </c>
       <c r="T144" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="U144" s="6">
@@ -18251,18 +17999,17 @@
         <v>314</v>
       </c>
       <c r="AN144" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="AO144" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AP144" s="6">
         <v>0.4392322461322693</v>
       </c>
       <c r="AS144" s="6">
-        <f t="shared" si="16"/>
         <v>0.4392322461322693</v>
       </c>
       <c r="AT144" s="6">
@@ -18278,14 +18025,13 @@
         <v>49.560419106537701</v>
       </c>
       <c r="AX144" s="2">
-        <f t="shared" si="17"/>
         <v>0.32485202552079334</v>
       </c>
       <c r="AY144" s="6">
         <v>0.65174897119341557</v>
       </c>
     </row>
-    <row r="145" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
         <v>140</v>
       </c>
@@ -18332,7 +18078,7 @@
         <v>3</v>
       </c>
       <c r="T145" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="U145" s="6">
@@ -18354,7 +18100,7 @@
         <v>3</v>
       </c>
       <c r="AA145" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="AB145" s="6">
@@ -18376,7 +18122,7 @@
         <v>2</v>
       </c>
       <c r="AH145" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="AI145" s="6">
@@ -18395,11 +18141,11 @@
         <v>314</v>
       </c>
       <c r="AN145" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2.6666666666666665</v>
       </c>
       <c r="AO145" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="AP145" s="6">
@@ -18412,7 +18158,6 @@
         <v>0.9797081524520318</v>
       </c>
       <c r="AS145" s="6">
-        <f t="shared" si="16"/>
         <v>0.88337221600725668</v>
       </c>
       <c r="AT145" s="6">
@@ -18426,14 +18171,13 @@
         <v>632.17167828485583</v>
       </c>
       <c r="AX145" s="2">
-        <f t="shared" si="17"/>
         <v>0.78916510318949329</v>
       </c>
       <c r="AY145" s="6">
         <v>0.12202562538133008</v>
       </c>
     </row>
-    <row r="146" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
         <v>141</v>
       </c>
@@ -18492,7 +18236,7 @@
         <v>2</v>
       </c>
       <c r="T146" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="U146" s="6">
@@ -18511,18 +18255,17 @@
         <v>314</v>
       </c>
       <c r="AN146" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="AO146" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="AP146" s="6">
         <v>0.54432881656500687</v>
       </c>
       <c r="AS146" s="6">
-        <f t="shared" si="16"/>
         <v>0.54432881656500687</v>
       </c>
       <c r="AT146" s="6">
@@ -18538,14 +18281,13 @@
         <v>74.427701188806736</v>
       </c>
       <c r="AX146" s="2">
-        <f t="shared" si="17"/>
         <v>0.35030512235714723</v>
       </c>
       <c r="AY146" s="6">
         <v>0.91104675217211406</v>
       </c>
     </row>
-    <row r="147" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
         <v>268</v>
       </c>
@@ -18604,7 +18346,7 @@
         <v>3</v>
       </c>
       <c r="T147" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="U147" s="6">
@@ -18623,18 +18365,17 @@
         <v>314</v>
       </c>
       <c r="AN147" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO147" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AP147" s="6">
         <v>1</v>
       </c>
       <c r="AS147" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT147" s="6">
@@ -18648,14 +18389,13 @@
         <v>112.33685020319277</v>
       </c>
       <c r="AX147" s="2">
-        <f t="shared" si="17"/>
         <v>0.39479300042680321</v>
       </c>
       <c r="AY147" s="6">
         <v>0.85944820406038525</v>
       </c>
     </row>
-    <row r="148" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
         <v>142</v>
       </c>
@@ -18702,7 +18442,7 @@
         <v>3</v>
       </c>
       <c r="T148" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="U148" s="6">
@@ -18721,18 +18461,17 @@
         <v>314</v>
       </c>
       <c r="AN148" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO148" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="AP148" s="6">
         <v>1</v>
       </c>
       <c r="AS148" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT148" s="6">
@@ -18746,14 +18485,13 @@
         <v>107.4549034268789</v>
       </c>
       <c r="AX148" s="2">
-        <f t="shared" si="17"/>
         <v>0.63992869875222813</v>
       </c>
       <c r="AY148" s="6">
         <v>0.24540266328471783</v>
       </c>
     </row>
-    <row r="149" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
         <v>143</v>
       </c>
@@ -18800,7 +18538,7 @@
         <v>3</v>
       </c>
       <c r="T149" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="U149" s="6">
@@ -18819,18 +18557,17 @@
         <v>314</v>
       </c>
       <c r="AN149" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO149" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>19</v>
       </c>
       <c r="AP149" s="6">
         <v>1</v>
       </c>
       <c r="AS149" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT149" s="6">
@@ -18844,14 +18581,13 @@
         <v>101.62024055702028</v>
       </c>
       <c r="AX149" s="2">
-        <f t="shared" si="17"/>
         <v>0.55851721094439544</v>
       </c>
       <c r="AY149" s="6">
         <v>8.7415540540540529E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
         <v>144</v>
       </c>
@@ -18898,7 +18634,7 @@
         <v>4</v>
       </c>
       <c r="T150" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="U150" s="6">
@@ -18917,18 +18653,17 @@
         <v>314</v>
       </c>
       <c r="AN150" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="AO150" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>29</v>
       </c>
       <c r="AP150" s="6">
         <v>1</v>
       </c>
       <c r="AS150" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT150" s="6">
@@ -18942,11 +18677,10 @@
         <v>439.23905389176014</v>
       </c>
       <c r="AX150" s="2">
-        <f t="shared" si="17"/>
         <v>0.41385355328808376</v>
       </c>
     </row>
-    <row r="151" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
         <v>145</v>
       </c>
@@ -18993,7 +18727,7 @@
         <v>4</v>
       </c>
       <c r="T151" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="U151" s="6">
@@ -19012,18 +18746,17 @@
         <v>314</v>
       </c>
       <c r="AN151" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="AO151" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="AP151" s="6">
         <v>0.84454421042342931</v>
       </c>
       <c r="AS151" s="6">
-        <f t="shared" si="16"/>
         <v>0.84454421042342931</v>
       </c>
       <c r="AT151" s="6">
@@ -19039,11 +18772,10 @@
         <v>190.68511895998034</v>
       </c>
       <c r="AX151" s="2">
-        <f t="shared" si="17"/>
         <v>0.40628728227153427</v>
       </c>
     </row>
-    <row r="152" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
         <v>146</v>
       </c>
@@ -19090,7 +18822,7 @@
         <v>4</v>
       </c>
       <c r="T152" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="U152" s="6">
@@ -19112,7 +18844,7 @@
         <v>3</v>
       </c>
       <c r="AA152" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="AB152" s="6">
@@ -19134,7 +18866,7 @@
         <v>2</v>
       </c>
       <c r="AH152" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="AI152" s="6">
@@ -19153,11 +18885,11 @@
         <v>314</v>
       </c>
       <c r="AN152" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO152" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>81</v>
       </c>
       <c r="AP152" s="6">
@@ -19170,7 +18902,6 @@
         <v>0.96217918778722056</v>
       </c>
       <c r="AS152" s="6">
-        <f t="shared" si="16"/>
         <v>0.9259508178768705</v>
       </c>
       <c r="AT152" s="6">
@@ -19184,14 +18915,13 @@
         <v>1563.6994596370193</v>
       </c>
       <c r="AX152" s="2">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AY152" s="6">
         <v>0.18088138566103926</v>
       </c>
     </row>
-    <row r="153" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
         <v>147</v>
       </c>
@@ -19238,7 +18968,7 @@
         <v>3</v>
       </c>
       <c r="T153" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="U153" s="6">
@@ -19260,7 +18990,7 @@
         <v>4</v>
       </c>
       <c r="AA153" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>19</v>
       </c>
       <c r="AB153" s="6">
@@ -19282,7 +19012,7 @@
         <v>3</v>
       </c>
       <c r="AH153" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="AI153" s="6">
@@ -19301,11 +19031,11 @@
         <v>314</v>
       </c>
       <c r="AN153" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3.3333333333333335</v>
       </c>
       <c r="AO153" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>72</v>
       </c>
       <c r="AP153" s="6">
@@ -19318,7 +19048,6 @@
         <v>0.76164821870266164</v>
       </c>
       <c r="AS153" s="6">
-        <f t="shared" si="16"/>
         <v>0.78586962736319421</v>
       </c>
       <c r="AT153" s="6">
@@ -19334,11 +19063,10 @@
         <v>833.18954101825022</v>
       </c>
       <c r="AX153" s="2">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
         <v>148</v>
       </c>
@@ -19397,7 +19125,7 @@
         <v>3</v>
       </c>
       <c r="T154" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="U154" s="6">
@@ -19419,7 +19147,7 @@
         <v>3</v>
       </c>
       <c r="AA154" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>19</v>
       </c>
       <c r="AB154" s="6">
@@ -19438,11 +19166,11 @@
         <v>314</v>
       </c>
       <c r="AN154" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO154" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="AP154" s="6">
@@ -19452,7 +19180,6 @@
         <v>0.83545784249957122</v>
       </c>
       <c r="AS154" s="6">
-        <f t="shared" si="16"/>
         <v>0.89278291852546621</v>
       </c>
       <c r="AT154" s="6">
@@ -19466,14 +19193,13 @@
         <v>632.73557409822365</v>
       </c>
       <c r="AX154" s="2">
-        <f t="shared" si="17"/>
         <v>0.62469613259668511</v>
       </c>
       <c r="AY154" s="6">
         <v>0.53051798086440116</v>
       </c>
     </row>
-    <row r="155" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
         <v>149</v>
       </c>
@@ -19520,7 +19246,7 @@
         <v>3</v>
       </c>
       <c r="T155" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="U155" s="6">
@@ -19542,7 +19268,7 @@
         <v>2</v>
       </c>
       <c r="AA155" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="AB155" s="6">
@@ -19564,7 +19290,7 @@
         <v>4</v>
       </c>
       <c r="AH155" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="AI155" s="6">
@@ -19583,11 +19309,11 @@
         <v>314</v>
       </c>
       <c r="AN155" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO155" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>48</v>
       </c>
       <c r="AP155" s="6">
@@ -19600,7 +19326,6 @@
         <v>0.47707149047809061</v>
       </c>
       <c r="AS155" s="6">
-        <f t="shared" si="16"/>
         <v>0.73599907904192552</v>
       </c>
       <c r="AT155" s="6">
@@ -19616,11 +19341,10 @@
         <v>1234.5190981221817</v>
       </c>
       <c r="AX155" s="2">
-        <f t="shared" si="17"/>
         <v>0.75872233497632158</v>
       </c>
     </row>
-    <row r="156" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>150</v>
       </c>
@@ -19667,7 +19391,7 @@
         <v>3</v>
       </c>
       <c r="T156" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="U156" s="6">
@@ -19689,7 +19413,7 @@
         <v>3</v>
       </c>
       <c r="AA156" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="AB156" s="6">
@@ -19708,11 +19432,11 @@
         <v>314</v>
       </c>
       <c r="AN156" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO156" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AP156" s="6">
@@ -19722,7 +19446,6 @@
         <v>0.78213824487768224</v>
       </c>
       <c r="AS156" s="6">
-        <f t="shared" si="16"/>
         <v>0.62888496477333466</v>
       </c>
       <c r="AT156" s="6">
@@ -19738,14 +19461,13 @@
         <v>353.65889350638042</v>
       </c>
       <c r="AX156" s="2">
-        <f t="shared" si="17"/>
         <v>0.76780808148495605</v>
       </c>
       <c r="AY156" s="6">
         <v>0.68963943404837968</v>
       </c>
     </row>
-    <row r="157" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
         <v>151</v>
       </c>
@@ -19792,7 +19514,7 @@
         <v>2</v>
       </c>
       <c r="T157" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="U157" s="6">
@@ -19814,7 +19536,7 @@
         <v>3</v>
       </c>
       <c r="AA157" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
       <c r="AB157" s="6">
@@ -19833,11 +19555,11 @@
         <v>314</v>
       </c>
       <c r="AN157" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
       <c r="AO157" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>35</v>
       </c>
       <c r="AP157" s="6">
@@ -19847,7 +19569,6 @@
         <v>0.67801650938838354</v>
       </c>
       <c r="AS157" s="6">
-        <f t="shared" si="16"/>
         <v>0.63624952746877872</v>
       </c>
       <c r="AT157" s="6">
@@ -19863,14 +19584,13 @@
         <v>485.20002125056351</v>
       </c>
       <c r="AX157" s="2">
-        <f t="shared" si="17"/>
         <v>0.77634652606287113</v>
       </c>
       <c r="AY157" s="6">
         <v>0.51370280146163216</v>
       </c>
     </row>
-    <row r="158" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
         <v>152</v>
       </c>
@@ -19917,7 +19637,7 @@
         <v>3</v>
       </c>
       <c r="T158" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="U158" s="6">
@@ -19936,18 +19656,17 @@
         <v>314</v>
       </c>
       <c r="AN158" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO158" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="AP158" s="6">
         <v>0.68680846990046163</v>
       </c>
       <c r="AS158" s="6">
-        <f t="shared" si="16"/>
         <v>0.68680846990046163</v>
       </c>
       <c r="AT158" s="6">
@@ -19963,14 +19682,13 @@
         <v>62.652124658276293</v>
       </c>
       <c r="AX158" s="2">
-        <f t="shared" si="17"/>
         <v>0.22577137420144081</v>
       </c>
       <c r="AY158" s="6">
         <v>0.36735653809971774</v>
       </c>
     </row>
-    <row r="159" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>153</v>
       </c>
@@ -20017,7 +19735,7 @@
         <v>3</v>
       </c>
       <c r="T159" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="U159" s="6">
@@ -20036,18 +19754,17 @@
         <v>314</v>
       </c>
       <c r="AN159" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO159" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>27</v>
       </c>
       <c r="AP159" s="6">
         <v>0.76668624907242333</v>
       </c>
       <c r="AS159" s="6">
-        <f t="shared" si="16"/>
         <v>0.76668624907242333</v>
       </c>
       <c r="AT159" s="6">
@@ -20063,14 +19780,13 @@
         <v>221.16272385336339</v>
       </c>
       <c r="AX159" s="2">
-        <f t="shared" si="17"/>
         <v>0.659493851873034</v>
       </c>
       <c r="AY159" s="6">
         <v>0.82460414129110826</v>
       </c>
     </row>
-    <row r="160" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
         <v>154</v>
       </c>
@@ -20117,7 +19833,7 @@
         <v>3</v>
       </c>
       <c r="T160" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="U160" s="6">
@@ -20136,18 +19852,17 @@
         <v>314</v>
       </c>
       <c r="AN160" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO160" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="AP160" s="6">
         <v>1</v>
       </c>
       <c r="AS160" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT160" s="6">
@@ -20161,14 +19876,13 @@
         <v>91.220742087680904</v>
       </c>
       <c r="AX160" s="2">
-        <f t="shared" si="17"/>
         <v>0.30622417524758966</v>
       </c>
       <c r="AY160" s="6">
         <v>0.57280701754385965</v>
       </c>
     </row>
-    <row r="161" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
         <v>155</v>
       </c>
@@ -20215,7 +19929,7 @@
         <v>3</v>
       </c>
       <c r="T161" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="U161" s="6">
@@ -20237,7 +19951,7 @@
         <v>3</v>
       </c>
       <c r="AA161" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="AB161" s="6">
@@ -20256,11 +19970,11 @@
         <v>314</v>
       </c>
       <c r="AN161" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO161" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="AP161" s="6">
@@ -20270,7 +19984,6 @@
         <v>0.91673840891215019</v>
       </c>
       <c r="AS161" s="6">
-        <f t="shared" si="16"/>
         <v>0.94368495437778366</v>
       </c>
       <c r="AT161" s="6">
@@ -20284,14 +19997,13 @@
         <v>731.936470121512</v>
       </c>
       <c r="AX161" s="2">
-        <f t="shared" si="17"/>
         <v>0.85645867542419252</v>
       </c>
       <c r="AY161" s="6">
         <v>0.97650375939849621</v>
       </c>
     </row>
-    <row r="162" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>156</v>
       </c>
@@ -20338,7 +20050,7 @@
         <v>3</v>
       </c>
       <c r="T162" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="U162" s="6">
@@ -20357,18 +20069,17 @@
         <v>314</v>
       </c>
       <c r="AN162" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO162" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>49</v>
       </c>
       <c r="AP162" s="6">
         <v>0.86085562287871809</v>
       </c>
       <c r="AS162" s="6">
-        <f t="shared" si="16"/>
         <v>0.86085562287871809</v>
       </c>
       <c r="AT162" s="6">
@@ -20384,14 +20095,13 @@
         <v>481.08985353027003</v>
       </c>
       <c r="AX162" s="2">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AY162" s="6">
         <v>0.65825562260010972</v>
       </c>
     </row>
-    <row r="163" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
         <v>157</v>
       </c>
@@ -20438,7 +20148,7 @@
         <v>3</v>
       </c>
       <c r="T163" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="U163" s="6">
@@ -20457,18 +20167,17 @@
         <v>314</v>
       </c>
       <c r="AN163" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO163" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="AP163" s="6">
         <v>0.90472993857307404</v>
       </c>
       <c r="AS163" s="6">
-        <f t="shared" si="16"/>
         <v>0.90472993857307404</v>
       </c>
       <c r="AT163" s="6">
@@ -20484,14 +20193,13 @@
         <v>397.53068099372842</v>
       </c>
       <c r="AX163" s="2">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AY163" s="6">
         <v>0.78913260219341974</v>
       </c>
     </row>
-    <row r="164" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
         <v>158</v>
       </c>
@@ -20538,7 +20246,7 @@
         <v>3</v>
       </c>
       <c r="T164" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>51</v>
       </c>
       <c r="U164" s="6">
@@ -20557,18 +20265,17 @@
         <v>314</v>
       </c>
       <c r="AN164" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO164" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>51</v>
       </c>
       <c r="AP164" s="6">
         <v>1</v>
       </c>
       <c r="AS164" s="6">
-        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AT164" s="6">
@@ -20582,14 +20289,13 @@
         <v>535.07821361659637</v>
       </c>
       <c r="AX164" s="2">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AY164" s="6">
         <v>0.60865139949109426</v>
       </c>
     </row>
-    <row r="165" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
         <v>159</v>
       </c>
@@ -20636,7 +20342,7 @@
         <v>4</v>
       </c>
       <c r="T165" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="U165" s="6">
@@ -20655,18 +20361,17 @@
         <v>314</v>
       </c>
       <c r="AN165" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="AO165" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>87</v>
       </c>
       <c r="AP165" s="6">
         <v>0.92307871410652198</v>
       </c>
       <c r="AS165" s="6">
-        <f t="shared" si="16"/>
         <v>0.92307871410652198</v>
       </c>
       <c r="AT165" s="6">
@@ -20682,14 +20387,13 @@
         <v>468.89924825657511</v>
       </c>
       <c r="AX165" s="2">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="AY165" s="6">
         <v>0.29351032448377579</v>
       </c>
     </row>
-    <row r="166" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
         <v>160</v>
       </c>
@@ -20748,7 +20452,7 @@
         <v>2</v>
       </c>
       <c r="T166" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="U166" s="6">
@@ -20767,18 +20471,17 @@
         <v>314</v>
       </c>
       <c r="AN166" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="AO166" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="AP166" s="6">
         <v>0.34860332032072772</v>
       </c>
       <c r="AS166" s="6">
-        <f t="shared" si="16"/>
         <v>0.34860332032072772</v>
       </c>
       <c r="AT166" s="6">
@@ -20794,14 +20497,13 @@
         <v>21.974384598077229</v>
       </c>
       <c r="AX166" s="2">
-        <f t="shared" si="17"/>
         <v>0.41179487179487179</v>
       </c>
       <c r="AY166" s="6">
         <v>0.40686823441582681</v>
       </c>
     </row>
-    <row r="167" spans="1:51" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:51" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
         <v>161</v>
       </c>
@@ -20848,7 +20550,7 @@
         <v>3</v>
       </c>
       <c r="T167" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="U167" s="6">
@@ -20867,18 +20569,17 @@
         <v>314</v>
       </c>
       <c r="AN167" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="AO167" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>32</v>
       </c>
       <c r="AP167" s="6">
         <v>0.80826863764989021</v>
       </c>
       <c r="AS167" s="6">
-        <f t="shared" si="16"/>
         <v>0.80826863764989021</v>
       </c>
       <c r="AT167" s="6">
@@ -20894,7 +20595,6 @@
         <v>165.27198249984968</v>
       </c>
       <c r="AX167" s="2">
-        <f t="shared" si="17"/>
         <v>0.54642433820624259</v>
       </c>
       <c r="AY167" s="6">
@@ -20904,6 +20604,16 @@
   </sheetData>
   <autoFilter ref="A1:AY167" xr:uid="{8C3B0A72-F028-47A8-9FE2-6569D238CC68}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="AX1:AX1048576">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AS1:AS1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -20911,23 +20621,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023C39E0-1681-4D3E-A16C-52E1C75CE2BB}">
   <dimension ref="A1:O92"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" style="4" customWidth="1"/>
-    <col min="5" max="6" width="8.6640625" style="4"/>
-    <col min="7" max="7" width="9.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="4"/>
-    <col min="9" max="9" width="11.109375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" style="4" customWidth="1"/>
-    <col min="11" max="14" width="8.6640625" style="4"/>
-    <col min="15" max="15" width="15.77734375" style="4" customWidth="1"/>
-    <col min="16" max="16384" width="8.6640625" style="4"/>
+    <col min="1" max="1" width="19.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="12.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.625" style="4"/>
+    <col min="7" max="7" width="9.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="4"/>
+    <col min="9" max="9" width="11.125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="4" customWidth="1"/>
+    <col min="11" max="14" width="8.625" style="4"/>
+    <col min="15" max="15" width="15.75" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="8.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>264</v>
       </c>
@@ -20974,7 +20684,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>203</v>
       </c>
@@ -21021,7 +20731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>204</v>
       </c>
@@ -21068,7 +20778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>205</v>
       </c>
@@ -21115,7 +20825,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>206</v>
       </c>
@@ -21162,7 +20872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>207</v>
       </c>
@@ -21209,7 +20919,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>208</v>
       </c>
@@ -21256,7 +20966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>209</v>
       </c>
@@ -21303,7 +21013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>210</v>
       </c>
@@ -21350,7 +21060,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>320</v>
       </c>
@@ -21397,7 +21107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>211</v>
       </c>
@@ -21444,7 +21154,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>212</v>
       </c>
@@ -21491,7 +21201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>213</v>
       </c>
@@ -21538,7 +21248,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>214</v>
       </c>
@@ -21585,7 +21295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>215</v>
       </c>
@@ -21632,7 +21342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>216</v>
       </c>
@@ -21679,7 +21389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>217</v>
       </c>
@@ -21726,7 +21436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>218</v>
       </c>
@@ -21773,7 +21483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>219</v>
       </c>
@@ -21808,7 +21518,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>220</v>
       </c>
@@ -21855,7 +21565,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>221</v>
       </c>
@@ -21902,7 +21612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>222</v>
       </c>
@@ -21949,7 +21659,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>223</v>
       </c>
@@ -21996,7 +21706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>224</v>
       </c>
@@ -22043,7 +21753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>225</v>
       </c>
@@ -22090,7 +21800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>226</v>
       </c>
@@ -22137,7 +21847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>227</v>
       </c>
@@ -22184,7 +21894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>228</v>
       </c>
@@ -22231,7 +21941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>229</v>
       </c>
@@ -22278,7 +21988,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>230</v>
       </c>
@@ -22325,7 +22035,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>231</v>
       </c>
@@ -22372,7 +22082,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>232</v>
       </c>
@@ -22419,7 +22129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>233</v>
       </c>
@@ -22466,7 +22176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>234</v>
       </c>
@@ -22513,7 +22223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>235</v>
       </c>
@@ -22560,7 +22270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>236</v>
       </c>
@@ -22607,7 +22317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>237</v>
       </c>
@@ -22654,7 +22364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>238</v>
       </c>
@@ -22701,7 +22411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>239</v>
       </c>
@@ -22748,7 +22458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>240</v>
       </c>
@@ -22795,7 +22505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>241</v>
       </c>
@@ -22842,7 +22552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>242</v>
       </c>
@@ -22889,7 +22599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>243</v>
       </c>
@@ -22936,7 +22646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>244</v>
       </c>
@@ -22983,7 +22693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>245</v>
       </c>
@@ -23030,7 +22740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>246</v>
       </c>
@@ -23077,7 +22787,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>247</v>
       </c>
@@ -23112,7 +22822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>248</v>
       </c>
@@ -23159,7 +22869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>249</v>
       </c>
@@ -23206,7 +22916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>250</v>
       </c>
@@ -23253,7 +22963,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>251</v>
       </c>
@@ -23300,7 +23010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>252</v>
       </c>
@@ -23347,7 +23057,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>253</v>
       </c>
@@ -23394,7 +23104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>254</v>
       </c>
@@ -23441,7 +23151,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>255</v>
       </c>
@@ -23488,7 +23198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>256</v>
       </c>
@@ -23535,7 +23245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>257</v>
       </c>
@@ -23582,7 +23292,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>361</v>
       </c>
@@ -23629,7 +23339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>258</v>
       </c>
@@ -23676,100 +23386,100 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B64" s="10"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B65" s="10"/>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B66" s="10"/>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B67" s="10"/>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B68" s="10"/>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B69" s="10"/>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B70" s="10"/>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B71" s="10"/>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B72" s="10"/>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B73" s="10"/>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B74" s="10"/>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B75" s="10"/>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B76" s="10"/>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B77" s="10"/>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B78" s="10"/>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B79" s="10"/>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B80" s="10"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B81" s="10"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B82" s="10"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B83" s="10"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B84" s="10"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B85" s="10"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B86" s="10"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B87" s="10"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B88" s="10"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B89" s="10"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B90" s="10"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B91" s="10"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B92" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B92">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
